--- a/englisch.xlsx
+++ b/englisch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nutzer\Desktop\Vokabellernspiel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EF111A2-80EB-4CDF-9F8B-39CA63F095EB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{662A5842-84D9-479A-9C8F-A8B05876858E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="8655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17970" windowHeight="5115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -17070,9 +17070,6 @@
     <t>Du siehst europäisch aus.</t>
   </si>
   <si>
-    <t>Das ist sehr deutsch.</t>
-  </si>
-  <si>
     <t>That is very german.</t>
   </si>
   <si>
@@ -17929,6 +17926,9 @@
   </si>
   <si>
     <t>Ihr (formell Du)</t>
+  </si>
+  <si>
+    <t>Das ist sehr deutsch .</t>
   </si>
 </sst>
 </file>
@@ -19067,7 +19067,7 @@
         <v>174</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>5751</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -19080,7 +19080,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>5963</v>
+        <v>5962</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>177</v>
@@ -19112,7 +19112,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>5964</v>
+        <v>5963</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>184</v>
@@ -19120,7 +19120,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>5965</v>
+        <v>5964</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>185</v>
@@ -19152,7 +19152,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>5966</v>
+        <v>5965</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>191</v>
@@ -19163,7 +19163,7 @@
         <v>32</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>5961</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -19184,7 +19184,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>5967</v>
+        <v>5966</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>195</v>
@@ -19192,7 +19192,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>5968</v>
+        <v>5967</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>196</v>
@@ -19235,7 +19235,7 @@
         <v>205</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>5726</v>
+        <v>5725</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -19251,7 +19251,7 @@
         <v>208</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>5856</v>
+        <v>5855</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -19283,7 +19283,7 @@
         <v>215</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>5727</v>
+        <v>5726</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -19291,7 +19291,7 @@
         <v>216</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>5728</v>
+        <v>5727</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -19419,7 +19419,7 @@
         <v>247</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>5960</v>
+        <v>5959</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -19443,7 +19443,7 @@
         <v>252</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>5729</v>
+        <v>5728</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -19507,12 +19507,12 @@
         <v>267</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>5730</v>
+        <v>5729</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>5750</v>
+        <v>5749</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>268</v>
@@ -19523,7 +19523,7 @@
         <v>269</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>5752</v>
+        <v>5751</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -19587,7 +19587,7 @@
         <v>284</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>5959</v>
+        <v>5958</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -19603,7 +19603,7 @@
         <v>287</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>5731</v>
+        <v>5730</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -19627,7 +19627,7 @@
         <v>292</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>5732</v>
+        <v>5731</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -19635,7 +19635,7 @@
         <v>293</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>5753</v>
+        <v>5752</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -19643,7 +19643,7 @@
         <v>294</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>5733</v>
+        <v>5732</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -19691,7 +19691,7 @@
         <v>305</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>5962</v>
+        <v>5961</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -19739,7 +19739,7 @@
         <v>316</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>5734</v>
+        <v>5733</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -19867,7 +19867,7 @@
         <v>346</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>5735</v>
+        <v>5734</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -19899,7 +19899,7 @@
         <v>353</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>5736</v>
+        <v>5735</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -20403,7 +20403,7 @@
         <v>474</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>5754</v>
+        <v>5753</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
@@ -20475,7 +20475,7 @@
         <v>491</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>5755</v>
+        <v>5754</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
@@ -20619,7 +20619,7 @@
         <v>524</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>5756</v>
+        <v>5755</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
@@ -21155,7 +21155,7 @@
         <v>653</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>5757</v>
+        <v>5756</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
@@ -21283,7 +21283,7 @@
         <v>683</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>5737</v>
+        <v>5736</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
@@ -21427,7 +21427,7 @@
         <v>718</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>5758</v>
+        <v>5757</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
@@ -21459,7 +21459,7 @@
         <v>725</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>5759</v>
+        <v>5758</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
@@ -21483,7 +21483,7 @@
         <v>730</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>5760</v>
+        <v>5759</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
@@ -21547,7 +21547,7 @@
         <v>745</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>5761</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
@@ -21555,7 +21555,7 @@
         <v>746</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>5857</v>
+        <v>5856</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
@@ -21595,7 +21595,7 @@
         <v>755</v>
       </c>
       <c r="B404" s="5" t="s">
-        <v>5858</v>
+        <v>5857</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
@@ -21603,7 +21603,7 @@
         <v>756</v>
       </c>
       <c r="B405" s="5" t="s">
-        <v>5762</v>
+        <v>5761</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
@@ -21611,7 +21611,7 @@
         <v>757</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>5763</v>
+        <v>5762</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
@@ -21627,7 +21627,7 @@
         <v>760</v>
       </c>
       <c r="B408" s="5" t="s">
-        <v>5764</v>
+        <v>5763</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
@@ -21667,7 +21667,7 @@
         <v>769</v>
       </c>
       <c r="B413" s="5" t="s">
-        <v>5738</v>
+        <v>5737</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
@@ -21675,7 +21675,7 @@
         <v>770</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>5739</v>
+        <v>5738</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
@@ -21747,7 +21747,7 @@
         <v>787</v>
       </c>
       <c r="B423" s="5" t="s">
-        <v>5740</v>
+        <v>5739</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
@@ -21787,7 +21787,7 @@
         <v>796</v>
       </c>
       <c r="B428" s="5" t="s">
-        <v>5741</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
@@ -22131,7 +22131,7 @@
         <v>862</v>
       </c>
       <c r="B471" s="5" t="s">
-        <v>5765</v>
+        <v>5764</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.25">
@@ -22203,7 +22203,7 @@
         <v>879</v>
       </c>
       <c r="B480" s="5" t="s">
-        <v>5742</v>
+        <v>5741</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.25">
@@ -22624,7 +22624,7 @@
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>5889</v>
+        <v>5888</v>
       </c>
       <c r="B533" s="5" t="s">
         <v>978</v>
@@ -22640,15 +22640,15 @@
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>5890</v>
+        <v>5889</v>
       </c>
       <c r="B535" s="5" t="s">
-        <v>5766</v>
+        <v>5765</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
-        <v>5891</v>
+        <v>5890</v>
       </c>
       <c r="B536" s="5" t="s">
         <v>981</v>
@@ -23299,7 +23299,7 @@
         <v>1137</v>
       </c>
       <c r="B617" s="5" t="s">
-        <v>5767</v>
+        <v>5766</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.25">
@@ -23355,7 +23355,7 @@
         <v>1150</v>
       </c>
       <c r="B624" s="5" t="s">
-        <v>5768</v>
+        <v>5767</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.25">
@@ -23363,7 +23363,7 @@
         <v>1151</v>
       </c>
       <c r="B625" s="5" t="s">
-        <v>5769</v>
+        <v>5768</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.25">
@@ -23571,7 +23571,7 @@
         <v>1202</v>
       </c>
       <c r="B651" s="5" t="s">
-        <v>5770</v>
+        <v>5769</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.25">
@@ -23851,7 +23851,7 @@
         <v>1269</v>
       </c>
       <c r="B686" s="5" t="s">
-        <v>5743</v>
+        <v>5742</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.25">
@@ -23915,7 +23915,7 @@
         <v>1284</v>
       </c>
       <c r="B694" s="5" t="s">
-        <v>5744</v>
+        <v>5743</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.25">
@@ -23971,7 +23971,7 @@
         <v>1297</v>
       </c>
       <c r="B701" s="5" t="s">
-        <v>5859</v>
+        <v>5858</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.25">
@@ -23979,7 +23979,7 @@
         <v>1298</v>
       </c>
       <c r="B702" s="5" t="s">
-        <v>5860</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.25">
@@ -23995,7 +23995,7 @@
         <v>1301</v>
       </c>
       <c r="B704" s="5" t="s">
-        <v>5745</v>
+        <v>5744</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.25">
@@ -24163,7 +24163,7 @@
         <v>1342</v>
       </c>
       <c r="B725" s="5" t="s">
-        <v>5861</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.25">
@@ -24227,7 +24227,7 @@
         <v>1357</v>
       </c>
       <c r="B733" s="5" t="s">
-        <v>5771</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.25">
@@ -24283,7 +24283,7 @@
         <v>1370</v>
       </c>
       <c r="B740" s="5" t="s">
-        <v>5772</v>
+        <v>5771</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.25">
@@ -24355,12 +24355,12 @@
         <v>1387</v>
       </c>
       <c r="B749" s="5" t="s">
-        <v>5773</v>
+        <v>5772</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A750" s="7" t="s">
-        <v>5880</v>
+        <v>5879</v>
       </c>
       <c r="B750" s="5" t="s">
         <v>1388</v>
@@ -24411,7 +24411,7 @@
         <v>1397</v>
       </c>
       <c r="B756" s="5" t="s">
-        <v>5774</v>
+        <v>5773</v>
       </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.25">
@@ -24443,7 +24443,7 @@
         <v>1404</v>
       </c>
       <c r="B760" s="5" t="s">
-        <v>5775</v>
+        <v>5774</v>
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.25">
@@ -24451,7 +24451,7 @@
         <v>1405</v>
       </c>
       <c r="B761" s="5" t="s">
-        <v>5776</v>
+        <v>5775</v>
       </c>
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.25">
@@ -24467,12 +24467,12 @@
         <v>1408</v>
       </c>
       <c r="B763" s="5" t="s">
-        <v>5777</v>
+        <v>5776</v>
       </c>
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A764" s="7" t="s">
-        <v>5881</v>
+        <v>5880</v>
       </c>
       <c r="B764" s="5" t="s">
         <v>1409</v>
@@ -24499,7 +24499,7 @@
         <v>347</v>
       </c>
       <c r="B767" s="5" t="s">
-        <v>5778</v>
+        <v>5777</v>
       </c>
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.25">
@@ -24579,7 +24579,7 @@
         <v>1432</v>
       </c>
       <c r="B777" s="5" t="s">
-        <v>5779</v>
+        <v>5778</v>
       </c>
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.25">
@@ -24651,7 +24651,7 @@
         <v>1449</v>
       </c>
       <c r="B786" s="5" t="s">
-        <v>5746</v>
+        <v>5745</v>
       </c>
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.25">
@@ -24899,7 +24899,7 @@
         <v>1510</v>
       </c>
       <c r="B817" s="5" t="s">
-        <v>5780</v>
+        <v>5779</v>
       </c>
     </row>
     <row r="818" spans="1:2" x14ac:dyDescent="0.25">
@@ -24931,7 +24931,7 @@
         <v>1517</v>
       </c>
       <c r="B821" s="5" t="s">
-        <v>5781</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="822" spans="1:2" x14ac:dyDescent="0.25">
@@ -24979,7 +24979,7 @@
         <v>1528</v>
       </c>
       <c r="B827" s="5" t="s">
-        <v>5862</v>
+        <v>5861</v>
       </c>
     </row>
     <row r="828" spans="1:2" x14ac:dyDescent="0.25">
@@ -24995,7 +24995,7 @@
         <v>1284</v>
       </c>
       <c r="B829" s="5" t="s">
-        <v>5863</v>
+        <v>5862</v>
       </c>
     </row>
     <row r="830" spans="1:2" x14ac:dyDescent="0.25">
@@ -25003,7 +25003,7 @@
         <v>1531</v>
       </c>
       <c r="B830" s="5" t="s">
-        <v>5864</v>
+        <v>5863</v>
       </c>
     </row>
     <row r="831" spans="1:2" x14ac:dyDescent="0.25">
@@ -25163,7 +25163,7 @@
         <v>1570</v>
       </c>
       <c r="B850" s="5" t="s">
-        <v>5865</v>
+        <v>5864</v>
       </c>
     </row>
     <row r="851" spans="1:2" x14ac:dyDescent="0.25">
@@ -25203,7 +25203,7 @@
         <v>1578</v>
       </c>
       <c r="B855" s="5" t="s">
-        <v>5782</v>
+        <v>5781</v>
       </c>
     </row>
     <row r="856" spans="1:2" x14ac:dyDescent="0.25">
@@ -25227,7 +25227,7 @@
         <v>1583</v>
       </c>
       <c r="B858" s="5" t="s">
-        <v>5783</v>
+        <v>5782</v>
       </c>
     </row>
     <row r="859" spans="1:2" x14ac:dyDescent="0.25">
@@ -25299,7 +25299,7 @@
         <v>1600</v>
       </c>
       <c r="B867" s="5" t="s">
-        <v>5747</v>
+        <v>5746</v>
       </c>
     </row>
     <row r="868" spans="1:2" x14ac:dyDescent="0.25">
@@ -25411,7 +25411,7 @@
         <v>1626</v>
       </c>
       <c r="B881" s="5" t="s">
-        <v>5784</v>
+        <v>5783</v>
       </c>
     </row>
     <row r="882" spans="1:2" x14ac:dyDescent="0.25">
@@ -25443,7 +25443,7 @@
         <v>1633</v>
       </c>
       <c r="B885" s="5" t="s">
-        <v>5785</v>
+        <v>5784</v>
       </c>
     </row>
     <row r="886" spans="1:2" x14ac:dyDescent="0.25">
@@ -25467,7 +25467,7 @@
         <v>1636</v>
       </c>
       <c r="B888" s="5" t="s">
-        <v>5786</v>
+        <v>5785</v>
       </c>
     </row>
     <row r="889" spans="1:2" x14ac:dyDescent="0.25">
@@ -25611,7 +25611,7 @@
         <v>1669</v>
       </c>
       <c r="B906" s="5" t="s">
-        <v>5787</v>
+        <v>5786</v>
       </c>
     </row>
     <row r="907" spans="1:2" x14ac:dyDescent="0.25">
@@ -25675,7 +25675,7 @@
         <v>1684</v>
       </c>
       <c r="B914" s="5" t="s">
-        <v>5788</v>
+        <v>5787</v>
       </c>
     </row>
     <row r="915" spans="1:2" x14ac:dyDescent="0.25">
@@ -25907,7 +25907,7 @@
         <v>1740</v>
       </c>
       <c r="B943" s="5" t="s">
-        <v>5789</v>
+        <v>5788</v>
       </c>
     </row>
     <row r="944" spans="1:2" x14ac:dyDescent="0.25">
@@ -25931,7 +25931,7 @@
         <v>1745</v>
       </c>
       <c r="B946" s="5" t="s">
-        <v>5790</v>
+        <v>5789</v>
       </c>
     </row>
     <row r="947" spans="1:2" x14ac:dyDescent="0.25">
@@ -26651,7 +26651,7 @@
         <v>1922</v>
       </c>
       <c r="B1036" s="5" t="s">
-        <v>5791</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="1037" spans="1:2" x14ac:dyDescent="0.25">
@@ -27040,7 +27040,7 @@
     </row>
     <row r="1085" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1085" s="2" t="s">
-        <v>5892</v>
+        <v>5891</v>
       </c>
       <c r="B1085" s="5" t="s">
         <v>2009</v>
@@ -27056,7 +27056,7 @@
     </row>
     <row r="1087" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1087" s="2" t="s">
-        <v>5893</v>
+        <v>5892</v>
       </c>
       <c r="B1087" s="5" t="s">
         <v>2012</v>
@@ -27835,7 +27835,7 @@
         <v>2202</v>
       </c>
       <c r="B1184" s="5" t="s">
-        <v>5792</v>
+        <v>5791</v>
       </c>
     </row>
     <row r="1185" spans="1:2" x14ac:dyDescent="0.25">
@@ -27899,7 +27899,7 @@
         <v>2217</v>
       </c>
       <c r="B1192" s="5" t="s">
-        <v>5793</v>
+        <v>5792</v>
       </c>
     </row>
     <row r="1193" spans="1:2" x14ac:dyDescent="0.25">
@@ -27936,7 +27936,7 @@
     </row>
     <row r="1197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1197" s="7" t="s">
-        <v>5882</v>
+        <v>5881</v>
       </c>
       <c r="B1197" s="5" t="s">
         <v>2226</v>
@@ -28059,7 +28059,7 @@
         <v>2255</v>
       </c>
       <c r="B1212" s="8" t="s">
-        <v>5794</v>
+        <v>5793</v>
       </c>
     </row>
     <row r="1213" spans="1:2" x14ac:dyDescent="0.25">
@@ -28155,7 +28155,7 @@
         <v>2278</v>
       </c>
       <c r="B1224" s="5" t="s">
-        <v>5795</v>
+        <v>5794</v>
       </c>
     </row>
     <row r="1225" spans="1:2" x14ac:dyDescent="0.25">
@@ -28331,7 +28331,7 @@
         <v>2321</v>
       </c>
       <c r="B1246" s="5" t="s">
-        <v>5796</v>
+        <v>5795</v>
       </c>
     </row>
     <row r="1247" spans="1:2" x14ac:dyDescent="0.25">
@@ -28544,7 +28544,7 @@
     </row>
     <row r="1273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1273" s="7" t="s">
-        <v>5883</v>
+        <v>5882</v>
       </c>
       <c r="B1273" s="5" t="s">
         <v>2374</v>
@@ -28555,7 +28555,7 @@
         <v>2375</v>
       </c>
       <c r="B1274" s="5" t="s">
-        <v>5797</v>
+        <v>5796</v>
       </c>
     </row>
     <row r="1275" spans="1:2" x14ac:dyDescent="0.25">
@@ -28619,7 +28619,7 @@
         <v>2390</v>
       </c>
       <c r="B1282" s="5" t="s">
-        <v>5866</v>
+        <v>5865</v>
       </c>
     </row>
     <row r="1283" spans="1:2" x14ac:dyDescent="0.25">
@@ -28995,7 +28995,7 @@
         <v>2483</v>
       </c>
       <c r="B1329" s="5" t="s">
-        <v>5798</v>
+        <v>5797</v>
       </c>
     </row>
     <row r="1330" spans="1:2" x14ac:dyDescent="0.25">
@@ -29451,7 +29451,7 @@
         <v>2592</v>
       </c>
       <c r="B1386" s="5" t="s">
-        <v>5799</v>
+        <v>5798</v>
       </c>
     </row>
     <row r="1387" spans="1:2" x14ac:dyDescent="0.25">
@@ -30288,7 +30288,7 @@
     </row>
     <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1491" s="2" t="s">
-        <v>5955</v>
+        <v>5954</v>
       </c>
       <c r="B1491" s="5" t="s">
         <v>2795</v>
@@ -30331,7 +30331,7 @@
         <v>2804</v>
       </c>
       <c r="B1496" s="5" t="s">
-        <v>5800</v>
+        <v>5799</v>
       </c>
     </row>
     <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
@@ -30379,7 +30379,7 @@
         <v>2813</v>
       </c>
       <c r="B1502" s="5" t="s">
-        <v>5801</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
@@ -30395,7 +30395,7 @@
         <v>2816</v>
       </c>
       <c r="B1504" s="5" t="s">
-        <v>5802</v>
+        <v>5801</v>
       </c>
     </row>
     <row r="1505" spans="1:2" x14ac:dyDescent="0.25">
@@ -30416,7 +30416,7 @@
     </row>
     <row r="1507" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1507" s="1" t="s">
-        <v>5956</v>
+        <v>5955</v>
       </c>
       <c r="B1507" s="5" t="s">
         <v>2821</v>
@@ -30427,7 +30427,7 @@
         <v>2822</v>
       </c>
       <c r="B1508" s="5" t="s">
-        <v>5803</v>
+        <v>5802</v>
       </c>
     </row>
     <row r="1509" spans="1:2" x14ac:dyDescent="0.25">
@@ -30931,7 +30931,7 @@
         <v>2935</v>
       </c>
       <c r="B1571" s="5" t="s">
-        <v>5867</v>
+        <v>5866</v>
       </c>
     </row>
     <row r="1572" spans="1:2" x14ac:dyDescent="0.25">
@@ -30979,7 +30979,7 @@
         <v>2946</v>
       </c>
       <c r="B1577" s="5" t="s">
-        <v>5868</v>
+        <v>5867</v>
       </c>
     </row>
     <row r="1578" spans="1:2" x14ac:dyDescent="0.25">
@@ -31019,7 +31019,7 @@
         <v>2955</v>
       </c>
       <c r="B1582" s="5" t="s">
-        <v>5748</v>
+        <v>5747</v>
       </c>
     </row>
     <row r="1583" spans="1:2" x14ac:dyDescent="0.25">
@@ -31035,7 +31035,7 @@
         <v>2958</v>
       </c>
       <c r="B1584" s="5" t="s">
-        <v>5804</v>
+        <v>5803</v>
       </c>
     </row>
     <row r="1585" spans="1:2" x14ac:dyDescent="0.25">
@@ -31259,7 +31259,7 @@
         <v>3013</v>
       </c>
       <c r="B1612" s="5" t="s">
-        <v>5749</v>
+        <v>5748</v>
       </c>
     </row>
     <row r="1613" spans="1:2" x14ac:dyDescent="0.25">
@@ -31299,7 +31299,7 @@
         <v>3022</v>
       </c>
       <c r="B1617" s="5" t="s">
-        <v>5805</v>
+        <v>5804</v>
       </c>
     </row>
     <row r="1618" spans="1:2" x14ac:dyDescent="0.25">
@@ -31395,7 +31395,7 @@
         <v>3045</v>
       </c>
       <c r="B1629" s="5" t="s">
-        <v>5806</v>
+        <v>5805</v>
       </c>
     </row>
     <row r="1630" spans="1:2" x14ac:dyDescent="0.25">
@@ -31419,7 +31419,7 @@
         <v>3050</v>
       </c>
       <c r="B1632" s="5" t="s">
-        <v>5807</v>
+        <v>5806</v>
       </c>
     </row>
     <row r="1633" spans="1:2" x14ac:dyDescent="0.25">
@@ -31432,7 +31432,7 @@
     </row>
     <row r="1634" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1634" s="9" t="s">
-        <v>5884</v>
+        <v>5883</v>
       </c>
       <c r="B1634" s="5" t="s">
         <v>3053</v>
@@ -31475,7 +31475,7 @@
         <v>3062</v>
       </c>
       <c r="B1639" s="5" t="s">
-        <v>5869</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="1640" spans="1:2" x14ac:dyDescent="0.25">
@@ -31531,7 +31531,7 @@
         <v>3075</v>
       </c>
       <c r="B1646" s="5" t="s">
-        <v>5808</v>
+        <v>5807</v>
       </c>
     </row>
     <row r="1647" spans="1:2" x14ac:dyDescent="0.25">
@@ -31659,7 +31659,7 @@
         <v>3106</v>
       </c>
       <c r="B1662" s="5" t="s">
-        <v>5809</v>
+        <v>5808</v>
       </c>
     </row>
     <row r="1663" spans="1:2" x14ac:dyDescent="0.25">
@@ -31843,7 +31843,7 @@
         <v>3151</v>
       </c>
       <c r="B1685" s="5" t="s">
-        <v>5810</v>
+        <v>5809</v>
       </c>
     </row>
     <row r="1686" spans="1:2" x14ac:dyDescent="0.25">
@@ -31963,7 +31963,7 @@
         <v>3180</v>
       </c>
       <c r="B1700" s="5" t="s">
-        <v>5811</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="1701" spans="1:2" x14ac:dyDescent="0.25">
@@ -32059,7 +32059,7 @@
         <v>3203</v>
       </c>
       <c r="B1712" s="5" t="s">
-        <v>5812</v>
+        <v>5811</v>
       </c>
     </row>
     <row r="1713" spans="1:2" x14ac:dyDescent="0.25">
@@ -32075,7 +32075,7 @@
         <v>3206</v>
       </c>
       <c r="B1714" s="5" t="s">
-        <v>5813</v>
+        <v>5812</v>
       </c>
     </row>
     <row r="1715" spans="1:2" x14ac:dyDescent="0.25">
@@ -32131,7 +32131,7 @@
         <v>3219</v>
       </c>
       <c r="B1721" s="5" t="s">
-        <v>5814</v>
+        <v>5813</v>
       </c>
     </row>
     <row r="1722" spans="1:2" x14ac:dyDescent="0.25">
@@ -32139,7 +32139,7 @@
         <v>3220</v>
       </c>
       <c r="B1722" s="5" t="s">
-        <v>5815</v>
+        <v>5814</v>
       </c>
     </row>
     <row r="1723" spans="1:2" x14ac:dyDescent="0.25">
@@ -32219,7 +32219,7 @@
         <v>3239</v>
       </c>
       <c r="B1732" s="5" t="s">
-        <v>5816</v>
+        <v>5815</v>
       </c>
     </row>
     <row r="1733" spans="1:2" x14ac:dyDescent="0.25">
@@ -32856,7 +32856,7 @@
     </row>
     <row r="1812" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1812" s="2" t="s">
-        <v>5894</v>
+        <v>5893</v>
       </c>
       <c r="B1812" s="5" t="s">
         <v>3372</v>
@@ -32872,7 +32872,7 @@
     </row>
     <row r="1814" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1814" s="2" t="s">
-        <v>5957</v>
+        <v>5956</v>
       </c>
       <c r="B1814" s="5" t="s">
         <v>3375</v>
@@ -32928,7 +32928,7 @@
     </row>
     <row r="1821" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1821" s="2" t="s">
-        <v>5895</v>
+        <v>5894</v>
       </c>
       <c r="B1821" s="5" t="s">
         <v>3388</v>
@@ -32995,7 +32995,7 @@
         <v>3403</v>
       </c>
       <c r="B1829" s="5" t="s">
-        <v>5817</v>
+        <v>5816</v>
       </c>
     </row>
     <row r="1830" spans="1:2" x14ac:dyDescent="0.25">
@@ -33035,7 +33035,7 @@
         <v>3412</v>
       </c>
       <c r="B1834" s="5" t="s">
-        <v>5870</v>
+        <v>5869</v>
       </c>
     </row>
     <row r="1835" spans="1:2" x14ac:dyDescent="0.25">
@@ -33771,7 +33771,7 @@
         <v>3577</v>
       </c>
       <c r="B1926" s="5" t="s">
-        <v>5818</v>
+        <v>5817</v>
       </c>
     </row>
     <row r="1927" spans="1:2" x14ac:dyDescent="0.25">
@@ -33907,7 +33907,7 @@
         <v>3610</v>
       </c>
       <c r="B1943" s="5" t="s">
-        <v>5819</v>
+        <v>5818</v>
       </c>
     </row>
     <row r="1944" spans="1:2" x14ac:dyDescent="0.25">
@@ -33987,7 +33987,7 @@
         <v>3629</v>
       </c>
       <c r="B1953" s="5" t="s">
-        <v>5820</v>
+        <v>5819</v>
       </c>
     </row>
     <row r="1954" spans="1:2" x14ac:dyDescent="0.25">
@@ -34043,7 +34043,7 @@
         <v>3642</v>
       </c>
       <c r="B1960" s="5" t="s">
-        <v>5821</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="1961" spans="1:2" x14ac:dyDescent="0.25">
@@ -34259,7 +34259,7 @@
         <v>3695</v>
       </c>
       <c r="B1987" s="5" t="s">
-        <v>5822</v>
+        <v>5821</v>
       </c>
     </row>
     <row r="1988" spans="1:2" x14ac:dyDescent="0.25">
@@ -34296,10 +34296,10 @@
     </row>
     <row r="1992" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1992" s="7" t="s">
+        <v>5884</v>
+      </c>
+      <c r="B1992" s="5" t="s">
         <v>5885</v>
-      </c>
-      <c r="B1992" s="5" t="s">
-        <v>5886</v>
       </c>
     </row>
     <row r="1993" spans="1:2" x14ac:dyDescent="0.25">
@@ -34392,7 +34392,7 @@
     </row>
     <row r="2004" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2004" s="7" t="s">
-        <v>5887</v>
+        <v>5886</v>
       </c>
       <c r="B2004" s="5" t="s">
         <v>3726</v>
@@ -34563,7 +34563,7 @@
         <v>3767</v>
       </c>
       <c r="B2025" s="5" t="s">
-        <v>5823</v>
+        <v>5822</v>
       </c>
     </row>
     <row r="2026" spans="1:2" x14ac:dyDescent="0.25">
@@ -34643,7 +34643,7 @@
         <v>3784</v>
       </c>
       <c r="B2035" s="5" t="s">
-        <v>5871</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="2036" spans="1:2" x14ac:dyDescent="0.25">
@@ -34675,7 +34675,7 @@
         <v>3791</v>
       </c>
       <c r="B2039" s="5" t="s">
-        <v>5824</v>
+        <v>5823</v>
       </c>
     </row>
     <row r="2040" spans="1:2" x14ac:dyDescent="0.25">
@@ -34755,7 +34755,7 @@
         <v>3810</v>
       </c>
       <c r="B2049" s="5" t="s">
-        <v>5872</v>
+        <v>5871</v>
       </c>
     </row>
     <row r="2050" spans="1:2" x14ac:dyDescent="0.25">
@@ -34795,7 +34795,7 @@
         <v>3819</v>
       </c>
       <c r="B2054" s="5" t="s">
-        <v>5825</v>
+        <v>5824</v>
       </c>
     </row>
     <row r="2055" spans="1:2" x14ac:dyDescent="0.25">
@@ -35043,7 +35043,7 @@
         <v>3880</v>
       </c>
       <c r="B2085" s="5" t="s">
-        <v>5826</v>
+        <v>5825</v>
       </c>
     </row>
     <row r="2086" spans="1:2" x14ac:dyDescent="0.25">
@@ -35227,7 +35227,7 @@
         <v>3925</v>
       </c>
       <c r="B2108" s="5" t="s">
-        <v>5827</v>
+        <v>5826</v>
       </c>
     </row>
     <row r="2109" spans="1:2" x14ac:dyDescent="0.25">
@@ -35424,7 +35424,7 @@
     </row>
     <row r="2133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2133" s="2" t="s">
-        <v>5896</v>
+        <v>5895</v>
       </c>
       <c r="B2133" s="5" t="s">
         <v>3971</v>
@@ -35432,7 +35432,7 @@
     </row>
     <row r="2134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2134" s="2" t="s">
-        <v>5897</v>
+        <v>5896</v>
       </c>
       <c r="B2134" s="5" t="s">
         <v>3972</v>
@@ -35504,7 +35504,7 @@
     </row>
     <row r="2143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2143" s="2" t="s">
-        <v>5898</v>
+        <v>5897</v>
       </c>
       <c r="B2143" s="5" t="s">
         <v>3989</v>
@@ -35520,7 +35520,7 @@
     </row>
     <row r="2145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2145" s="2" t="s">
-        <v>5899</v>
+        <v>5898</v>
       </c>
       <c r="B2145" s="5" t="s">
         <v>3992</v>
@@ -35795,7 +35795,7 @@
         <v>4052</v>
       </c>
       <c r="B2179" s="5" t="s">
-        <v>5828</v>
+        <v>5827</v>
       </c>
     </row>
     <row r="2180" spans="1:2" x14ac:dyDescent="0.25">
@@ -36107,7 +36107,7 @@
         <v>4129</v>
       </c>
       <c r="B2218" s="5" t="s">
-        <v>5829</v>
+        <v>5828</v>
       </c>
     </row>
     <row r="2219" spans="1:2" x14ac:dyDescent="0.25">
@@ -36203,7 +36203,7 @@
         <v>4152</v>
       </c>
       <c r="B2230" s="5" t="s">
-        <v>5830</v>
+        <v>5829</v>
       </c>
     </row>
     <row r="2231" spans="1:2" x14ac:dyDescent="0.25">
@@ -36283,7 +36283,7 @@
         <v>4171</v>
       </c>
       <c r="B2240" s="5" t="s">
-        <v>5831</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="2241" spans="1:2" x14ac:dyDescent="0.25">
@@ -36560,7 +36560,7 @@
     </row>
     <row r="2275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2275" s="2" t="s">
-        <v>5900</v>
+        <v>5899</v>
       </c>
       <c r="B2275" s="5" t="s">
         <v>4236</v>
@@ -36584,7 +36584,7 @@
     </row>
     <row r="2278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2278" s="2" t="s">
-        <v>5901</v>
+        <v>5900</v>
       </c>
       <c r="B2278" s="5" t="s">
         <v>4241</v>
@@ -36592,7 +36592,7 @@
     </row>
     <row r="2279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2279" s="2" t="s">
-        <v>5902</v>
+        <v>5901</v>
       </c>
       <c r="B2279" s="5" t="s">
         <v>4242</v>
@@ -36608,7 +36608,7 @@
     </row>
     <row r="2281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2281" s="2" t="s">
-        <v>5903</v>
+        <v>5902</v>
       </c>
       <c r="B2281" s="5" t="s">
         <v>4245</v>
@@ -36616,7 +36616,7 @@
     </row>
     <row r="2282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2282" s="2" t="s">
-        <v>5904</v>
+        <v>5903</v>
       </c>
       <c r="B2282" s="5" t="s">
         <v>4246</v>
@@ -37139,7 +37139,7 @@
         <v>4371</v>
       </c>
       <c r="B2347" s="5" t="s">
-        <v>5832</v>
+        <v>5831</v>
       </c>
     </row>
     <row r="2348" spans="1:2" x14ac:dyDescent="0.25">
@@ -37243,7 +37243,7 @@
         <v>4396</v>
       </c>
       <c r="B2360" s="5" t="s">
-        <v>5833</v>
+        <v>5832</v>
       </c>
     </row>
     <row r="2361" spans="1:2" x14ac:dyDescent="0.25">
@@ -37259,7 +37259,7 @@
         <v>4399</v>
       </c>
       <c r="B2362" s="5" t="s">
-        <v>5834</v>
+        <v>5833</v>
       </c>
     </row>
     <row r="2363" spans="1:2" x14ac:dyDescent="0.25">
@@ -37515,7 +37515,7 @@
         <v>4462</v>
       </c>
       <c r="B2394" s="5" t="s">
-        <v>5835</v>
+        <v>5834</v>
       </c>
     </row>
     <row r="2395" spans="1:2" x14ac:dyDescent="0.25">
@@ -37643,7 +37643,7 @@
         <v>4493</v>
       </c>
       <c r="B2410" s="5" t="s">
-        <v>5836</v>
+        <v>5835</v>
       </c>
     </row>
     <row r="2411" spans="1:2" x14ac:dyDescent="0.25">
@@ -37651,7 +37651,7 @@
         <v>4494</v>
       </c>
       <c r="B2411" s="5" t="s">
-        <v>5837</v>
+        <v>5836</v>
       </c>
     </row>
     <row r="2412" spans="1:2" x14ac:dyDescent="0.25">
@@ -37739,7 +37739,7 @@
         <v>4515</v>
       </c>
       <c r="B2422" s="5" t="s">
-        <v>5838</v>
+        <v>5837</v>
       </c>
     </row>
     <row r="2423" spans="1:2" x14ac:dyDescent="0.25">
@@ -37856,7 +37856,7 @@
     </row>
     <row r="2437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2437" s="2" t="s">
-        <v>5905</v>
+        <v>5904</v>
       </c>
       <c r="B2437" s="5" t="s">
         <v>4541</v>
@@ -37864,7 +37864,7 @@
     </row>
     <row r="2438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2438" s="2" t="s">
-        <v>5906</v>
+        <v>5905</v>
       </c>
       <c r="B2438" s="5" t="s">
         <v>4542</v>
@@ -38051,7 +38051,7 @@
         <v>4584</v>
       </c>
       <c r="B2461" s="5" t="s">
-        <v>5839</v>
+        <v>5838</v>
       </c>
     </row>
     <row r="2462" spans="1:2" x14ac:dyDescent="0.25">
@@ -38155,7 +38155,7 @@
         <v>4609</v>
       </c>
       <c r="B2474" s="5" t="s">
-        <v>5873</v>
+        <v>5872</v>
       </c>
     </row>
     <row r="2475" spans="1:2" x14ac:dyDescent="0.25">
@@ -38283,7 +38283,7 @@
         <v>4640</v>
       </c>
       <c r="B2490" s="5" t="s">
-        <v>5840</v>
+        <v>5839</v>
       </c>
     </row>
     <row r="2491" spans="1:2" x14ac:dyDescent="0.25">
@@ -38347,7 +38347,7 @@
         <v>4655</v>
       </c>
       <c r="B2498" s="5" t="s">
-        <v>5841</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="2499" spans="1:2" x14ac:dyDescent="0.25">
@@ -38379,7 +38379,7 @@
         <v>4662</v>
       </c>
       <c r="B2502" s="5" t="s">
-        <v>5874</v>
+        <v>5873</v>
       </c>
     </row>
     <row r="2503" spans="1:2" x14ac:dyDescent="0.25">
@@ -38443,7 +38443,7 @@
         <v>4677</v>
       </c>
       <c r="B2510" s="5" t="s">
-        <v>5842</v>
+        <v>5841</v>
       </c>
     </row>
     <row r="2511" spans="1:2" x14ac:dyDescent="0.25">
@@ -38587,7 +38587,7 @@
         <v>4710</v>
       </c>
       <c r="B2528" s="5" t="s">
-        <v>5843</v>
+        <v>5842</v>
       </c>
     </row>
     <row r="2529" spans="1:2" x14ac:dyDescent="0.25">
@@ -38699,7 +38699,7 @@
         <v>4737</v>
       </c>
       <c r="B2542" s="5" t="s">
-        <v>5844</v>
+        <v>5843</v>
       </c>
     </row>
     <row r="2543" spans="1:2" x14ac:dyDescent="0.25">
@@ -38771,7 +38771,7 @@
         <v>4753</v>
       </c>
       <c r="B2551" s="5" t="s">
-        <v>5875</v>
+        <v>5874</v>
       </c>
     </row>
     <row r="2552" spans="1:2" x14ac:dyDescent="0.25">
@@ -38915,7 +38915,7 @@
         <v>4787</v>
       </c>
       <c r="B2569" s="5" t="s">
-        <v>5876</v>
+        <v>5875</v>
       </c>
     </row>
     <row r="2570" spans="1:2" x14ac:dyDescent="0.25">
@@ -39075,7 +39075,7 @@
         <v>4823</v>
       </c>
       <c r="B2589" s="5" t="s">
-        <v>5877</v>
+        <v>5876</v>
       </c>
     </row>
     <row r="2590" spans="1:2" x14ac:dyDescent="0.25">
@@ -39235,7 +39235,7 @@
         <v>4862</v>
       </c>
       <c r="B2609" s="5" t="s">
-        <v>5845</v>
+        <v>5844</v>
       </c>
     </row>
     <row r="2610" spans="1:2" x14ac:dyDescent="0.25">
@@ -39331,7 +39331,7 @@
         <v>4885</v>
       </c>
       <c r="B2621" s="5" t="s">
-        <v>5846</v>
+        <v>5845</v>
       </c>
     </row>
     <row r="2622" spans="1:2" x14ac:dyDescent="0.25">
@@ -39443,7 +39443,7 @@
         <v>4912</v>
       </c>
       <c r="B2635" s="5" t="s">
-        <v>5847</v>
+        <v>5846</v>
       </c>
     </row>
     <row r="2636" spans="1:2" x14ac:dyDescent="0.25">
@@ -39624,7 +39624,7 @@
     </row>
     <row r="2658" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2658" s="2" t="s">
-        <v>5907</v>
+        <v>5906</v>
       </c>
       <c r="B2658" s="5" t="s">
         <v>4953</v>
@@ -39632,7 +39632,7 @@
     </row>
     <row r="2659" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2659" s="2" t="s">
-        <v>5908</v>
+        <v>5907</v>
       </c>
       <c r="B2659" s="5" t="s">
         <v>4954</v>
@@ -39747,7 +39747,7 @@
         <v>4981</v>
       </c>
       <c r="B2673" s="5" t="s">
-        <v>5848</v>
+        <v>5847</v>
       </c>
     </row>
     <row r="2674" spans="1:2" x14ac:dyDescent="0.25">
@@ -39824,7 +39824,7 @@
     </row>
     <row r="2683" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2683" s="2" t="s">
-        <v>5909</v>
+        <v>5908</v>
       </c>
       <c r="B2683" s="5" t="s">
         <v>5000</v>
@@ -39832,7 +39832,7 @@
     </row>
     <row r="2684" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2684" s="2" t="s">
-        <v>5910</v>
+        <v>5909</v>
       </c>
       <c r="B2684" s="5" t="s">
         <v>5001</v>
@@ -39840,7 +39840,7 @@
     </row>
     <row r="2685" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2685" s="2" t="s">
-        <v>5911</v>
+        <v>5910</v>
       </c>
       <c r="B2685" s="5" t="s">
         <v>5002</v>
@@ -39864,7 +39864,7 @@
     </row>
     <row r="2688" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2688" s="2" t="s">
-        <v>5912</v>
+        <v>5911</v>
       </c>
       <c r="B2688" s="5" t="s">
         <v>5007</v>
@@ -39872,7 +39872,7 @@
     </row>
     <row r="2689" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2689" s="2" t="s">
-        <v>5913</v>
+        <v>5912</v>
       </c>
       <c r="B2689" s="5" t="s">
         <v>5008</v>
@@ -39880,7 +39880,7 @@
     </row>
     <row r="2690" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2690" s="2" t="s">
-        <v>5914</v>
+        <v>5913</v>
       </c>
       <c r="B2690" s="5" t="s">
         <v>5009</v>
@@ -39888,7 +39888,7 @@
     </row>
     <row r="2691" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2691" s="2" t="s">
-        <v>5915</v>
+        <v>5914</v>
       </c>
       <c r="B2691" s="5" t="s">
         <v>5010</v>
@@ -39896,7 +39896,7 @@
     </row>
     <row r="2692" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2692" s="2" t="s">
-        <v>5916</v>
+        <v>5915</v>
       </c>
       <c r="B2692" s="5" t="s">
         <v>5011</v>
@@ -39904,7 +39904,7 @@
     </row>
     <row r="2693" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2693" s="2" t="s">
-        <v>5917</v>
+        <v>5916</v>
       </c>
       <c r="B2693" s="5" t="s">
         <v>5012</v>
@@ -39912,7 +39912,7 @@
     </row>
     <row r="2694" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2694" s="2" t="s">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="B2694" s="5" t="s">
         <v>5013</v>
@@ -39920,7 +39920,7 @@
     </row>
     <row r="2695" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2695" s="2" t="s">
-        <v>5919</v>
+        <v>5918</v>
       </c>
       <c r="B2695" s="5" t="s">
         <v>5014</v>
@@ -39936,7 +39936,7 @@
     </row>
     <row r="2697" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2697" s="2" t="s">
-        <v>5920</v>
+        <v>5919</v>
       </c>
       <c r="B2697" s="5" t="s">
         <v>5017</v>
@@ -39944,7 +39944,7 @@
     </row>
     <row r="2698" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2698" s="2" t="s">
-        <v>5921</v>
+        <v>5920</v>
       </c>
       <c r="B2698" s="5" t="s">
         <v>5018</v>
@@ -39952,7 +39952,7 @@
     </row>
     <row r="2699" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2699" s="2" t="s">
-        <v>5922</v>
+        <v>5921</v>
       </c>
       <c r="B2699" s="5" t="s">
         <v>5019</v>
@@ -39960,7 +39960,7 @@
     </row>
     <row r="2700" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2700" s="2" t="s">
-        <v>5923</v>
+        <v>5922</v>
       </c>
       <c r="B2700" s="5" t="s">
         <v>5020</v>
@@ -39968,7 +39968,7 @@
     </row>
     <row r="2701" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2701" s="2" t="s">
-        <v>5924</v>
+        <v>5923</v>
       </c>
       <c r="B2701" s="5" t="s">
         <v>5021</v>
@@ -39976,7 +39976,7 @@
     </row>
     <row r="2702" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2702" s="2" t="s">
-        <v>5925</v>
+        <v>5924</v>
       </c>
       <c r="B2702" s="5" t="s">
         <v>5022</v>
@@ -39984,7 +39984,7 @@
     </row>
     <row r="2703" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2703" s="2" t="s">
-        <v>5926</v>
+        <v>5925</v>
       </c>
       <c r="B2703" s="5" t="s">
         <v>5023</v>
@@ -39992,7 +39992,7 @@
     </row>
     <row r="2704" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2704" s="2" t="s">
-        <v>5927</v>
+        <v>5926</v>
       </c>
       <c r="B2704" s="5" t="s">
         <v>5024</v>
@@ -40000,7 +40000,7 @@
     </row>
     <row r="2705" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2705" s="2" t="s">
-        <v>5928</v>
+        <v>5927</v>
       </c>
       <c r="B2705" s="5" t="s">
         <v>5025</v>
@@ -40032,7 +40032,7 @@
     </row>
     <row r="2709" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2709" s="2" t="s">
-        <v>5929</v>
+        <v>5928</v>
       </c>
       <c r="B2709" s="5" t="s">
         <v>5032</v>
@@ -40040,7 +40040,7 @@
     </row>
     <row r="2710" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2710" s="2" t="s">
-        <v>5958</v>
+        <v>5957</v>
       </c>
       <c r="B2710" s="5" t="s">
         <v>5033</v>
@@ -40048,7 +40048,7 @@
     </row>
     <row r="2711" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2711" s="2" t="s">
-        <v>5930</v>
+        <v>5929</v>
       </c>
       <c r="B2711" s="5" t="s">
         <v>5034</v>
@@ -40056,7 +40056,7 @@
     </row>
     <row r="2712" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2712" s="2" t="s">
-        <v>5931</v>
+        <v>5930</v>
       </c>
       <c r="B2712" s="5" t="s">
         <v>5035</v>
@@ -40139,7 +40139,7 @@
         <v>5053</v>
       </c>
       <c r="B2722" s="5" t="s">
-        <v>5849</v>
+        <v>5848</v>
       </c>
     </row>
     <row r="2723" spans="1:2" x14ac:dyDescent="0.25">
@@ -40323,7 +40323,7 @@
         <v>5098</v>
       </c>
       <c r="B2745" s="5" t="s">
-        <v>5850</v>
+        <v>5849</v>
       </c>
     </row>
     <row r="2746" spans="1:2" x14ac:dyDescent="0.25">
@@ -40707,7 +40707,7 @@
         <v>5193</v>
       </c>
       <c r="B2793" s="5" t="s">
-        <v>5851</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="2794" spans="1:2" x14ac:dyDescent="0.25">
@@ -40939,7 +40939,7 @@
         <v>5250</v>
       </c>
       <c r="B2822" s="5" t="s">
-        <v>5852</v>
+        <v>5851</v>
       </c>
     </row>
     <row r="2823" spans="1:2" x14ac:dyDescent="0.25">
@@ -42032,7 +42032,7 @@
     </row>
     <row r="2959" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2959" s="2" t="s">
-        <v>5932</v>
+        <v>5931</v>
       </c>
       <c r="B2959" s="5" t="s">
         <v>5518</v>
@@ -42040,7 +42040,7 @@
     </row>
     <row r="2960" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2960" s="2" t="s">
-        <v>5933</v>
+        <v>5932</v>
       </c>
       <c r="B2960" s="5" t="s">
         <v>5519</v>
@@ -42048,7 +42048,7 @@
     </row>
     <row r="2961" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2961" s="2" t="s">
-        <v>5934</v>
+        <v>5933</v>
       </c>
       <c r="B2961" s="5" t="s">
         <v>5520</v>
@@ -42056,7 +42056,7 @@
     </row>
     <row r="2962" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2962" s="2" t="s">
-        <v>5935</v>
+        <v>5934</v>
       </c>
       <c r="B2962" s="5" t="s">
         <v>5521</v>
@@ -42064,7 +42064,7 @@
     </row>
     <row r="2963" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2963" s="2" t="s">
-        <v>5936</v>
+        <v>5935</v>
       </c>
       <c r="B2963" s="5" t="s">
         <v>5522</v>
@@ -42072,7 +42072,7 @@
     </row>
     <row r="2964" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2964" s="2" t="s">
-        <v>5937</v>
+        <v>5936</v>
       </c>
       <c r="B2964" s="5" t="s">
         <v>5523</v>
@@ -42080,7 +42080,7 @@
     </row>
     <row r="2965" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2965" s="2" t="s">
-        <v>5938</v>
+        <v>5937</v>
       </c>
       <c r="B2965" s="5" t="s">
         <v>5524</v>
@@ -42088,15 +42088,15 @@
     </row>
     <row r="2966" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2966" s="2" t="s">
-        <v>5939</v>
+        <v>5938</v>
       </c>
       <c r="B2966" s="5" t="s">
-        <v>5878</v>
+        <v>5877</v>
       </c>
     </row>
     <row r="2967" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2967" s="2" t="s">
-        <v>5940</v>
+        <v>5939</v>
       </c>
       <c r="B2967" s="5" t="s">
         <v>5525</v>
@@ -42104,7 +42104,7 @@
     </row>
     <row r="2968" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2968" s="2" t="s">
-        <v>5941</v>
+        <v>5940</v>
       </c>
       <c r="B2968" s="5" t="s">
         <v>5526</v>
@@ -42112,7 +42112,7 @@
     </row>
     <row r="2969" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2969" s="2" t="s">
-        <v>5942</v>
+        <v>5941</v>
       </c>
       <c r="B2969" s="5" t="s">
         <v>5527</v>
@@ -42120,7 +42120,7 @@
     </row>
     <row r="2970" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2970" s="2" t="s">
-        <v>5943</v>
+        <v>5942</v>
       </c>
       <c r="B2970" s="5" t="s">
         <v>5528</v>
@@ -42128,7 +42128,7 @@
     </row>
     <row r="2971" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2971" s="2" t="s">
-        <v>5944</v>
+        <v>5943</v>
       </c>
       <c r="B2971" s="5" t="s">
         <v>5529</v>
@@ -42136,7 +42136,7 @@
     </row>
     <row r="2972" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2972" s="2" t="s">
-        <v>5945</v>
+        <v>5944</v>
       </c>
       <c r="B2972" s="5" t="s">
         <v>5530</v>
@@ -42144,7 +42144,7 @@
     </row>
     <row r="2973" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2973" s="2" t="s">
-        <v>5946</v>
+        <v>5945</v>
       </c>
       <c r="B2973" s="5" t="s">
         <v>5531</v>
@@ -42152,7 +42152,7 @@
     </row>
     <row r="2974" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2974" s="2" t="s">
-        <v>5947</v>
+        <v>5946</v>
       </c>
       <c r="B2974" s="5" t="s">
         <v>5532</v>
@@ -42160,7 +42160,7 @@
     </row>
     <row r="2975" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2975" s="2" t="s">
-        <v>5948</v>
+        <v>5947</v>
       </c>
       <c r="B2975" s="5" t="s">
         <v>5533</v>
@@ -42168,7 +42168,7 @@
     </row>
     <row r="2976" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2976" s="2" t="s">
-        <v>5949</v>
+        <v>5948</v>
       </c>
       <c r="B2976" s="5" t="s">
         <v>5534</v>
@@ -42176,7 +42176,7 @@
     </row>
     <row r="2977" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2977" s="2" t="s">
-        <v>5950</v>
+        <v>5949</v>
       </c>
       <c r="B2977" s="5" t="s">
         <v>5535</v>
@@ -42184,7 +42184,7 @@
     </row>
     <row r="2978" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2978" s="2" t="s">
-        <v>5951</v>
+        <v>5950</v>
       </c>
       <c r="B2978" s="5" t="s">
         <v>5536</v>
@@ -42192,7 +42192,7 @@
     </row>
     <row r="2979" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2979" s="2" t="s">
-        <v>5952</v>
+        <v>5951</v>
       </c>
       <c r="B2979" s="5" t="s">
         <v>5537</v>
@@ -42200,7 +42200,7 @@
     </row>
     <row r="2980" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2980" s="2" t="s">
-        <v>5953</v>
+        <v>5952</v>
       </c>
       <c r="B2980" s="5" t="s">
         <v>5538</v>
@@ -42208,7 +42208,7 @@
     </row>
     <row r="2981" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2981" s="2" t="s">
-        <v>5954</v>
+        <v>5953</v>
       </c>
       <c r="B2981" s="5" t="s">
         <v>5539</v>
@@ -42443,7 +42443,7 @@
         <v>5593</v>
       </c>
       <c r="B3010" s="5" t="s">
-        <v>5853</v>
+        <v>5852</v>
       </c>
     </row>
     <row r="3011" spans="1:2" x14ac:dyDescent="0.25">
@@ -42779,7 +42779,7 @@
         <v>5676</v>
       </c>
       <c r="B3052" s="5" t="s">
-        <v>5879</v>
+        <v>5878</v>
       </c>
     </row>
     <row r="3053" spans="1:2" x14ac:dyDescent="0.25">
@@ -42803,191 +42803,191 @@
         <v>5681</v>
       </c>
       <c r="B3055" s="5" t="s">
-        <v>5854</v>
+        <v>5853</v>
       </c>
     </row>
     <row r="3056" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3056" s="3" t="s">
+        <v>5968</v>
+      </c>
+      <c r="B3056" s="5" t="s">
         <v>5682</v>
-      </c>
-      <c r="B3056" s="5" t="s">
-        <v>5683</v>
       </c>
     </row>
     <row r="3057" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3057" s="3" t="s">
+        <v>5683</v>
+      </c>
+      <c r="B3057" s="5" t="s">
         <v>5684</v>
-      </c>
-      <c r="B3057" s="5" t="s">
-        <v>5685</v>
       </c>
     </row>
     <row r="3058" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3058" s="3" t="s">
+        <v>5685</v>
+      </c>
+      <c r="B3058" s="5" t="s">
         <v>5686</v>
-      </c>
-      <c r="B3058" s="5" t="s">
-        <v>5687</v>
       </c>
     </row>
     <row r="3059" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3059" s="3" t="s">
+        <v>5687</v>
+      </c>
+      <c r="B3059" s="5" t="s">
         <v>5688</v>
-      </c>
-      <c r="B3059" s="5" t="s">
-        <v>5689</v>
       </c>
     </row>
     <row r="3060" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3060" s="9" t="s">
-        <v>5888</v>
+        <v>5887</v>
       </c>
       <c r="B3060" s="5" t="s">
-        <v>5690</v>
+        <v>5689</v>
       </c>
     </row>
     <row r="3061" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3061" s="3" t="s">
+        <v>5690</v>
+      </c>
+      <c r="B3061" s="5" t="s">
         <v>5691</v>
-      </c>
-      <c r="B3061" s="5" t="s">
-        <v>5692</v>
       </c>
     </row>
     <row r="3062" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3062" s="3" t="s">
+        <v>5692</v>
+      </c>
+      <c r="B3062" s="5" t="s">
         <v>5693</v>
-      </c>
-      <c r="B3062" s="5" t="s">
-        <v>5694</v>
       </c>
     </row>
     <row r="3063" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3063" s="3" t="s">
+        <v>5694</v>
+      </c>
+      <c r="B3063" s="5" t="s">
         <v>5695</v>
-      </c>
-      <c r="B3063" s="5" t="s">
-        <v>5696</v>
       </c>
     </row>
     <row r="3064" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3064" s="3" t="s">
+        <v>5696</v>
+      </c>
+      <c r="B3064" s="5" t="s">
         <v>5697</v>
-      </c>
-      <c r="B3064" s="5" t="s">
-        <v>5698</v>
       </c>
     </row>
     <row r="3065" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3065" s="3" t="s">
+        <v>5698</v>
+      </c>
+      <c r="B3065" s="5" t="s">
         <v>5699</v>
-      </c>
-      <c r="B3065" s="5" t="s">
-        <v>5700</v>
       </c>
     </row>
     <row r="3066" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3066" s="3" t="s">
+        <v>5700</v>
+      </c>
+      <c r="B3066" s="5" t="s">
         <v>5701</v>
-      </c>
-      <c r="B3066" s="5" t="s">
-        <v>5702</v>
       </c>
     </row>
     <row r="3067" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3067" s="3" t="s">
+        <v>5702</v>
+      </c>
+      <c r="B3067" s="5" t="s">
         <v>5703</v>
-      </c>
-      <c r="B3067" s="5" t="s">
-        <v>5704</v>
       </c>
     </row>
     <row r="3068" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3068" s="3" t="s">
-        <v>5705</v>
+        <v>5704</v>
       </c>
       <c r="B3068" s="5" t="s">
-        <v>5855</v>
+        <v>5854</v>
       </c>
     </row>
     <row r="3069" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3069" s="3" t="s">
+        <v>5705</v>
+      </c>
+      <c r="B3069" s="5" t="s">
         <v>5706</v>
-      </c>
-      <c r="B3069" s="5" t="s">
-        <v>5707</v>
       </c>
     </row>
     <row r="3070" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3070" s="3" t="s">
+        <v>5707</v>
+      </c>
+      <c r="B3070" s="5" t="s">
         <v>5708</v>
-      </c>
-      <c r="B3070" s="5" t="s">
-        <v>5709</v>
       </c>
     </row>
     <row r="3071" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3071" s="3" t="s">
+        <v>5709</v>
+      </c>
+      <c r="B3071" s="5" t="s">
         <v>5710</v>
-      </c>
-      <c r="B3071" s="5" t="s">
-        <v>5711</v>
       </c>
     </row>
     <row r="3072" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3072" s="3" t="s">
+        <v>5711</v>
+      </c>
+      <c r="B3072" s="5" t="s">
         <v>5712</v>
-      </c>
-      <c r="B3072" s="5" t="s">
-        <v>5713</v>
       </c>
     </row>
     <row r="3073" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3073" s="3" t="s">
+        <v>5713</v>
+      </c>
+      <c r="B3073" s="5" t="s">
         <v>5714</v>
-      </c>
-      <c r="B3073" s="5" t="s">
-        <v>5715</v>
       </c>
     </row>
     <row r="3074" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3074" s="3" t="s">
+        <v>5715</v>
+      </c>
+      <c r="B3074" s="5" t="s">
         <v>5716</v>
-      </c>
-      <c r="B3074" s="5" t="s">
-        <v>5717</v>
       </c>
     </row>
     <row r="3075" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3075" s="3" t="s">
+        <v>5717</v>
+      </c>
+      <c r="B3075" s="5" t="s">
         <v>5718</v>
-      </c>
-      <c r="B3075" s="5" t="s">
-        <v>5719</v>
       </c>
     </row>
     <row r="3076" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3076" s="3" t="s">
+        <v>5719</v>
+      </c>
+      <c r="B3076" s="5" t="s">
         <v>5720</v>
-      </c>
-      <c r="B3076" s="5" t="s">
-        <v>5721</v>
       </c>
     </row>
     <row r="3077" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3077" s="3" t="s">
+        <v>5721</v>
+      </c>
+      <c r="B3077" s="5" t="s">
         <v>5722</v>
-      </c>
-      <c r="B3077" s="5" t="s">
-        <v>5723</v>
       </c>
     </row>
     <row r="3078" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3078" s="3" t="s">
+        <v>5723</v>
+      </c>
+      <c r="B3078" s="5" t="s">
         <v>5724</v>
-      </c>
-      <c r="B3078" s="5" t="s">
-        <v>5725</v>
       </c>
     </row>
   </sheetData>

--- a/englisch.xlsx
+++ b/englisch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nutzer\Desktop\Vokabellernspiel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{662A5842-84D9-479A-9C8F-A8B05876858E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EF111A2-80EB-4CDF-9F8B-39CA63F095EB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17970" windowHeight="5115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="8655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -17070,6 +17070,9 @@
     <t>Du siehst europäisch aus.</t>
   </si>
   <si>
+    <t>Das ist sehr deutsch.</t>
+  </si>
+  <si>
     <t>That is very german.</t>
   </si>
   <si>
@@ -17926,9 +17929,6 @@
   </si>
   <si>
     <t>Ihr (formell Du)</t>
-  </si>
-  <si>
-    <t>Das ist sehr deutsch .</t>
   </si>
 </sst>
 </file>
@@ -19067,7 +19067,7 @@
         <v>174</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>5750</v>
+        <v>5751</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -19080,7 +19080,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>5962</v>
+        <v>5963</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>177</v>
@@ -19112,7 +19112,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>5963</v>
+        <v>5964</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>184</v>
@@ -19120,7 +19120,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>5964</v>
+        <v>5965</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>185</v>
@@ -19152,7 +19152,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>5965</v>
+        <v>5966</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>191</v>
@@ -19163,7 +19163,7 @@
         <v>32</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>5960</v>
+        <v>5961</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -19184,7 +19184,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>5966</v>
+        <v>5967</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>195</v>
@@ -19192,7 +19192,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>5967</v>
+        <v>5968</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>196</v>
@@ -19235,7 +19235,7 @@
         <v>205</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>5725</v>
+        <v>5726</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -19251,7 +19251,7 @@
         <v>208</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>5855</v>
+        <v>5856</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -19283,7 +19283,7 @@
         <v>215</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>5726</v>
+        <v>5727</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -19291,7 +19291,7 @@
         <v>216</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>5727</v>
+        <v>5728</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -19419,7 +19419,7 @@
         <v>247</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>5959</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -19443,7 +19443,7 @@
         <v>252</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>5728</v>
+        <v>5729</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -19507,12 +19507,12 @@
         <v>267</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>5729</v>
+        <v>5730</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>5749</v>
+        <v>5750</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>268</v>
@@ -19523,7 +19523,7 @@
         <v>269</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>5751</v>
+        <v>5752</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -19587,7 +19587,7 @@
         <v>284</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>5958</v>
+        <v>5959</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -19603,7 +19603,7 @@
         <v>287</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>5730</v>
+        <v>5731</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -19627,7 +19627,7 @@
         <v>292</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>5731</v>
+        <v>5732</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -19635,7 +19635,7 @@
         <v>293</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>5752</v>
+        <v>5753</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -19643,7 +19643,7 @@
         <v>294</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>5732</v>
+        <v>5733</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -19691,7 +19691,7 @@
         <v>305</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>5961</v>
+        <v>5962</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -19739,7 +19739,7 @@
         <v>316</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>5733</v>
+        <v>5734</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -19867,7 +19867,7 @@
         <v>346</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>5734</v>
+        <v>5735</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -19899,7 +19899,7 @@
         <v>353</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>5735</v>
+        <v>5736</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -20403,7 +20403,7 @@
         <v>474</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>5753</v>
+        <v>5754</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
@@ -20475,7 +20475,7 @@
         <v>491</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>5754</v>
+        <v>5755</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
@@ -20619,7 +20619,7 @@
         <v>524</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>5755</v>
+        <v>5756</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
@@ -21155,7 +21155,7 @@
         <v>653</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>5756</v>
+        <v>5757</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
@@ -21283,7 +21283,7 @@
         <v>683</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>5736</v>
+        <v>5737</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
@@ -21427,7 +21427,7 @@
         <v>718</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>5757</v>
+        <v>5758</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
@@ -21459,7 +21459,7 @@
         <v>725</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>5758</v>
+        <v>5759</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
@@ -21483,7 +21483,7 @@
         <v>730</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
@@ -21547,7 +21547,7 @@
         <v>745</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>5760</v>
+        <v>5761</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
@@ -21555,7 +21555,7 @@
         <v>746</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>5856</v>
+        <v>5857</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
@@ -21595,7 +21595,7 @@
         <v>755</v>
       </c>
       <c r="B404" s="5" t="s">
-        <v>5857</v>
+        <v>5858</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
@@ -21603,7 +21603,7 @@
         <v>756</v>
       </c>
       <c r="B405" s="5" t="s">
-        <v>5761</v>
+        <v>5762</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
@@ -21611,7 +21611,7 @@
         <v>757</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>5762</v>
+        <v>5763</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
@@ -21627,7 +21627,7 @@
         <v>760</v>
       </c>
       <c r="B408" s="5" t="s">
-        <v>5763</v>
+        <v>5764</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
@@ -21667,7 +21667,7 @@
         <v>769</v>
       </c>
       <c r="B413" s="5" t="s">
-        <v>5737</v>
+        <v>5738</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
@@ -21675,7 +21675,7 @@
         <v>770</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>5738</v>
+        <v>5739</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
@@ -21747,7 +21747,7 @@
         <v>787</v>
       </c>
       <c r="B423" s="5" t="s">
-        <v>5739</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
@@ -21787,7 +21787,7 @@
         <v>796</v>
       </c>
       <c r="B428" s="5" t="s">
-        <v>5740</v>
+        <v>5741</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
@@ -22131,7 +22131,7 @@
         <v>862</v>
       </c>
       <c r="B471" s="5" t="s">
-        <v>5764</v>
+        <v>5765</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.25">
@@ -22203,7 +22203,7 @@
         <v>879</v>
       </c>
       <c r="B480" s="5" t="s">
-        <v>5741</v>
+        <v>5742</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.25">
@@ -22624,7 +22624,7 @@
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>5888</v>
+        <v>5889</v>
       </c>
       <c r="B533" s="5" t="s">
         <v>978</v>
@@ -22640,15 +22640,15 @@
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>5889</v>
+        <v>5890</v>
       </c>
       <c r="B535" s="5" t="s">
-        <v>5765</v>
+        <v>5766</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
-        <v>5890</v>
+        <v>5891</v>
       </c>
       <c r="B536" s="5" t="s">
         <v>981</v>
@@ -23299,7 +23299,7 @@
         <v>1137</v>
       </c>
       <c r="B617" s="5" t="s">
-        <v>5766</v>
+        <v>5767</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.25">
@@ -23355,7 +23355,7 @@
         <v>1150</v>
       </c>
       <c r="B624" s="5" t="s">
-        <v>5767</v>
+        <v>5768</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.25">
@@ -23363,7 +23363,7 @@
         <v>1151</v>
       </c>
       <c r="B625" s="5" t="s">
-        <v>5768</v>
+        <v>5769</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.25">
@@ -23571,7 +23571,7 @@
         <v>1202</v>
       </c>
       <c r="B651" s="5" t="s">
-        <v>5769</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.25">
@@ -23851,7 +23851,7 @@
         <v>1269</v>
       </c>
       <c r="B686" s="5" t="s">
-        <v>5742</v>
+        <v>5743</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.25">
@@ -23915,7 +23915,7 @@
         <v>1284</v>
       </c>
       <c r="B694" s="5" t="s">
-        <v>5743</v>
+        <v>5744</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.25">
@@ -23971,7 +23971,7 @@
         <v>1297</v>
       </c>
       <c r="B701" s="5" t="s">
-        <v>5858</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.25">
@@ -23979,7 +23979,7 @@
         <v>1298</v>
       </c>
       <c r="B702" s="5" t="s">
-        <v>5859</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.25">
@@ -23995,7 +23995,7 @@
         <v>1301</v>
       </c>
       <c r="B704" s="5" t="s">
-        <v>5744</v>
+        <v>5745</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.25">
@@ -24163,7 +24163,7 @@
         <v>1342</v>
       </c>
       <c r="B725" s="5" t="s">
-        <v>5860</v>
+        <v>5861</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.25">
@@ -24227,7 +24227,7 @@
         <v>1357</v>
       </c>
       <c r="B733" s="5" t="s">
-        <v>5770</v>
+        <v>5771</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.25">
@@ -24283,7 +24283,7 @@
         <v>1370</v>
       </c>
       <c r="B740" s="5" t="s">
-        <v>5771</v>
+        <v>5772</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.25">
@@ -24355,12 +24355,12 @@
         <v>1387</v>
       </c>
       <c r="B749" s="5" t="s">
-        <v>5772</v>
+        <v>5773</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A750" s="7" t="s">
-        <v>5879</v>
+        <v>5880</v>
       </c>
       <c r="B750" s="5" t="s">
         <v>1388</v>
@@ -24411,7 +24411,7 @@
         <v>1397</v>
       </c>
       <c r="B756" s="5" t="s">
-        <v>5773</v>
+        <v>5774</v>
       </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.25">
@@ -24443,7 +24443,7 @@
         <v>1404</v>
       </c>
       <c r="B760" s="5" t="s">
-        <v>5774</v>
+        <v>5775</v>
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.25">
@@ -24451,7 +24451,7 @@
         <v>1405</v>
       </c>
       <c r="B761" s="5" t="s">
-        <v>5775</v>
+        <v>5776</v>
       </c>
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.25">
@@ -24467,12 +24467,12 @@
         <v>1408</v>
       </c>
       <c r="B763" s="5" t="s">
-        <v>5776</v>
+        <v>5777</v>
       </c>
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A764" s="7" t="s">
-        <v>5880</v>
+        <v>5881</v>
       </c>
       <c r="B764" s="5" t="s">
         <v>1409</v>
@@ -24499,7 +24499,7 @@
         <v>347</v>
       </c>
       <c r="B767" s="5" t="s">
-        <v>5777</v>
+        <v>5778</v>
       </c>
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.25">
@@ -24579,7 +24579,7 @@
         <v>1432</v>
       </c>
       <c r="B777" s="5" t="s">
-        <v>5778</v>
+        <v>5779</v>
       </c>
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.25">
@@ -24651,7 +24651,7 @@
         <v>1449</v>
       </c>
       <c r="B786" s="5" t="s">
-        <v>5745</v>
+        <v>5746</v>
       </c>
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.25">
@@ -24899,7 +24899,7 @@
         <v>1510</v>
       </c>
       <c r="B817" s="5" t="s">
-        <v>5779</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="818" spans="1:2" x14ac:dyDescent="0.25">
@@ -24931,7 +24931,7 @@
         <v>1517</v>
       </c>
       <c r="B821" s="5" t="s">
-        <v>5780</v>
+        <v>5781</v>
       </c>
     </row>
     <row r="822" spans="1:2" x14ac:dyDescent="0.25">
@@ -24979,7 +24979,7 @@
         <v>1528</v>
       </c>
       <c r="B827" s="5" t="s">
-        <v>5861</v>
+        <v>5862</v>
       </c>
     </row>
     <row r="828" spans="1:2" x14ac:dyDescent="0.25">
@@ -24995,7 +24995,7 @@
         <v>1284</v>
       </c>
       <c r="B829" s="5" t="s">
-        <v>5862</v>
+        <v>5863</v>
       </c>
     </row>
     <row r="830" spans="1:2" x14ac:dyDescent="0.25">
@@ -25003,7 +25003,7 @@
         <v>1531</v>
       </c>
       <c r="B830" s="5" t="s">
-        <v>5863</v>
+        <v>5864</v>
       </c>
     </row>
     <row r="831" spans="1:2" x14ac:dyDescent="0.25">
@@ -25163,7 +25163,7 @@
         <v>1570</v>
       </c>
       <c r="B850" s="5" t="s">
-        <v>5864</v>
+        <v>5865</v>
       </c>
     </row>
     <row r="851" spans="1:2" x14ac:dyDescent="0.25">
@@ -25203,7 +25203,7 @@
         <v>1578</v>
       </c>
       <c r="B855" s="5" t="s">
-        <v>5781</v>
+        <v>5782</v>
       </c>
     </row>
     <row r="856" spans="1:2" x14ac:dyDescent="0.25">
@@ -25227,7 +25227,7 @@
         <v>1583</v>
       </c>
       <c r="B858" s="5" t="s">
-        <v>5782</v>
+        <v>5783</v>
       </c>
     </row>
     <row r="859" spans="1:2" x14ac:dyDescent="0.25">
@@ -25299,7 +25299,7 @@
         <v>1600</v>
       </c>
       <c r="B867" s="5" t="s">
-        <v>5746</v>
+        <v>5747</v>
       </c>
     </row>
     <row r="868" spans="1:2" x14ac:dyDescent="0.25">
@@ -25411,7 +25411,7 @@
         <v>1626</v>
       </c>
       <c r="B881" s="5" t="s">
-        <v>5783</v>
+        <v>5784</v>
       </c>
     </row>
     <row r="882" spans="1:2" x14ac:dyDescent="0.25">
@@ -25443,7 +25443,7 @@
         <v>1633</v>
       </c>
       <c r="B885" s="5" t="s">
-        <v>5784</v>
+        <v>5785</v>
       </c>
     </row>
     <row r="886" spans="1:2" x14ac:dyDescent="0.25">
@@ -25467,7 +25467,7 @@
         <v>1636</v>
       </c>
       <c r="B888" s="5" t="s">
-        <v>5785</v>
+        <v>5786</v>
       </c>
     </row>
     <row r="889" spans="1:2" x14ac:dyDescent="0.25">
@@ -25611,7 +25611,7 @@
         <v>1669</v>
       </c>
       <c r="B906" s="5" t="s">
-        <v>5786</v>
+        <v>5787</v>
       </c>
     </row>
     <row r="907" spans="1:2" x14ac:dyDescent="0.25">
@@ -25675,7 +25675,7 @@
         <v>1684</v>
       </c>
       <c r="B914" s="5" t="s">
-        <v>5787</v>
+        <v>5788</v>
       </c>
     </row>
     <row r="915" spans="1:2" x14ac:dyDescent="0.25">
@@ -25907,7 +25907,7 @@
         <v>1740</v>
       </c>
       <c r="B943" s="5" t="s">
-        <v>5788</v>
+        <v>5789</v>
       </c>
     </row>
     <row r="944" spans="1:2" x14ac:dyDescent="0.25">
@@ -25931,7 +25931,7 @@
         <v>1745</v>
       </c>
       <c r="B946" s="5" t="s">
-        <v>5789</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="947" spans="1:2" x14ac:dyDescent="0.25">
@@ -26651,7 +26651,7 @@
         <v>1922</v>
       </c>
       <c r="B1036" s="5" t="s">
-        <v>5790</v>
+        <v>5791</v>
       </c>
     </row>
     <row r="1037" spans="1:2" x14ac:dyDescent="0.25">
@@ -27040,7 +27040,7 @@
     </row>
     <row r="1085" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1085" s="2" t="s">
-        <v>5891</v>
+        <v>5892</v>
       </c>
       <c r="B1085" s="5" t="s">
         <v>2009</v>
@@ -27056,7 +27056,7 @@
     </row>
     <row r="1087" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1087" s="2" t="s">
-        <v>5892</v>
+        <v>5893</v>
       </c>
       <c r="B1087" s="5" t="s">
         <v>2012</v>
@@ -27835,7 +27835,7 @@
         <v>2202</v>
       </c>
       <c r="B1184" s="5" t="s">
-        <v>5791</v>
+        <v>5792</v>
       </c>
     </row>
     <row r="1185" spans="1:2" x14ac:dyDescent="0.25">
@@ -27899,7 +27899,7 @@
         <v>2217</v>
       </c>
       <c r="B1192" s="5" t="s">
-        <v>5792</v>
+        <v>5793</v>
       </c>
     </row>
     <row r="1193" spans="1:2" x14ac:dyDescent="0.25">
@@ -27936,7 +27936,7 @@
     </row>
     <row r="1197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1197" s="7" t="s">
-        <v>5881</v>
+        <v>5882</v>
       </c>
       <c r="B1197" s="5" t="s">
         <v>2226</v>
@@ -28059,7 +28059,7 @@
         <v>2255</v>
       </c>
       <c r="B1212" s="8" t="s">
-        <v>5793</v>
+        <v>5794</v>
       </c>
     </row>
     <row r="1213" spans="1:2" x14ac:dyDescent="0.25">
@@ -28155,7 +28155,7 @@
         <v>2278</v>
       </c>
       <c r="B1224" s="5" t="s">
-        <v>5794</v>
+        <v>5795</v>
       </c>
     </row>
     <row r="1225" spans="1:2" x14ac:dyDescent="0.25">
@@ -28331,7 +28331,7 @@
         <v>2321</v>
       </c>
       <c r="B1246" s="5" t="s">
-        <v>5795</v>
+        <v>5796</v>
       </c>
     </row>
     <row r="1247" spans="1:2" x14ac:dyDescent="0.25">
@@ -28544,7 +28544,7 @@
     </row>
     <row r="1273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1273" s="7" t="s">
-        <v>5882</v>
+        <v>5883</v>
       </c>
       <c r="B1273" s="5" t="s">
         <v>2374</v>
@@ -28555,7 +28555,7 @@
         <v>2375</v>
       </c>
       <c r="B1274" s="5" t="s">
-        <v>5796</v>
+        <v>5797</v>
       </c>
     </row>
     <row r="1275" spans="1:2" x14ac:dyDescent="0.25">
@@ -28619,7 +28619,7 @@
         <v>2390</v>
       </c>
       <c r="B1282" s="5" t="s">
-        <v>5865</v>
+        <v>5866</v>
       </c>
     </row>
     <row r="1283" spans="1:2" x14ac:dyDescent="0.25">
@@ -28995,7 +28995,7 @@
         <v>2483</v>
       </c>
       <c r="B1329" s="5" t="s">
-        <v>5797</v>
+        <v>5798</v>
       </c>
     </row>
     <row r="1330" spans="1:2" x14ac:dyDescent="0.25">
@@ -29451,7 +29451,7 @@
         <v>2592</v>
       </c>
       <c r="B1386" s="5" t="s">
-        <v>5798</v>
+        <v>5799</v>
       </c>
     </row>
     <row r="1387" spans="1:2" x14ac:dyDescent="0.25">
@@ -30288,7 +30288,7 @@
     </row>
     <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1491" s="2" t="s">
-        <v>5954</v>
+        <v>5955</v>
       </c>
       <c r="B1491" s="5" t="s">
         <v>2795</v>
@@ -30331,7 +30331,7 @@
         <v>2804</v>
       </c>
       <c r="B1496" s="5" t="s">
-        <v>5799</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
@@ -30379,7 +30379,7 @@
         <v>2813</v>
       </c>
       <c r="B1502" s="5" t="s">
-        <v>5800</v>
+        <v>5801</v>
       </c>
     </row>
     <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
@@ -30395,7 +30395,7 @@
         <v>2816</v>
       </c>
       <c r="B1504" s="5" t="s">
-        <v>5801</v>
+        <v>5802</v>
       </c>
     </row>
     <row r="1505" spans="1:2" x14ac:dyDescent="0.25">
@@ -30416,7 +30416,7 @@
     </row>
     <row r="1507" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1507" s="1" t="s">
-        <v>5955</v>
+        <v>5956</v>
       </c>
       <c r="B1507" s="5" t="s">
         <v>2821</v>
@@ -30427,7 +30427,7 @@
         <v>2822</v>
       </c>
       <c r="B1508" s="5" t="s">
-        <v>5802</v>
+        <v>5803</v>
       </c>
     </row>
     <row r="1509" spans="1:2" x14ac:dyDescent="0.25">
@@ -30931,7 +30931,7 @@
         <v>2935</v>
       </c>
       <c r="B1571" s="5" t="s">
-        <v>5866</v>
+        <v>5867</v>
       </c>
     </row>
     <row r="1572" spans="1:2" x14ac:dyDescent="0.25">
@@ -30979,7 +30979,7 @@
         <v>2946</v>
       </c>
       <c r="B1577" s="5" t="s">
-        <v>5867</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="1578" spans="1:2" x14ac:dyDescent="0.25">
@@ -31019,7 +31019,7 @@
         <v>2955</v>
       </c>
       <c r="B1582" s="5" t="s">
-        <v>5747</v>
+        <v>5748</v>
       </c>
     </row>
     <row r="1583" spans="1:2" x14ac:dyDescent="0.25">
@@ -31035,7 +31035,7 @@
         <v>2958</v>
       </c>
       <c r="B1584" s="5" t="s">
-        <v>5803</v>
+        <v>5804</v>
       </c>
     </row>
     <row r="1585" spans="1:2" x14ac:dyDescent="0.25">
@@ -31259,7 +31259,7 @@
         <v>3013</v>
       </c>
       <c r="B1612" s="5" t="s">
-        <v>5748</v>
+        <v>5749</v>
       </c>
     </row>
     <row r="1613" spans="1:2" x14ac:dyDescent="0.25">
@@ -31299,7 +31299,7 @@
         <v>3022</v>
       </c>
       <c r="B1617" s="5" t="s">
-        <v>5804</v>
+        <v>5805</v>
       </c>
     </row>
     <row r="1618" spans="1:2" x14ac:dyDescent="0.25">
@@ -31395,7 +31395,7 @@
         <v>3045</v>
       </c>
       <c r="B1629" s="5" t="s">
-        <v>5805</v>
+        <v>5806</v>
       </c>
     </row>
     <row r="1630" spans="1:2" x14ac:dyDescent="0.25">
@@ -31419,7 +31419,7 @@
         <v>3050</v>
       </c>
       <c r="B1632" s="5" t="s">
-        <v>5806</v>
+        <v>5807</v>
       </c>
     </row>
     <row r="1633" spans="1:2" x14ac:dyDescent="0.25">
@@ -31432,7 +31432,7 @@
     </row>
     <row r="1634" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1634" s="9" t="s">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="B1634" s="5" t="s">
         <v>3053</v>
@@ -31475,7 +31475,7 @@
         <v>3062</v>
       </c>
       <c r="B1639" s="5" t="s">
-        <v>5868</v>
+        <v>5869</v>
       </c>
     </row>
     <row r="1640" spans="1:2" x14ac:dyDescent="0.25">
@@ -31531,7 +31531,7 @@
         <v>3075</v>
       </c>
       <c r="B1646" s="5" t="s">
-        <v>5807</v>
+        <v>5808</v>
       </c>
     </row>
     <row r="1647" spans="1:2" x14ac:dyDescent="0.25">
@@ -31659,7 +31659,7 @@
         <v>3106</v>
       </c>
       <c r="B1662" s="5" t="s">
-        <v>5808</v>
+        <v>5809</v>
       </c>
     </row>
     <row r="1663" spans="1:2" x14ac:dyDescent="0.25">
@@ -31843,7 +31843,7 @@
         <v>3151</v>
       </c>
       <c r="B1685" s="5" t="s">
-        <v>5809</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="1686" spans="1:2" x14ac:dyDescent="0.25">
@@ -31963,7 +31963,7 @@
         <v>3180</v>
       </c>
       <c r="B1700" s="5" t="s">
-        <v>5810</v>
+        <v>5811</v>
       </c>
     </row>
     <row r="1701" spans="1:2" x14ac:dyDescent="0.25">
@@ -32059,7 +32059,7 @@
         <v>3203</v>
       </c>
       <c r="B1712" s="5" t="s">
-        <v>5811</v>
+        <v>5812</v>
       </c>
     </row>
     <row r="1713" spans="1:2" x14ac:dyDescent="0.25">
@@ -32075,7 +32075,7 @@
         <v>3206</v>
       </c>
       <c r="B1714" s="5" t="s">
-        <v>5812</v>
+        <v>5813</v>
       </c>
     </row>
     <row r="1715" spans="1:2" x14ac:dyDescent="0.25">
@@ -32131,7 +32131,7 @@
         <v>3219</v>
       </c>
       <c r="B1721" s="5" t="s">
-        <v>5813</v>
+        <v>5814</v>
       </c>
     </row>
     <row r="1722" spans="1:2" x14ac:dyDescent="0.25">
@@ -32139,7 +32139,7 @@
         <v>3220</v>
       </c>
       <c r="B1722" s="5" t="s">
-        <v>5814</v>
+        <v>5815</v>
       </c>
     </row>
     <row r="1723" spans="1:2" x14ac:dyDescent="0.25">
@@ -32219,7 +32219,7 @@
         <v>3239</v>
       </c>
       <c r="B1732" s="5" t="s">
-        <v>5815</v>
+        <v>5816</v>
       </c>
     </row>
     <row r="1733" spans="1:2" x14ac:dyDescent="0.25">
@@ -32856,7 +32856,7 @@
     </row>
     <row r="1812" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1812" s="2" t="s">
-        <v>5893</v>
+        <v>5894</v>
       </c>
       <c r="B1812" s="5" t="s">
         <v>3372</v>
@@ -32872,7 +32872,7 @@
     </row>
     <row r="1814" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1814" s="2" t="s">
-        <v>5956</v>
+        <v>5957</v>
       </c>
       <c r="B1814" s="5" t="s">
         <v>3375</v>
@@ -32928,7 +32928,7 @@
     </row>
     <row r="1821" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1821" s="2" t="s">
-        <v>5894</v>
+        <v>5895</v>
       </c>
       <c r="B1821" s="5" t="s">
         <v>3388</v>
@@ -32995,7 +32995,7 @@
         <v>3403</v>
       </c>
       <c r="B1829" s="5" t="s">
-        <v>5816</v>
+        <v>5817</v>
       </c>
     </row>
     <row r="1830" spans="1:2" x14ac:dyDescent="0.25">
@@ -33035,7 +33035,7 @@
         <v>3412</v>
       </c>
       <c r="B1834" s="5" t="s">
-        <v>5869</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="1835" spans="1:2" x14ac:dyDescent="0.25">
@@ -33771,7 +33771,7 @@
         <v>3577</v>
       </c>
       <c r="B1926" s="5" t="s">
-        <v>5817</v>
+        <v>5818</v>
       </c>
     </row>
     <row r="1927" spans="1:2" x14ac:dyDescent="0.25">
@@ -33907,7 +33907,7 @@
         <v>3610</v>
       </c>
       <c r="B1943" s="5" t="s">
-        <v>5818</v>
+        <v>5819</v>
       </c>
     </row>
     <row r="1944" spans="1:2" x14ac:dyDescent="0.25">
@@ -33987,7 +33987,7 @@
         <v>3629</v>
       </c>
       <c r="B1953" s="5" t="s">
-        <v>5819</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="1954" spans="1:2" x14ac:dyDescent="0.25">
@@ -34043,7 +34043,7 @@
         <v>3642</v>
       </c>
       <c r="B1960" s="5" t="s">
-        <v>5820</v>
+        <v>5821</v>
       </c>
     </row>
     <row r="1961" spans="1:2" x14ac:dyDescent="0.25">
@@ -34259,7 +34259,7 @@
         <v>3695</v>
       </c>
       <c r="B1987" s="5" t="s">
-        <v>5821</v>
+        <v>5822</v>
       </c>
     </row>
     <row r="1988" spans="1:2" x14ac:dyDescent="0.25">
@@ -34296,10 +34296,10 @@
     </row>
     <row r="1992" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1992" s="7" t="s">
-        <v>5884</v>
+        <v>5885</v>
       </c>
       <c r="B1992" s="5" t="s">
-        <v>5885</v>
+        <v>5886</v>
       </c>
     </row>
     <row r="1993" spans="1:2" x14ac:dyDescent="0.25">
@@ -34392,7 +34392,7 @@
     </row>
     <row r="2004" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2004" s="7" t="s">
-        <v>5886</v>
+        <v>5887</v>
       </c>
       <c r="B2004" s="5" t="s">
         <v>3726</v>
@@ -34563,7 +34563,7 @@
         <v>3767</v>
       </c>
       <c r="B2025" s="5" t="s">
-        <v>5822</v>
+        <v>5823</v>
       </c>
     </row>
     <row r="2026" spans="1:2" x14ac:dyDescent="0.25">
@@ -34643,7 +34643,7 @@
         <v>3784</v>
       </c>
       <c r="B2035" s="5" t="s">
-        <v>5870</v>
+        <v>5871</v>
       </c>
     </row>
     <row r="2036" spans="1:2" x14ac:dyDescent="0.25">
@@ -34675,7 +34675,7 @@
         <v>3791</v>
       </c>
       <c r="B2039" s="5" t="s">
-        <v>5823</v>
+        <v>5824</v>
       </c>
     </row>
     <row r="2040" spans="1:2" x14ac:dyDescent="0.25">
@@ -34755,7 +34755,7 @@
         <v>3810</v>
       </c>
       <c r="B2049" s="5" t="s">
-        <v>5871</v>
+        <v>5872</v>
       </c>
     </row>
     <row r="2050" spans="1:2" x14ac:dyDescent="0.25">
@@ -34795,7 +34795,7 @@
         <v>3819</v>
       </c>
       <c r="B2054" s="5" t="s">
-        <v>5824</v>
+        <v>5825</v>
       </c>
     </row>
     <row r="2055" spans="1:2" x14ac:dyDescent="0.25">
@@ -35043,7 +35043,7 @@
         <v>3880</v>
       </c>
       <c r="B2085" s="5" t="s">
-        <v>5825</v>
+        <v>5826</v>
       </c>
     </row>
     <row r="2086" spans="1:2" x14ac:dyDescent="0.25">
@@ -35227,7 +35227,7 @@
         <v>3925</v>
       </c>
       <c r="B2108" s="5" t="s">
-        <v>5826</v>
+        <v>5827</v>
       </c>
     </row>
     <row r="2109" spans="1:2" x14ac:dyDescent="0.25">
@@ -35424,7 +35424,7 @@
     </row>
     <row r="2133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2133" s="2" t="s">
-        <v>5895</v>
+        <v>5896</v>
       </c>
       <c r="B2133" s="5" t="s">
         <v>3971</v>
@@ -35432,7 +35432,7 @@
     </row>
     <row r="2134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2134" s="2" t="s">
-        <v>5896</v>
+        <v>5897</v>
       </c>
       <c r="B2134" s="5" t="s">
         <v>3972</v>
@@ -35504,7 +35504,7 @@
     </row>
     <row r="2143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2143" s="2" t="s">
-        <v>5897</v>
+        <v>5898</v>
       </c>
       <c r="B2143" s="5" t="s">
         <v>3989</v>
@@ -35520,7 +35520,7 @@
     </row>
     <row r="2145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2145" s="2" t="s">
-        <v>5898</v>
+        <v>5899</v>
       </c>
       <c r="B2145" s="5" t="s">
         <v>3992</v>
@@ -35795,7 +35795,7 @@
         <v>4052</v>
       </c>
       <c r="B2179" s="5" t="s">
-        <v>5827</v>
+        <v>5828</v>
       </c>
     </row>
     <row r="2180" spans="1:2" x14ac:dyDescent="0.25">
@@ -36107,7 +36107,7 @@
         <v>4129</v>
       </c>
       <c r="B2218" s="5" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
     </row>
     <row r="2219" spans="1:2" x14ac:dyDescent="0.25">
@@ -36203,7 +36203,7 @@
         <v>4152</v>
       </c>
       <c r="B2230" s="5" t="s">
-        <v>5829</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="2231" spans="1:2" x14ac:dyDescent="0.25">
@@ -36283,7 +36283,7 @@
         <v>4171</v>
       </c>
       <c r="B2240" s="5" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
     </row>
     <row r="2241" spans="1:2" x14ac:dyDescent="0.25">
@@ -36560,7 +36560,7 @@
     </row>
     <row r="2275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2275" s="2" t="s">
-        <v>5899</v>
+        <v>5900</v>
       </c>
       <c r="B2275" s="5" t="s">
         <v>4236</v>
@@ -36584,7 +36584,7 @@
     </row>
     <row r="2278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2278" s="2" t="s">
-        <v>5900</v>
+        <v>5901</v>
       </c>
       <c r="B2278" s="5" t="s">
         <v>4241</v>
@@ -36592,7 +36592,7 @@
     </row>
     <row r="2279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2279" s="2" t="s">
-        <v>5901</v>
+        <v>5902</v>
       </c>
       <c r="B2279" s="5" t="s">
         <v>4242</v>
@@ -36608,7 +36608,7 @@
     </row>
     <row r="2281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2281" s="2" t="s">
-        <v>5902</v>
+        <v>5903</v>
       </c>
       <c r="B2281" s="5" t="s">
         <v>4245</v>
@@ -36616,7 +36616,7 @@
     </row>
     <row r="2282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2282" s="2" t="s">
-        <v>5903</v>
+        <v>5904</v>
       </c>
       <c r="B2282" s="5" t="s">
         <v>4246</v>
@@ -37139,7 +37139,7 @@
         <v>4371</v>
       </c>
       <c r="B2347" s="5" t="s">
-        <v>5831</v>
+        <v>5832</v>
       </c>
     </row>
     <row r="2348" spans="1:2" x14ac:dyDescent="0.25">
@@ -37243,7 +37243,7 @@
         <v>4396</v>
       </c>
       <c r="B2360" s="5" t="s">
-        <v>5832</v>
+        <v>5833</v>
       </c>
     </row>
     <row r="2361" spans="1:2" x14ac:dyDescent="0.25">
@@ -37259,7 +37259,7 @@
         <v>4399</v>
       </c>
       <c r="B2362" s="5" t="s">
-        <v>5833</v>
+        <v>5834</v>
       </c>
     </row>
     <row r="2363" spans="1:2" x14ac:dyDescent="0.25">
@@ -37515,7 +37515,7 @@
         <v>4462</v>
       </c>
       <c r="B2394" s="5" t="s">
-        <v>5834</v>
+        <v>5835</v>
       </c>
     </row>
     <row r="2395" spans="1:2" x14ac:dyDescent="0.25">
@@ -37643,7 +37643,7 @@
         <v>4493</v>
       </c>
       <c r="B2410" s="5" t="s">
-        <v>5835</v>
+        <v>5836</v>
       </c>
     </row>
     <row r="2411" spans="1:2" x14ac:dyDescent="0.25">
@@ -37651,7 +37651,7 @@
         <v>4494</v>
       </c>
       <c r="B2411" s="5" t="s">
-        <v>5836</v>
+        <v>5837</v>
       </c>
     </row>
     <row r="2412" spans="1:2" x14ac:dyDescent="0.25">
@@ -37739,7 +37739,7 @@
         <v>4515</v>
       </c>
       <c r="B2422" s="5" t="s">
-        <v>5837</v>
+        <v>5838</v>
       </c>
     </row>
     <row r="2423" spans="1:2" x14ac:dyDescent="0.25">
@@ -37856,7 +37856,7 @@
     </row>
     <row r="2437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2437" s="2" t="s">
-        <v>5904</v>
+        <v>5905</v>
       </c>
       <c r="B2437" s="5" t="s">
         <v>4541</v>
@@ -37864,7 +37864,7 @@
     </row>
     <row r="2438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2438" s="2" t="s">
-        <v>5905</v>
+        <v>5906</v>
       </c>
       <c r="B2438" s="5" t="s">
         <v>4542</v>
@@ -38051,7 +38051,7 @@
         <v>4584</v>
       </c>
       <c r="B2461" s="5" t="s">
-        <v>5838</v>
+        <v>5839</v>
       </c>
     </row>
     <row r="2462" spans="1:2" x14ac:dyDescent="0.25">
@@ -38155,7 +38155,7 @@
         <v>4609</v>
       </c>
       <c r="B2474" s="5" t="s">
-        <v>5872</v>
+        <v>5873</v>
       </c>
     </row>
     <row r="2475" spans="1:2" x14ac:dyDescent="0.25">
@@ -38283,7 +38283,7 @@
         <v>4640</v>
       </c>
       <c r="B2490" s="5" t="s">
-        <v>5839</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="2491" spans="1:2" x14ac:dyDescent="0.25">
@@ -38347,7 +38347,7 @@
         <v>4655</v>
       </c>
       <c r="B2498" s="5" t="s">
-        <v>5840</v>
+        <v>5841</v>
       </c>
     </row>
     <row r="2499" spans="1:2" x14ac:dyDescent="0.25">
@@ -38379,7 +38379,7 @@
         <v>4662</v>
       </c>
       <c r="B2502" s="5" t="s">
-        <v>5873</v>
+        <v>5874</v>
       </c>
     </row>
     <row r="2503" spans="1:2" x14ac:dyDescent="0.25">
@@ -38443,7 +38443,7 @@
         <v>4677</v>
       </c>
       <c r="B2510" s="5" t="s">
-        <v>5841</v>
+        <v>5842</v>
       </c>
     </row>
     <row r="2511" spans="1:2" x14ac:dyDescent="0.25">
@@ -38587,7 +38587,7 @@
         <v>4710</v>
       </c>
       <c r="B2528" s="5" t="s">
-        <v>5842</v>
+        <v>5843</v>
       </c>
     </row>
     <row r="2529" spans="1:2" x14ac:dyDescent="0.25">
@@ -38699,7 +38699,7 @@
         <v>4737</v>
       </c>
       <c r="B2542" s="5" t="s">
-        <v>5843</v>
+        <v>5844</v>
       </c>
     </row>
     <row r="2543" spans="1:2" x14ac:dyDescent="0.25">
@@ -38771,7 +38771,7 @@
         <v>4753</v>
       </c>
       <c r="B2551" s="5" t="s">
-        <v>5874</v>
+        <v>5875</v>
       </c>
     </row>
     <row r="2552" spans="1:2" x14ac:dyDescent="0.25">
@@ -38915,7 +38915,7 @@
         <v>4787</v>
       </c>
       <c r="B2569" s="5" t="s">
-        <v>5875</v>
+        <v>5876</v>
       </c>
     </row>
     <row r="2570" spans="1:2" x14ac:dyDescent="0.25">
@@ -39075,7 +39075,7 @@
         <v>4823</v>
       </c>
       <c r="B2589" s="5" t="s">
-        <v>5876</v>
+        <v>5877</v>
       </c>
     </row>
     <row r="2590" spans="1:2" x14ac:dyDescent="0.25">
@@ -39235,7 +39235,7 @@
         <v>4862</v>
       </c>
       <c r="B2609" s="5" t="s">
-        <v>5844</v>
+        <v>5845</v>
       </c>
     </row>
     <row r="2610" spans="1:2" x14ac:dyDescent="0.25">
@@ -39331,7 +39331,7 @@
         <v>4885</v>
       </c>
       <c r="B2621" s="5" t="s">
-        <v>5845</v>
+        <v>5846</v>
       </c>
     </row>
     <row r="2622" spans="1:2" x14ac:dyDescent="0.25">
@@ -39443,7 +39443,7 @@
         <v>4912</v>
       </c>
       <c r="B2635" s="5" t="s">
-        <v>5846</v>
+        <v>5847</v>
       </c>
     </row>
     <row r="2636" spans="1:2" x14ac:dyDescent="0.25">
@@ -39624,7 +39624,7 @@
     </row>
     <row r="2658" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2658" s="2" t="s">
-        <v>5906</v>
+        <v>5907</v>
       </c>
       <c r="B2658" s="5" t="s">
         <v>4953</v>
@@ -39632,7 +39632,7 @@
     </row>
     <row r="2659" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2659" s="2" t="s">
-        <v>5907</v>
+        <v>5908</v>
       </c>
       <c r="B2659" s="5" t="s">
         <v>4954</v>
@@ -39747,7 +39747,7 @@
         <v>4981</v>
       </c>
       <c r="B2673" s="5" t="s">
-        <v>5847</v>
+        <v>5848</v>
       </c>
     </row>
     <row r="2674" spans="1:2" x14ac:dyDescent="0.25">
@@ -39824,7 +39824,7 @@
     </row>
     <row r="2683" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2683" s="2" t="s">
-        <v>5908</v>
+        <v>5909</v>
       </c>
       <c r="B2683" s="5" t="s">
         <v>5000</v>
@@ -39832,7 +39832,7 @@
     </row>
     <row r="2684" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2684" s="2" t="s">
-        <v>5909</v>
+        <v>5910</v>
       </c>
       <c r="B2684" s="5" t="s">
         <v>5001</v>
@@ -39840,7 +39840,7 @@
     </row>
     <row r="2685" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2685" s="2" t="s">
-        <v>5910</v>
+        <v>5911</v>
       </c>
       <c r="B2685" s="5" t="s">
         <v>5002</v>
@@ -39864,7 +39864,7 @@
     </row>
     <row r="2688" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2688" s="2" t="s">
-        <v>5911</v>
+        <v>5912</v>
       </c>
       <c r="B2688" s="5" t="s">
         <v>5007</v>
@@ -39872,7 +39872,7 @@
     </row>
     <row r="2689" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2689" s="2" t="s">
-        <v>5912</v>
+        <v>5913</v>
       </c>
       <c r="B2689" s="5" t="s">
         <v>5008</v>
@@ -39880,7 +39880,7 @@
     </row>
     <row r="2690" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2690" s="2" t="s">
-        <v>5913</v>
+        <v>5914</v>
       </c>
       <c r="B2690" s="5" t="s">
         <v>5009</v>
@@ -39888,7 +39888,7 @@
     </row>
     <row r="2691" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2691" s="2" t="s">
-        <v>5914</v>
+        <v>5915</v>
       </c>
       <c r="B2691" s="5" t="s">
         <v>5010</v>
@@ -39896,7 +39896,7 @@
     </row>
     <row r="2692" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2692" s="2" t="s">
-        <v>5915</v>
+        <v>5916</v>
       </c>
       <c r="B2692" s="5" t="s">
         <v>5011</v>
@@ -39904,7 +39904,7 @@
     </row>
     <row r="2693" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2693" s="2" t="s">
-        <v>5916</v>
+        <v>5917</v>
       </c>
       <c r="B2693" s="5" t="s">
         <v>5012</v>
@@ -39912,7 +39912,7 @@
     </row>
     <row r="2694" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2694" s="2" t="s">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="B2694" s="5" t="s">
         <v>5013</v>
@@ -39920,7 +39920,7 @@
     </row>
     <row r="2695" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2695" s="2" t="s">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="B2695" s="5" t="s">
         <v>5014</v>
@@ -39936,7 +39936,7 @@
     </row>
     <row r="2697" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2697" s="2" t="s">
-        <v>5919</v>
+        <v>5920</v>
       </c>
       <c r="B2697" s="5" t="s">
         <v>5017</v>
@@ -39944,7 +39944,7 @@
     </row>
     <row r="2698" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2698" s="2" t="s">
-        <v>5920</v>
+        <v>5921</v>
       </c>
       <c r="B2698" s="5" t="s">
         <v>5018</v>
@@ -39952,7 +39952,7 @@
     </row>
     <row r="2699" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2699" s="2" t="s">
-        <v>5921</v>
+        <v>5922</v>
       </c>
       <c r="B2699" s="5" t="s">
         <v>5019</v>
@@ -39960,7 +39960,7 @@
     </row>
     <row r="2700" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2700" s="2" t="s">
-        <v>5922</v>
+        <v>5923</v>
       </c>
       <c r="B2700" s="5" t="s">
         <v>5020</v>
@@ -39968,7 +39968,7 @@
     </row>
     <row r="2701" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2701" s="2" t="s">
-        <v>5923</v>
+        <v>5924</v>
       </c>
       <c r="B2701" s="5" t="s">
         <v>5021</v>
@@ -39976,7 +39976,7 @@
     </row>
     <row r="2702" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2702" s="2" t="s">
-        <v>5924</v>
+        <v>5925</v>
       </c>
       <c r="B2702" s="5" t="s">
         <v>5022</v>
@@ -39984,7 +39984,7 @@
     </row>
     <row r="2703" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2703" s="2" t="s">
-        <v>5925</v>
+        <v>5926</v>
       </c>
       <c r="B2703" s="5" t="s">
         <v>5023</v>
@@ -39992,7 +39992,7 @@
     </row>
     <row r="2704" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2704" s="2" t="s">
-        <v>5926</v>
+        <v>5927</v>
       </c>
       <c r="B2704" s="5" t="s">
         <v>5024</v>
@@ -40000,7 +40000,7 @@
     </row>
     <row r="2705" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2705" s="2" t="s">
-        <v>5927</v>
+        <v>5928</v>
       </c>
       <c r="B2705" s="5" t="s">
         <v>5025</v>
@@ -40032,7 +40032,7 @@
     </row>
     <row r="2709" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2709" s="2" t="s">
-        <v>5928</v>
+        <v>5929</v>
       </c>
       <c r="B2709" s="5" t="s">
         <v>5032</v>
@@ -40040,7 +40040,7 @@
     </row>
     <row r="2710" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2710" s="2" t="s">
-        <v>5957</v>
+        <v>5958</v>
       </c>
       <c r="B2710" s="5" t="s">
         <v>5033</v>
@@ -40048,7 +40048,7 @@
     </row>
     <row r="2711" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2711" s="2" t="s">
-        <v>5929</v>
+        <v>5930</v>
       </c>
       <c r="B2711" s="5" t="s">
         <v>5034</v>
@@ -40056,7 +40056,7 @@
     </row>
     <row r="2712" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2712" s="2" t="s">
-        <v>5930</v>
+        <v>5931</v>
       </c>
       <c r="B2712" s="5" t="s">
         <v>5035</v>
@@ -40139,7 +40139,7 @@
         <v>5053</v>
       </c>
       <c r="B2722" s="5" t="s">
-        <v>5848</v>
+        <v>5849</v>
       </c>
     </row>
     <row r="2723" spans="1:2" x14ac:dyDescent="0.25">
@@ -40323,7 +40323,7 @@
         <v>5098</v>
       </c>
       <c r="B2745" s="5" t="s">
-        <v>5849</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="2746" spans="1:2" x14ac:dyDescent="0.25">
@@ -40707,7 +40707,7 @@
         <v>5193</v>
       </c>
       <c r="B2793" s="5" t="s">
-        <v>5850</v>
+        <v>5851</v>
       </c>
     </row>
     <row r="2794" spans="1:2" x14ac:dyDescent="0.25">
@@ -40939,7 +40939,7 @@
         <v>5250</v>
       </c>
       <c r="B2822" s="5" t="s">
-        <v>5851</v>
+        <v>5852</v>
       </c>
     </row>
     <row r="2823" spans="1:2" x14ac:dyDescent="0.25">
@@ -42032,7 +42032,7 @@
     </row>
     <row r="2959" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2959" s="2" t="s">
-        <v>5931</v>
+        <v>5932</v>
       </c>
       <c r="B2959" s="5" t="s">
         <v>5518</v>
@@ -42040,7 +42040,7 @@
     </row>
     <row r="2960" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2960" s="2" t="s">
-        <v>5932</v>
+        <v>5933</v>
       </c>
       <c r="B2960" s="5" t="s">
         <v>5519</v>
@@ -42048,7 +42048,7 @@
     </row>
     <row r="2961" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2961" s="2" t="s">
-        <v>5933</v>
+        <v>5934</v>
       </c>
       <c r="B2961" s="5" t="s">
         <v>5520</v>
@@ -42056,7 +42056,7 @@
     </row>
     <row r="2962" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2962" s="2" t="s">
-        <v>5934</v>
+        <v>5935</v>
       </c>
       <c r="B2962" s="5" t="s">
         <v>5521</v>
@@ -42064,7 +42064,7 @@
     </row>
     <row r="2963" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2963" s="2" t="s">
-        <v>5935</v>
+        <v>5936</v>
       </c>
       <c r="B2963" s="5" t="s">
         <v>5522</v>
@@ -42072,7 +42072,7 @@
     </row>
     <row r="2964" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2964" s="2" t="s">
-        <v>5936</v>
+        <v>5937</v>
       </c>
       <c r="B2964" s="5" t="s">
         <v>5523</v>
@@ -42080,7 +42080,7 @@
     </row>
     <row r="2965" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2965" s="2" t="s">
-        <v>5937</v>
+        <v>5938</v>
       </c>
       <c r="B2965" s="5" t="s">
         <v>5524</v>
@@ -42088,15 +42088,15 @@
     </row>
     <row r="2966" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2966" s="2" t="s">
-        <v>5938</v>
+        <v>5939</v>
       </c>
       <c r="B2966" s="5" t="s">
-        <v>5877</v>
+        <v>5878</v>
       </c>
     </row>
     <row r="2967" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2967" s="2" t="s">
-        <v>5939</v>
+        <v>5940</v>
       </c>
       <c r="B2967" s="5" t="s">
         <v>5525</v>
@@ -42104,7 +42104,7 @@
     </row>
     <row r="2968" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2968" s="2" t="s">
-        <v>5940</v>
+        <v>5941</v>
       </c>
       <c r="B2968" s="5" t="s">
         <v>5526</v>
@@ -42112,7 +42112,7 @@
     </row>
     <row r="2969" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2969" s="2" t="s">
-        <v>5941</v>
+        <v>5942</v>
       </c>
       <c r="B2969" s="5" t="s">
         <v>5527</v>
@@ -42120,7 +42120,7 @@
     </row>
     <row r="2970" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2970" s="2" t="s">
-        <v>5942</v>
+        <v>5943</v>
       </c>
       <c r="B2970" s="5" t="s">
         <v>5528</v>
@@ -42128,7 +42128,7 @@
     </row>
     <row r="2971" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2971" s="2" t="s">
-        <v>5943</v>
+        <v>5944</v>
       </c>
       <c r="B2971" s="5" t="s">
         <v>5529</v>
@@ -42136,7 +42136,7 @@
     </row>
     <row r="2972" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2972" s="2" t="s">
-        <v>5944</v>
+        <v>5945</v>
       </c>
       <c r="B2972" s="5" t="s">
         <v>5530</v>
@@ -42144,7 +42144,7 @@
     </row>
     <row r="2973" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2973" s="2" t="s">
-        <v>5945</v>
+        <v>5946</v>
       </c>
       <c r="B2973" s="5" t="s">
         <v>5531</v>
@@ -42152,7 +42152,7 @@
     </row>
     <row r="2974" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2974" s="2" t="s">
-        <v>5946</v>
+        <v>5947</v>
       </c>
       <c r="B2974" s="5" t="s">
         <v>5532</v>
@@ -42160,7 +42160,7 @@
     </row>
     <row r="2975" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2975" s="2" t="s">
-        <v>5947</v>
+        <v>5948</v>
       </c>
       <c r="B2975" s="5" t="s">
         <v>5533</v>
@@ -42168,7 +42168,7 @@
     </row>
     <row r="2976" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2976" s="2" t="s">
-        <v>5948</v>
+        <v>5949</v>
       </c>
       <c r="B2976" s="5" t="s">
         <v>5534</v>
@@ -42176,7 +42176,7 @@
     </row>
     <row r="2977" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2977" s="2" t="s">
-        <v>5949</v>
+        <v>5950</v>
       </c>
       <c r="B2977" s="5" t="s">
         <v>5535</v>
@@ -42184,7 +42184,7 @@
     </row>
     <row r="2978" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2978" s="2" t="s">
-        <v>5950</v>
+        <v>5951</v>
       </c>
       <c r="B2978" s="5" t="s">
         <v>5536</v>
@@ -42192,7 +42192,7 @@
     </row>
     <row r="2979" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2979" s="2" t="s">
-        <v>5951</v>
+        <v>5952</v>
       </c>
       <c r="B2979" s="5" t="s">
         <v>5537</v>
@@ -42200,7 +42200,7 @@
     </row>
     <row r="2980" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2980" s="2" t="s">
-        <v>5952</v>
+        <v>5953</v>
       </c>
       <c r="B2980" s="5" t="s">
         <v>5538</v>
@@ -42208,7 +42208,7 @@
     </row>
     <row r="2981" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2981" s="2" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="B2981" s="5" t="s">
         <v>5539</v>
@@ -42443,7 +42443,7 @@
         <v>5593</v>
       </c>
       <c r="B3010" s="5" t="s">
-        <v>5852</v>
+        <v>5853</v>
       </c>
     </row>
     <row r="3011" spans="1:2" x14ac:dyDescent="0.25">
@@ -42779,7 +42779,7 @@
         <v>5676</v>
       </c>
       <c r="B3052" s="5" t="s">
-        <v>5878</v>
+        <v>5879</v>
       </c>
     </row>
     <row r="3053" spans="1:2" x14ac:dyDescent="0.25">
@@ -42803,191 +42803,191 @@
         <v>5681</v>
       </c>
       <c r="B3055" s="5" t="s">
-        <v>5853</v>
+        <v>5854</v>
       </c>
     </row>
     <row r="3056" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3056" s="3" t="s">
-        <v>5968</v>
+        <v>5682</v>
       </c>
       <c r="B3056" s="5" t="s">
-        <v>5682</v>
+        <v>5683</v>
       </c>
     </row>
     <row r="3057" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3057" s="3" t="s">
-        <v>5683</v>
+        <v>5684</v>
       </c>
       <c r="B3057" s="5" t="s">
-        <v>5684</v>
+        <v>5685</v>
       </c>
     </row>
     <row r="3058" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3058" s="3" t="s">
-        <v>5685</v>
+        <v>5686</v>
       </c>
       <c r="B3058" s="5" t="s">
-        <v>5686</v>
+        <v>5687</v>
       </c>
     </row>
     <row r="3059" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3059" s="3" t="s">
-        <v>5687</v>
+        <v>5688</v>
       </c>
       <c r="B3059" s="5" t="s">
-        <v>5688</v>
+        <v>5689</v>
       </c>
     </row>
     <row r="3060" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3060" s="9" t="s">
-        <v>5887</v>
+        <v>5888</v>
       </c>
       <c r="B3060" s="5" t="s">
-        <v>5689</v>
+        <v>5690</v>
       </c>
     </row>
     <row r="3061" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3061" s="3" t="s">
-        <v>5690</v>
+        <v>5691</v>
       </c>
       <c r="B3061" s="5" t="s">
-        <v>5691</v>
+        <v>5692</v>
       </c>
     </row>
     <row r="3062" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3062" s="3" t="s">
-        <v>5692</v>
+        <v>5693</v>
       </c>
       <c r="B3062" s="5" t="s">
-        <v>5693</v>
+        <v>5694</v>
       </c>
     </row>
     <row r="3063" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3063" s="3" t="s">
-        <v>5694</v>
+        <v>5695</v>
       </c>
       <c r="B3063" s="5" t="s">
-        <v>5695</v>
+        <v>5696</v>
       </c>
     </row>
     <row r="3064" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3064" s="3" t="s">
-        <v>5696</v>
+        <v>5697</v>
       </c>
       <c r="B3064" s="5" t="s">
-        <v>5697</v>
+        <v>5698</v>
       </c>
     </row>
     <row r="3065" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3065" s="3" t="s">
-        <v>5698</v>
+        <v>5699</v>
       </c>
       <c r="B3065" s="5" t="s">
-        <v>5699</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="3066" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3066" s="3" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="B3066" s="5" t="s">
-        <v>5701</v>
+        <v>5702</v>
       </c>
     </row>
     <row r="3067" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3067" s="3" t="s">
-        <v>5702</v>
+        <v>5703</v>
       </c>
       <c r="B3067" s="5" t="s">
-        <v>5703</v>
+        <v>5704</v>
       </c>
     </row>
     <row r="3068" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3068" s="3" t="s">
-        <v>5704</v>
+        <v>5705</v>
       </c>
       <c r="B3068" s="5" t="s">
-        <v>5854</v>
+        <v>5855</v>
       </c>
     </row>
     <row r="3069" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3069" s="3" t="s">
-        <v>5705</v>
+        <v>5706</v>
       </c>
       <c r="B3069" s="5" t="s">
-        <v>5706</v>
+        <v>5707</v>
       </c>
     </row>
     <row r="3070" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3070" s="3" t="s">
-        <v>5707</v>
+        <v>5708</v>
       </c>
       <c r="B3070" s="5" t="s">
-        <v>5708</v>
+        <v>5709</v>
       </c>
     </row>
     <row r="3071" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3071" s="3" t="s">
-        <v>5709</v>
+        <v>5710</v>
       </c>
       <c r="B3071" s="5" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
     </row>
     <row r="3072" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3072" s="3" t="s">
-        <v>5711</v>
+        <v>5712</v>
       </c>
       <c r="B3072" s="5" t="s">
-        <v>5712</v>
+        <v>5713</v>
       </c>
     </row>
     <row r="3073" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3073" s="3" t="s">
-        <v>5713</v>
+        <v>5714</v>
       </c>
       <c r="B3073" s="5" t="s">
-        <v>5714</v>
+        <v>5715</v>
       </c>
     </row>
     <row r="3074" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3074" s="3" t="s">
-        <v>5715</v>
+        <v>5716</v>
       </c>
       <c r="B3074" s="5" t="s">
-        <v>5716</v>
+        <v>5717</v>
       </c>
     </row>
     <row r="3075" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3075" s="3" t="s">
-        <v>5717</v>
+        <v>5718</v>
       </c>
       <c r="B3075" s="5" t="s">
-        <v>5718</v>
+        <v>5719</v>
       </c>
     </row>
     <row r="3076" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3076" s="3" t="s">
-        <v>5719</v>
+        <v>5720</v>
       </c>
       <c r="B3076" s="5" t="s">
-        <v>5720</v>
+        <v>5721</v>
       </c>
     </row>
     <row r="3077" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3077" s="3" t="s">
-        <v>5721</v>
+        <v>5722</v>
       </c>
       <c r="B3077" s="5" t="s">
-        <v>5722</v>
+        <v>5723</v>
       </c>
     </row>
     <row r="3078" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3078" s="3" t="s">
-        <v>5723</v>
+        <v>5724</v>
       </c>
       <c r="B3078" s="5" t="s">
-        <v>5724</v>
+        <v>5725</v>
       </c>
     </row>
   </sheetData>

--- a/englisch.xlsx
+++ b/englisch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nutzer\Desktop\Vokabellernspiel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EF111A2-80EB-4CDF-9F8B-39CA63F095EB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E3A18D-5881-467C-9A75-7C9AC9588E8C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="8655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17070,9 +17070,6 @@
     <t>Du siehst europäisch aus.</t>
   </si>
   <si>
-    <t>Das ist sehr deutsch.</t>
-  </si>
-  <si>
     <t>That is very german.</t>
   </si>
   <si>
@@ -17929,6 +17926,9 @@
   </si>
   <si>
     <t>Ihr (formell Du)</t>
+  </si>
+  <si>
+    <t>Das ist sehr schweiz.</t>
   </si>
 </sst>
 </file>
@@ -19067,7 +19067,7 @@
         <v>174</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>5751</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -19080,7 +19080,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>5963</v>
+        <v>5962</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>177</v>
@@ -19112,7 +19112,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>5964</v>
+        <v>5963</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>184</v>
@@ -19120,7 +19120,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>5965</v>
+        <v>5964</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>185</v>
@@ -19152,7 +19152,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>5966</v>
+        <v>5965</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>191</v>
@@ -19163,7 +19163,7 @@
         <v>32</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>5961</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -19184,7 +19184,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>5967</v>
+        <v>5966</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>195</v>
@@ -19192,7 +19192,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>5968</v>
+        <v>5967</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>196</v>
@@ -19235,7 +19235,7 @@
         <v>205</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>5726</v>
+        <v>5725</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -19251,7 +19251,7 @@
         <v>208</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>5856</v>
+        <v>5855</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -19283,7 +19283,7 @@
         <v>215</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>5727</v>
+        <v>5726</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -19291,7 +19291,7 @@
         <v>216</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>5728</v>
+        <v>5727</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -19419,7 +19419,7 @@
         <v>247</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>5960</v>
+        <v>5959</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -19443,7 +19443,7 @@
         <v>252</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>5729</v>
+        <v>5728</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -19507,12 +19507,12 @@
         <v>267</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>5730</v>
+        <v>5729</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>5750</v>
+        <v>5749</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>268</v>
@@ -19523,7 +19523,7 @@
         <v>269</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>5752</v>
+        <v>5751</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -19587,7 +19587,7 @@
         <v>284</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>5959</v>
+        <v>5958</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -19603,7 +19603,7 @@
         <v>287</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>5731</v>
+        <v>5730</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -19627,7 +19627,7 @@
         <v>292</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>5732</v>
+        <v>5731</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -19635,7 +19635,7 @@
         <v>293</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>5753</v>
+        <v>5752</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -19643,7 +19643,7 @@
         <v>294</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>5733</v>
+        <v>5732</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -19691,7 +19691,7 @@
         <v>305</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>5962</v>
+        <v>5961</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -19739,7 +19739,7 @@
         <v>316</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>5734</v>
+        <v>5733</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -19867,7 +19867,7 @@
         <v>346</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>5735</v>
+        <v>5734</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -19899,7 +19899,7 @@
         <v>353</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>5736</v>
+        <v>5735</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -20403,7 +20403,7 @@
         <v>474</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>5754</v>
+        <v>5753</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
@@ -20475,7 +20475,7 @@
         <v>491</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>5755</v>
+        <v>5754</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
@@ -20619,7 +20619,7 @@
         <v>524</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>5756</v>
+        <v>5755</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
@@ -21155,7 +21155,7 @@
         <v>653</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>5757</v>
+        <v>5756</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
@@ -21283,7 +21283,7 @@
         <v>683</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>5737</v>
+        <v>5736</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
@@ -21427,7 +21427,7 @@
         <v>718</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>5758</v>
+        <v>5757</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
@@ -21459,7 +21459,7 @@
         <v>725</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>5759</v>
+        <v>5758</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
@@ -21483,7 +21483,7 @@
         <v>730</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>5760</v>
+        <v>5759</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
@@ -21547,7 +21547,7 @@
         <v>745</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>5761</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
@@ -21555,7 +21555,7 @@
         <v>746</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>5857</v>
+        <v>5856</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
@@ -21595,7 +21595,7 @@
         <v>755</v>
       </c>
       <c r="B404" s="5" t="s">
-        <v>5858</v>
+        <v>5857</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
@@ -21603,7 +21603,7 @@
         <v>756</v>
       </c>
       <c r="B405" s="5" t="s">
-        <v>5762</v>
+        <v>5761</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
@@ -21611,7 +21611,7 @@
         <v>757</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>5763</v>
+        <v>5762</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
@@ -21627,7 +21627,7 @@
         <v>760</v>
       </c>
       <c r="B408" s="5" t="s">
-        <v>5764</v>
+        <v>5763</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
@@ -21667,7 +21667,7 @@
         <v>769</v>
       </c>
       <c r="B413" s="5" t="s">
-        <v>5738</v>
+        <v>5737</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
@@ -21675,7 +21675,7 @@
         <v>770</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>5739</v>
+        <v>5738</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
@@ -21747,7 +21747,7 @@
         <v>787</v>
       </c>
       <c r="B423" s="5" t="s">
-        <v>5740</v>
+        <v>5739</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
@@ -21787,7 +21787,7 @@
         <v>796</v>
       </c>
       <c r="B428" s="5" t="s">
-        <v>5741</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
@@ -22131,7 +22131,7 @@
         <v>862</v>
       </c>
       <c r="B471" s="5" t="s">
-        <v>5765</v>
+        <v>5764</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.25">
@@ -22203,7 +22203,7 @@
         <v>879</v>
       </c>
       <c r="B480" s="5" t="s">
-        <v>5742</v>
+        <v>5741</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.25">
@@ -22624,7 +22624,7 @@
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>5889</v>
+        <v>5888</v>
       </c>
       <c r="B533" s="5" t="s">
         <v>978</v>
@@ -22640,15 +22640,15 @@
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>5890</v>
+        <v>5889</v>
       </c>
       <c r="B535" s="5" t="s">
-        <v>5766</v>
+        <v>5765</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
-        <v>5891</v>
+        <v>5890</v>
       </c>
       <c r="B536" s="5" t="s">
         <v>981</v>
@@ -23299,7 +23299,7 @@
         <v>1137</v>
       </c>
       <c r="B617" s="5" t="s">
-        <v>5767</v>
+        <v>5766</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.25">
@@ -23355,7 +23355,7 @@
         <v>1150</v>
       </c>
       <c r="B624" s="5" t="s">
-        <v>5768</v>
+        <v>5767</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.25">
@@ -23363,7 +23363,7 @@
         <v>1151</v>
       </c>
       <c r="B625" s="5" t="s">
-        <v>5769</v>
+        <v>5768</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.25">
@@ -23571,7 +23571,7 @@
         <v>1202</v>
       </c>
       <c r="B651" s="5" t="s">
-        <v>5770</v>
+        <v>5769</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.25">
@@ -23851,7 +23851,7 @@
         <v>1269</v>
       </c>
       <c r="B686" s="5" t="s">
-        <v>5743</v>
+        <v>5742</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.25">
@@ -23915,7 +23915,7 @@
         <v>1284</v>
       </c>
       <c r="B694" s="5" t="s">
-        <v>5744</v>
+        <v>5743</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.25">
@@ -23971,7 +23971,7 @@
         <v>1297</v>
       </c>
       <c r="B701" s="5" t="s">
-        <v>5859</v>
+        <v>5858</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.25">
@@ -23979,7 +23979,7 @@
         <v>1298</v>
       </c>
       <c r="B702" s="5" t="s">
-        <v>5860</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.25">
@@ -23995,7 +23995,7 @@
         <v>1301</v>
       </c>
       <c r="B704" s="5" t="s">
-        <v>5745</v>
+        <v>5744</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.25">
@@ -24163,7 +24163,7 @@
         <v>1342</v>
       </c>
       <c r="B725" s="5" t="s">
-        <v>5861</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.25">
@@ -24227,7 +24227,7 @@
         <v>1357</v>
       </c>
       <c r="B733" s="5" t="s">
-        <v>5771</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.25">
@@ -24283,7 +24283,7 @@
         <v>1370</v>
       </c>
       <c r="B740" s="5" t="s">
-        <v>5772</v>
+        <v>5771</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.25">
@@ -24355,12 +24355,12 @@
         <v>1387</v>
       </c>
       <c r="B749" s="5" t="s">
-        <v>5773</v>
+        <v>5772</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A750" s="7" t="s">
-        <v>5880</v>
+        <v>5879</v>
       </c>
       <c r="B750" s="5" t="s">
         <v>1388</v>
@@ -24411,7 +24411,7 @@
         <v>1397</v>
       </c>
       <c r="B756" s="5" t="s">
-        <v>5774</v>
+        <v>5773</v>
       </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.25">
@@ -24443,7 +24443,7 @@
         <v>1404</v>
       </c>
       <c r="B760" s="5" t="s">
-        <v>5775</v>
+        <v>5774</v>
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.25">
@@ -24451,7 +24451,7 @@
         <v>1405</v>
       </c>
       <c r="B761" s="5" t="s">
-        <v>5776</v>
+        <v>5775</v>
       </c>
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.25">
@@ -24467,12 +24467,12 @@
         <v>1408</v>
       </c>
       <c r="B763" s="5" t="s">
-        <v>5777</v>
+        <v>5776</v>
       </c>
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A764" s="7" t="s">
-        <v>5881</v>
+        <v>5880</v>
       </c>
       <c r="B764" s="5" t="s">
         <v>1409</v>
@@ -24499,7 +24499,7 @@
         <v>347</v>
       </c>
       <c r="B767" s="5" t="s">
-        <v>5778</v>
+        <v>5777</v>
       </c>
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.25">
@@ -24579,7 +24579,7 @@
         <v>1432</v>
       </c>
       <c r="B777" s="5" t="s">
-        <v>5779</v>
+        <v>5778</v>
       </c>
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.25">
@@ -24651,7 +24651,7 @@
         <v>1449</v>
       </c>
       <c r="B786" s="5" t="s">
-        <v>5746</v>
+        <v>5745</v>
       </c>
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.25">
@@ -24899,7 +24899,7 @@
         <v>1510</v>
       </c>
       <c r="B817" s="5" t="s">
-        <v>5780</v>
+        <v>5779</v>
       </c>
     </row>
     <row r="818" spans="1:2" x14ac:dyDescent="0.25">
@@ -24931,7 +24931,7 @@
         <v>1517</v>
       </c>
       <c r="B821" s="5" t="s">
-        <v>5781</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="822" spans="1:2" x14ac:dyDescent="0.25">
@@ -24979,7 +24979,7 @@
         <v>1528</v>
       </c>
       <c r="B827" s="5" t="s">
-        <v>5862</v>
+        <v>5861</v>
       </c>
     </row>
     <row r="828" spans="1:2" x14ac:dyDescent="0.25">
@@ -24995,7 +24995,7 @@
         <v>1284</v>
       </c>
       <c r="B829" s="5" t="s">
-        <v>5863</v>
+        <v>5862</v>
       </c>
     </row>
     <row r="830" spans="1:2" x14ac:dyDescent="0.25">
@@ -25003,7 +25003,7 @@
         <v>1531</v>
       </c>
       <c r="B830" s="5" t="s">
-        <v>5864</v>
+        <v>5863</v>
       </c>
     </row>
     <row r="831" spans="1:2" x14ac:dyDescent="0.25">
@@ -25163,7 +25163,7 @@
         <v>1570</v>
       </c>
       <c r="B850" s="5" t="s">
-        <v>5865</v>
+        <v>5864</v>
       </c>
     </row>
     <row r="851" spans="1:2" x14ac:dyDescent="0.25">
@@ -25203,7 +25203,7 @@
         <v>1578</v>
       </c>
       <c r="B855" s="5" t="s">
-        <v>5782</v>
+        <v>5781</v>
       </c>
     </row>
     <row r="856" spans="1:2" x14ac:dyDescent="0.25">
@@ -25227,7 +25227,7 @@
         <v>1583</v>
       </c>
       <c r="B858" s="5" t="s">
-        <v>5783</v>
+        <v>5782</v>
       </c>
     </row>
     <row r="859" spans="1:2" x14ac:dyDescent="0.25">
@@ -25299,7 +25299,7 @@
         <v>1600</v>
       </c>
       <c r="B867" s="5" t="s">
-        <v>5747</v>
+        <v>5746</v>
       </c>
     </row>
     <row r="868" spans="1:2" x14ac:dyDescent="0.25">
@@ -25411,7 +25411,7 @@
         <v>1626</v>
       </c>
       <c r="B881" s="5" t="s">
-        <v>5784</v>
+        <v>5783</v>
       </c>
     </row>
     <row r="882" spans="1:2" x14ac:dyDescent="0.25">
@@ -25443,7 +25443,7 @@
         <v>1633</v>
       </c>
       <c r="B885" s="5" t="s">
-        <v>5785</v>
+        <v>5784</v>
       </c>
     </row>
     <row r="886" spans="1:2" x14ac:dyDescent="0.25">
@@ -25467,7 +25467,7 @@
         <v>1636</v>
       </c>
       <c r="B888" s="5" t="s">
-        <v>5786</v>
+        <v>5785</v>
       </c>
     </row>
     <row r="889" spans="1:2" x14ac:dyDescent="0.25">
@@ -25611,7 +25611,7 @@
         <v>1669</v>
       </c>
       <c r="B906" s="5" t="s">
-        <v>5787</v>
+        <v>5786</v>
       </c>
     </row>
     <row r="907" spans="1:2" x14ac:dyDescent="0.25">
@@ -25675,7 +25675,7 @@
         <v>1684</v>
       </c>
       <c r="B914" s="5" t="s">
-        <v>5788</v>
+        <v>5787</v>
       </c>
     </row>
     <row r="915" spans="1:2" x14ac:dyDescent="0.25">
@@ -25907,7 +25907,7 @@
         <v>1740</v>
       </c>
       <c r="B943" s="5" t="s">
-        <v>5789</v>
+        <v>5788</v>
       </c>
     </row>
     <row r="944" spans="1:2" x14ac:dyDescent="0.25">
@@ -25931,7 +25931,7 @@
         <v>1745</v>
       </c>
       <c r="B946" s="5" t="s">
-        <v>5790</v>
+        <v>5789</v>
       </c>
     </row>
     <row r="947" spans="1:2" x14ac:dyDescent="0.25">
@@ -26651,7 +26651,7 @@
         <v>1922</v>
       </c>
       <c r="B1036" s="5" t="s">
-        <v>5791</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="1037" spans="1:2" x14ac:dyDescent="0.25">
@@ -27040,7 +27040,7 @@
     </row>
     <row r="1085" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1085" s="2" t="s">
-        <v>5892</v>
+        <v>5891</v>
       </c>
       <c r="B1085" s="5" t="s">
         <v>2009</v>
@@ -27056,7 +27056,7 @@
     </row>
     <row r="1087" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1087" s="2" t="s">
-        <v>5893</v>
+        <v>5892</v>
       </c>
       <c r="B1087" s="5" t="s">
         <v>2012</v>
@@ -27835,7 +27835,7 @@
         <v>2202</v>
       </c>
       <c r="B1184" s="5" t="s">
-        <v>5792</v>
+        <v>5791</v>
       </c>
     </row>
     <row r="1185" spans="1:2" x14ac:dyDescent="0.25">
@@ -27899,7 +27899,7 @@
         <v>2217</v>
       </c>
       <c r="B1192" s="5" t="s">
-        <v>5793</v>
+        <v>5792</v>
       </c>
     </row>
     <row r="1193" spans="1:2" x14ac:dyDescent="0.25">
@@ -27936,7 +27936,7 @@
     </row>
     <row r="1197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1197" s="7" t="s">
-        <v>5882</v>
+        <v>5881</v>
       </c>
       <c r="B1197" s="5" t="s">
         <v>2226</v>
@@ -28059,7 +28059,7 @@
         <v>2255</v>
       </c>
       <c r="B1212" s="8" t="s">
-        <v>5794</v>
+        <v>5793</v>
       </c>
     </row>
     <row r="1213" spans="1:2" x14ac:dyDescent="0.25">
@@ -28155,7 +28155,7 @@
         <v>2278</v>
       </c>
       <c r="B1224" s="5" t="s">
-        <v>5795</v>
+        <v>5794</v>
       </c>
     </row>
     <row r="1225" spans="1:2" x14ac:dyDescent="0.25">
@@ -28331,7 +28331,7 @@
         <v>2321</v>
       </c>
       <c r="B1246" s="5" t="s">
-        <v>5796</v>
+        <v>5795</v>
       </c>
     </row>
     <row r="1247" spans="1:2" x14ac:dyDescent="0.25">
@@ -28544,7 +28544,7 @@
     </row>
     <row r="1273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1273" s="7" t="s">
-        <v>5883</v>
+        <v>5882</v>
       </c>
       <c r="B1273" s="5" t="s">
         <v>2374</v>
@@ -28555,7 +28555,7 @@
         <v>2375</v>
       </c>
       <c r="B1274" s="5" t="s">
-        <v>5797</v>
+        <v>5796</v>
       </c>
     </row>
     <row r="1275" spans="1:2" x14ac:dyDescent="0.25">
@@ -28619,7 +28619,7 @@
         <v>2390</v>
       </c>
       <c r="B1282" s="5" t="s">
-        <v>5866</v>
+        <v>5865</v>
       </c>
     </row>
     <row r="1283" spans="1:2" x14ac:dyDescent="0.25">
@@ -28995,7 +28995,7 @@
         <v>2483</v>
       </c>
       <c r="B1329" s="5" t="s">
-        <v>5798</v>
+        <v>5797</v>
       </c>
     </row>
     <row r="1330" spans="1:2" x14ac:dyDescent="0.25">
@@ -29451,7 +29451,7 @@
         <v>2592</v>
       </c>
       <c r="B1386" s="5" t="s">
-        <v>5799</v>
+        <v>5798</v>
       </c>
     </row>
     <row r="1387" spans="1:2" x14ac:dyDescent="0.25">
@@ -30288,7 +30288,7 @@
     </row>
     <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1491" s="2" t="s">
-        <v>5955</v>
+        <v>5954</v>
       </c>
       <c r="B1491" s="5" t="s">
         <v>2795</v>
@@ -30331,7 +30331,7 @@
         <v>2804</v>
       </c>
       <c r="B1496" s="5" t="s">
-        <v>5800</v>
+        <v>5799</v>
       </c>
     </row>
     <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
@@ -30379,7 +30379,7 @@
         <v>2813</v>
       </c>
       <c r="B1502" s="5" t="s">
-        <v>5801</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
@@ -30395,7 +30395,7 @@
         <v>2816</v>
       </c>
       <c r="B1504" s="5" t="s">
-        <v>5802</v>
+        <v>5801</v>
       </c>
     </row>
     <row r="1505" spans="1:2" x14ac:dyDescent="0.25">
@@ -30416,7 +30416,7 @@
     </row>
     <row r="1507" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1507" s="1" t="s">
-        <v>5956</v>
+        <v>5955</v>
       </c>
       <c r="B1507" s="5" t="s">
         <v>2821</v>
@@ -30427,7 +30427,7 @@
         <v>2822</v>
       </c>
       <c r="B1508" s="5" t="s">
-        <v>5803</v>
+        <v>5802</v>
       </c>
     </row>
     <row r="1509" spans="1:2" x14ac:dyDescent="0.25">
@@ -30931,7 +30931,7 @@
         <v>2935</v>
       </c>
       <c r="B1571" s="5" t="s">
-        <v>5867</v>
+        <v>5866</v>
       </c>
     </row>
     <row r="1572" spans="1:2" x14ac:dyDescent="0.25">
@@ -30979,7 +30979,7 @@
         <v>2946</v>
       </c>
       <c r="B1577" s="5" t="s">
-        <v>5868</v>
+        <v>5867</v>
       </c>
     </row>
     <row r="1578" spans="1:2" x14ac:dyDescent="0.25">
@@ -31019,7 +31019,7 @@
         <v>2955</v>
       </c>
       <c r="B1582" s="5" t="s">
-        <v>5748</v>
+        <v>5747</v>
       </c>
     </row>
     <row r="1583" spans="1:2" x14ac:dyDescent="0.25">
@@ -31035,7 +31035,7 @@
         <v>2958</v>
       </c>
       <c r="B1584" s="5" t="s">
-        <v>5804</v>
+        <v>5803</v>
       </c>
     </row>
     <row r="1585" spans="1:2" x14ac:dyDescent="0.25">
@@ -31259,7 +31259,7 @@
         <v>3013</v>
       </c>
       <c r="B1612" s="5" t="s">
-        <v>5749</v>
+        <v>5748</v>
       </c>
     </row>
     <row r="1613" spans="1:2" x14ac:dyDescent="0.25">
@@ -31299,7 +31299,7 @@
         <v>3022</v>
       </c>
       <c r="B1617" s="5" t="s">
-        <v>5805</v>
+        <v>5804</v>
       </c>
     </row>
     <row r="1618" spans="1:2" x14ac:dyDescent="0.25">
@@ -31395,7 +31395,7 @@
         <v>3045</v>
       </c>
       <c r="B1629" s="5" t="s">
-        <v>5806</v>
+        <v>5805</v>
       </c>
     </row>
     <row r="1630" spans="1:2" x14ac:dyDescent="0.25">
@@ -31419,7 +31419,7 @@
         <v>3050</v>
       </c>
       <c r="B1632" s="5" t="s">
-        <v>5807</v>
+        <v>5806</v>
       </c>
     </row>
     <row r="1633" spans="1:2" x14ac:dyDescent="0.25">
@@ -31432,7 +31432,7 @@
     </row>
     <row r="1634" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1634" s="9" t="s">
-        <v>5884</v>
+        <v>5883</v>
       </c>
       <c r="B1634" s="5" t="s">
         <v>3053</v>
@@ -31475,7 +31475,7 @@
         <v>3062</v>
       </c>
       <c r="B1639" s="5" t="s">
-        <v>5869</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="1640" spans="1:2" x14ac:dyDescent="0.25">
@@ -31531,7 +31531,7 @@
         <v>3075</v>
       </c>
       <c r="B1646" s="5" t="s">
-        <v>5808</v>
+        <v>5807</v>
       </c>
     </row>
     <row r="1647" spans="1:2" x14ac:dyDescent="0.25">
@@ -31659,7 +31659,7 @@
         <v>3106</v>
       </c>
       <c r="B1662" s="5" t="s">
-        <v>5809</v>
+        <v>5808</v>
       </c>
     </row>
     <row r="1663" spans="1:2" x14ac:dyDescent="0.25">
@@ -31843,7 +31843,7 @@
         <v>3151</v>
       </c>
       <c r="B1685" s="5" t="s">
-        <v>5810</v>
+        <v>5809</v>
       </c>
     </row>
     <row r="1686" spans="1:2" x14ac:dyDescent="0.25">
@@ -31963,7 +31963,7 @@
         <v>3180</v>
       </c>
       <c r="B1700" s="5" t="s">
-        <v>5811</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="1701" spans="1:2" x14ac:dyDescent="0.25">
@@ -32059,7 +32059,7 @@
         <v>3203</v>
       </c>
       <c r="B1712" s="5" t="s">
-        <v>5812</v>
+        <v>5811</v>
       </c>
     </row>
     <row r="1713" spans="1:2" x14ac:dyDescent="0.25">
@@ -32075,7 +32075,7 @@
         <v>3206</v>
       </c>
       <c r="B1714" s="5" t="s">
-        <v>5813</v>
+        <v>5812</v>
       </c>
     </row>
     <row r="1715" spans="1:2" x14ac:dyDescent="0.25">
@@ -32131,7 +32131,7 @@
         <v>3219</v>
       </c>
       <c r="B1721" s="5" t="s">
-        <v>5814</v>
+        <v>5813</v>
       </c>
     </row>
     <row r="1722" spans="1:2" x14ac:dyDescent="0.25">
@@ -32139,7 +32139,7 @@
         <v>3220</v>
       </c>
       <c r="B1722" s="5" t="s">
-        <v>5815</v>
+        <v>5814</v>
       </c>
     </row>
     <row r="1723" spans="1:2" x14ac:dyDescent="0.25">
@@ -32219,7 +32219,7 @@
         <v>3239</v>
       </c>
       <c r="B1732" s="5" t="s">
-        <v>5816</v>
+        <v>5815</v>
       </c>
     </row>
     <row r="1733" spans="1:2" x14ac:dyDescent="0.25">
@@ -32856,7 +32856,7 @@
     </row>
     <row r="1812" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1812" s="2" t="s">
-        <v>5894</v>
+        <v>5893</v>
       </c>
       <c r="B1812" s="5" t="s">
         <v>3372</v>
@@ -32872,7 +32872,7 @@
     </row>
     <row r="1814" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1814" s="2" t="s">
-        <v>5957</v>
+        <v>5956</v>
       </c>
       <c r="B1814" s="5" t="s">
         <v>3375</v>
@@ -32928,7 +32928,7 @@
     </row>
     <row r="1821" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1821" s="2" t="s">
-        <v>5895</v>
+        <v>5894</v>
       </c>
       <c r="B1821" s="5" t="s">
         <v>3388</v>
@@ -32995,7 +32995,7 @@
         <v>3403</v>
       </c>
       <c r="B1829" s="5" t="s">
-        <v>5817</v>
+        <v>5816</v>
       </c>
     </row>
     <row r="1830" spans="1:2" x14ac:dyDescent="0.25">
@@ -33035,7 +33035,7 @@
         <v>3412</v>
       </c>
       <c r="B1834" s="5" t="s">
-        <v>5870</v>
+        <v>5869</v>
       </c>
     </row>
     <row r="1835" spans="1:2" x14ac:dyDescent="0.25">
@@ -33771,7 +33771,7 @@
         <v>3577</v>
       </c>
       <c r="B1926" s="5" t="s">
-        <v>5818</v>
+        <v>5817</v>
       </c>
     </row>
     <row r="1927" spans="1:2" x14ac:dyDescent="0.25">
@@ -33907,7 +33907,7 @@
         <v>3610</v>
       </c>
       <c r="B1943" s="5" t="s">
-        <v>5819</v>
+        <v>5818</v>
       </c>
     </row>
     <row r="1944" spans="1:2" x14ac:dyDescent="0.25">
@@ -33987,7 +33987,7 @@
         <v>3629</v>
       </c>
       <c r="B1953" s="5" t="s">
-        <v>5820</v>
+        <v>5819</v>
       </c>
     </row>
     <row r="1954" spans="1:2" x14ac:dyDescent="0.25">
@@ -34043,7 +34043,7 @@
         <v>3642</v>
       </c>
       <c r="B1960" s="5" t="s">
-        <v>5821</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="1961" spans="1:2" x14ac:dyDescent="0.25">
@@ -34259,7 +34259,7 @@
         <v>3695</v>
       </c>
       <c r="B1987" s="5" t="s">
-        <v>5822</v>
+        <v>5821</v>
       </c>
     </row>
     <row r="1988" spans="1:2" x14ac:dyDescent="0.25">
@@ -34296,10 +34296,10 @@
     </row>
     <row r="1992" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1992" s="7" t="s">
+        <v>5884</v>
+      </c>
+      <c r="B1992" s="5" t="s">
         <v>5885</v>
-      </c>
-      <c r="B1992" s="5" t="s">
-        <v>5886</v>
       </c>
     </row>
     <row r="1993" spans="1:2" x14ac:dyDescent="0.25">
@@ -34392,7 +34392,7 @@
     </row>
     <row r="2004" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2004" s="7" t="s">
-        <v>5887</v>
+        <v>5886</v>
       </c>
       <c r="B2004" s="5" t="s">
         <v>3726</v>
@@ -34563,7 +34563,7 @@
         <v>3767</v>
       </c>
       <c r="B2025" s="5" t="s">
-        <v>5823</v>
+        <v>5822</v>
       </c>
     </row>
     <row r="2026" spans="1:2" x14ac:dyDescent="0.25">
@@ -34643,7 +34643,7 @@
         <v>3784</v>
       </c>
       <c r="B2035" s="5" t="s">
-        <v>5871</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="2036" spans="1:2" x14ac:dyDescent="0.25">
@@ -34675,7 +34675,7 @@
         <v>3791</v>
       </c>
       <c r="B2039" s="5" t="s">
-        <v>5824</v>
+        <v>5823</v>
       </c>
     </row>
     <row r="2040" spans="1:2" x14ac:dyDescent="0.25">
@@ -34755,7 +34755,7 @@
         <v>3810</v>
       </c>
       <c r="B2049" s="5" t="s">
-        <v>5872</v>
+        <v>5871</v>
       </c>
     </row>
     <row r="2050" spans="1:2" x14ac:dyDescent="0.25">
@@ -34795,7 +34795,7 @@
         <v>3819</v>
       </c>
       <c r="B2054" s="5" t="s">
-        <v>5825</v>
+        <v>5824</v>
       </c>
     </row>
     <row r="2055" spans="1:2" x14ac:dyDescent="0.25">
@@ -35043,7 +35043,7 @@
         <v>3880</v>
       </c>
       <c r="B2085" s="5" t="s">
-        <v>5826</v>
+        <v>5825</v>
       </c>
     </row>
     <row r="2086" spans="1:2" x14ac:dyDescent="0.25">
@@ -35227,7 +35227,7 @@
         <v>3925</v>
       </c>
       <c r="B2108" s="5" t="s">
-        <v>5827</v>
+        <v>5826</v>
       </c>
     </row>
     <row r="2109" spans="1:2" x14ac:dyDescent="0.25">
@@ -35424,7 +35424,7 @@
     </row>
     <row r="2133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2133" s="2" t="s">
-        <v>5896</v>
+        <v>5895</v>
       </c>
       <c r="B2133" s="5" t="s">
         <v>3971</v>
@@ -35432,7 +35432,7 @@
     </row>
     <row r="2134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2134" s="2" t="s">
-        <v>5897</v>
+        <v>5896</v>
       </c>
       <c r="B2134" s="5" t="s">
         <v>3972</v>
@@ -35504,7 +35504,7 @@
     </row>
     <row r="2143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2143" s="2" t="s">
-        <v>5898</v>
+        <v>5897</v>
       </c>
       <c r="B2143" s="5" t="s">
         <v>3989</v>
@@ -35520,7 +35520,7 @@
     </row>
     <row r="2145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2145" s="2" t="s">
-        <v>5899</v>
+        <v>5898</v>
       </c>
       <c r="B2145" s="5" t="s">
         <v>3992</v>
@@ -35795,7 +35795,7 @@
         <v>4052</v>
       </c>
       <c r="B2179" s="5" t="s">
-        <v>5828</v>
+        <v>5827</v>
       </c>
     </row>
     <row r="2180" spans="1:2" x14ac:dyDescent="0.25">
@@ -36107,7 +36107,7 @@
         <v>4129</v>
       </c>
       <c r="B2218" s="5" t="s">
-        <v>5829</v>
+        <v>5828</v>
       </c>
     </row>
     <row r="2219" spans="1:2" x14ac:dyDescent="0.25">
@@ -36203,7 +36203,7 @@
         <v>4152</v>
       </c>
       <c r="B2230" s="5" t="s">
-        <v>5830</v>
+        <v>5829</v>
       </c>
     </row>
     <row r="2231" spans="1:2" x14ac:dyDescent="0.25">
@@ -36283,7 +36283,7 @@
         <v>4171</v>
       </c>
       <c r="B2240" s="5" t="s">
-        <v>5831</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="2241" spans="1:2" x14ac:dyDescent="0.25">
@@ -36560,7 +36560,7 @@
     </row>
     <row r="2275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2275" s="2" t="s">
-        <v>5900</v>
+        <v>5899</v>
       </c>
       <c r="B2275" s="5" t="s">
         <v>4236</v>
@@ -36584,7 +36584,7 @@
     </row>
     <row r="2278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2278" s="2" t="s">
-        <v>5901</v>
+        <v>5900</v>
       </c>
       <c r="B2278" s="5" t="s">
         <v>4241</v>
@@ -36592,7 +36592,7 @@
     </row>
     <row r="2279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2279" s="2" t="s">
-        <v>5902</v>
+        <v>5901</v>
       </c>
       <c r="B2279" s="5" t="s">
         <v>4242</v>
@@ -36608,7 +36608,7 @@
     </row>
     <row r="2281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2281" s="2" t="s">
-        <v>5903</v>
+        <v>5902</v>
       </c>
       <c r="B2281" s="5" t="s">
         <v>4245</v>
@@ -36616,7 +36616,7 @@
     </row>
     <row r="2282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2282" s="2" t="s">
-        <v>5904</v>
+        <v>5903</v>
       </c>
       <c r="B2282" s="5" t="s">
         <v>4246</v>
@@ -37139,7 +37139,7 @@
         <v>4371</v>
       </c>
       <c r="B2347" s="5" t="s">
-        <v>5832</v>
+        <v>5831</v>
       </c>
     </row>
     <row r="2348" spans="1:2" x14ac:dyDescent="0.25">
@@ -37243,7 +37243,7 @@
         <v>4396</v>
       </c>
       <c r="B2360" s="5" t="s">
-        <v>5833</v>
+        <v>5832</v>
       </c>
     </row>
     <row r="2361" spans="1:2" x14ac:dyDescent="0.25">
@@ -37259,7 +37259,7 @@
         <v>4399</v>
       </c>
       <c r="B2362" s="5" t="s">
-        <v>5834</v>
+        <v>5833</v>
       </c>
     </row>
     <row r="2363" spans="1:2" x14ac:dyDescent="0.25">
@@ -37515,7 +37515,7 @@
         <v>4462</v>
       </c>
       <c r="B2394" s="5" t="s">
-        <v>5835</v>
+        <v>5834</v>
       </c>
     </row>
     <row r="2395" spans="1:2" x14ac:dyDescent="0.25">
@@ -37643,7 +37643,7 @@
         <v>4493</v>
       </c>
       <c r="B2410" s="5" t="s">
-        <v>5836</v>
+        <v>5835</v>
       </c>
     </row>
     <row r="2411" spans="1:2" x14ac:dyDescent="0.25">
@@ -37651,7 +37651,7 @@
         <v>4494</v>
       </c>
       <c r="B2411" s="5" t="s">
-        <v>5837</v>
+        <v>5836</v>
       </c>
     </row>
     <row r="2412" spans="1:2" x14ac:dyDescent="0.25">
@@ -37739,7 +37739,7 @@
         <v>4515</v>
       </c>
       <c r="B2422" s="5" t="s">
-        <v>5838</v>
+        <v>5837</v>
       </c>
     </row>
     <row r="2423" spans="1:2" x14ac:dyDescent="0.25">
@@ -37856,7 +37856,7 @@
     </row>
     <row r="2437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2437" s="2" t="s">
-        <v>5905</v>
+        <v>5904</v>
       </c>
       <c r="B2437" s="5" t="s">
         <v>4541</v>
@@ -37864,7 +37864,7 @@
     </row>
     <row r="2438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2438" s="2" t="s">
-        <v>5906</v>
+        <v>5905</v>
       </c>
       <c r="B2438" s="5" t="s">
         <v>4542</v>
@@ -38051,7 +38051,7 @@
         <v>4584</v>
       </c>
       <c r="B2461" s="5" t="s">
-        <v>5839</v>
+        <v>5838</v>
       </c>
     </row>
     <row r="2462" spans="1:2" x14ac:dyDescent="0.25">
@@ -38155,7 +38155,7 @@
         <v>4609</v>
       </c>
       <c r="B2474" s="5" t="s">
-        <v>5873</v>
+        <v>5872</v>
       </c>
     </row>
     <row r="2475" spans="1:2" x14ac:dyDescent="0.25">
@@ -38283,7 +38283,7 @@
         <v>4640</v>
       </c>
       <c r="B2490" s="5" t="s">
-        <v>5840</v>
+        <v>5839</v>
       </c>
     </row>
     <row r="2491" spans="1:2" x14ac:dyDescent="0.25">
@@ -38347,7 +38347,7 @@
         <v>4655</v>
       </c>
       <c r="B2498" s="5" t="s">
-        <v>5841</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="2499" spans="1:2" x14ac:dyDescent="0.25">
@@ -38379,7 +38379,7 @@
         <v>4662</v>
       </c>
       <c r="B2502" s="5" t="s">
-        <v>5874</v>
+        <v>5873</v>
       </c>
     </row>
     <row r="2503" spans="1:2" x14ac:dyDescent="0.25">
@@ -38443,7 +38443,7 @@
         <v>4677</v>
       </c>
       <c r="B2510" s="5" t="s">
-        <v>5842</v>
+        <v>5841</v>
       </c>
     </row>
     <row r="2511" spans="1:2" x14ac:dyDescent="0.25">
@@ -38587,7 +38587,7 @@
         <v>4710</v>
       </c>
       <c r="B2528" s="5" t="s">
-        <v>5843</v>
+        <v>5842</v>
       </c>
     </row>
     <row r="2529" spans="1:2" x14ac:dyDescent="0.25">
@@ -38699,7 +38699,7 @@
         <v>4737</v>
       </c>
       <c r="B2542" s="5" t="s">
-        <v>5844</v>
+        <v>5843</v>
       </c>
     </row>
     <row r="2543" spans="1:2" x14ac:dyDescent="0.25">
@@ -38771,7 +38771,7 @@
         <v>4753</v>
       </c>
       <c r="B2551" s="5" t="s">
-        <v>5875</v>
+        <v>5874</v>
       </c>
     </row>
     <row r="2552" spans="1:2" x14ac:dyDescent="0.25">
@@ -38915,7 +38915,7 @@
         <v>4787</v>
       </c>
       <c r="B2569" s="5" t="s">
-        <v>5876</v>
+        <v>5875</v>
       </c>
     </row>
     <row r="2570" spans="1:2" x14ac:dyDescent="0.25">
@@ -39075,7 +39075,7 @@
         <v>4823</v>
       </c>
       <c r="B2589" s="5" t="s">
-        <v>5877</v>
+        <v>5876</v>
       </c>
     </row>
     <row r="2590" spans="1:2" x14ac:dyDescent="0.25">
@@ -39235,7 +39235,7 @@
         <v>4862</v>
       </c>
       <c r="B2609" s="5" t="s">
-        <v>5845</v>
+        <v>5844</v>
       </c>
     </row>
     <row r="2610" spans="1:2" x14ac:dyDescent="0.25">
@@ -39331,7 +39331,7 @@
         <v>4885</v>
       </c>
       <c r="B2621" s="5" t="s">
-        <v>5846</v>
+        <v>5845</v>
       </c>
     </row>
     <row r="2622" spans="1:2" x14ac:dyDescent="0.25">
@@ -39443,7 +39443,7 @@
         <v>4912</v>
       </c>
       <c r="B2635" s="5" t="s">
-        <v>5847</v>
+        <v>5846</v>
       </c>
     </row>
     <row r="2636" spans="1:2" x14ac:dyDescent="0.25">
@@ -39624,7 +39624,7 @@
     </row>
     <row r="2658" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2658" s="2" t="s">
-        <v>5907</v>
+        <v>5906</v>
       </c>
       <c r="B2658" s="5" t="s">
         <v>4953</v>
@@ -39632,7 +39632,7 @@
     </row>
     <row r="2659" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2659" s="2" t="s">
-        <v>5908</v>
+        <v>5907</v>
       </c>
       <c r="B2659" s="5" t="s">
         <v>4954</v>
@@ -39747,7 +39747,7 @@
         <v>4981</v>
       </c>
       <c r="B2673" s="5" t="s">
-        <v>5848</v>
+        <v>5847</v>
       </c>
     </row>
     <row r="2674" spans="1:2" x14ac:dyDescent="0.25">
@@ -39824,7 +39824,7 @@
     </row>
     <row r="2683" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2683" s="2" t="s">
-        <v>5909</v>
+        <v>5908</v>
       </c>
       <c r="B2683" s="5" t="s">
         <v>5000</v>
@@ -39832,7 +39832,7 @@
     </row>
     <row r="2684" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2684" s="2" t="s">
-        <v>5910</v>
+        <v>5909</v>
       </c>
       <c r="B2684" s="5" t="s">
         <v>5001</v>
@@ -39840,7 +39840,7 @@
     </row>
     <row r="2685" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2685" s="2" t="s">
-        <v>5911</v>
+        <v>5910</v>
       </c>
       <c r="B2685" s="5" t="s">
         <v>5002</v>
@@ -39864,7 +39864,7 @@
     </row>
     <row r="2688" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2688" s="2" t="s">
-        <v>5912</v>
+        <v>5911</v>
       </c>
       <c r="B2688" s="5" t="s">
         <v>5007</v>
@@ -39872,7 +39872,7 @@
     </row>
     <row r="2689" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2689" s="2" t="s">
-        <v>5913</v>
+        <v>5912</v>
       </c>
       <c r="B2689" s="5" t="s">
         <v>5008</v>
@@ -39880,7 +39880,7 @@
     </row>
     <row r="2690" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2690" s="2" t="s">
-        <v>5914</v>
+        <v>5913</v>
       </c>
       <c r="B2690" s="5" t="s">
         <v>5009</v>
@@ -39888,7 +39888,7 @@
     </row>
     <row r="2691" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2691" s="2" t="s">
-        <v>5915</v>
+        <v>5914</v>
       </c>
       <c r="B2691" s="5" t="s">
         <v>5010</v>
@@ -39896,7 +39896,7 @@
     </row>
     <row r="2692" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2692" s="2" t="s">
-        <v>5916</v>
+        <v>5915</v>
       </c>
       <c r="B2692" s="5" t="s">
         <v>5011</v>
@@ -39904,7 +39904,7 @@
     </row>
     <row r="2693" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2693" s="2" t="s">
-        <v>5917</v>
+        <v>5916</v>
       </c>
       <c r="B2693" s="5" t="s">
         <v>5012</v>
@@ -39912,7 +39912,7 @@
     </row>
     <row r="2694" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2694" s="2" t="s">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="B2694" s="5" t="s">
         <v>5013</v>
@@ -39920,7 +39920,7 @@
     </row>
     <row r="2695" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2695" s="2" t="s">
-        <v>5919</v>
+        <v>5918</v>
       </c>
       <c r="B2695" s="5" t="s">
         <v>5014</v>
@@ -39936,7 +39936,7 @@
     </row>
     <row r="2697" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2697" s="2" t="s">
-        <v>5920</v>
+        <v>5919</v>
       </c>
       <c r="B2697" s="5" t="s">
         <v>5017</v>
@@ -39944,7 +39944,7 @@
     </row>
     <row r="2698" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2698" s="2" t="s">
-        <v>5921</v>
+        <v>5920</v>
       </c>
       <c r="B2698" s="5" t="s">
         <v>5018</v>
@@ -39952,7 +39952,7 @@
     </row>
     <row r="2699" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2699" s="2" t="s">
-        <v>5922</v>
+        <v>5921</v>
       </c>
       <c r="B2699" s="5" t="s">
         <v>5019</v>
@@ -39960,7 +39960,7 @@
     </row>
     <row r="2700" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2700" s="2" t="s">
-        <v>5923</v>
+        <v>5922</v>
       </c>
       <c r="B2700" s="5" t="s">
         <v>5020</v>
@@ -39968,7 +39968,7 @@
     </row>
     <row r="2701" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2701" s="2" t="s">
-        <v>5924</v>
+        <v>5923</v>
       </c>
       <c r="B2701" s="5" t="s">
         <v>5021</v>
@@ -39976,7 +39976,7 @@
     </row>
     <row r="2702" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2702" s="2" t="s">
-        <v>5925</v>
+        <v>5924</v>
       </c>
       <c r="B2702" s="5" t="s">
         <v>5022</v>
@@ -39984,7 +39984,7 @@
     </row>
     <row r="2703" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2703" s="2" t="s">
-        <v>5926</v>
+        <v>5925</v>
       </c>
       <c r="B2703" s="5" t="s">
         <v>5023</v>
@@ -39992,7 +39992,7 @@
     </row>
     <row r="2704" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2704" s="2" t="s">
-        <v>5927</v>
+        <v>5926</v>
       </c>
       <c r="B2704" s="5" t="s">
         <v>5024</v>
@@ -40000,7 +40000,7 @@
     </row>
     <row r="2705" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2705" s="2" t="s">
-        <v>5928</v>
+        <v>5927</v>
       </c>
       <c r="B2705" s="5" t="s">
         <v>5025</v>
@@ -40032,7 +40032,7 @@
     </row>
     <row r="2709" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2709" s="2" t="s">
-        <v>5929</v>
+        <v>5928</v>
       </c>
       <c r="B2709" s="5" t="s">
         <v>5032</v>
@@ -40040,7 +40040,7 @@
     </row>
     <row r="2710" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2710" s="2" t="s">
-        <v>5958</v>
+        <v>5957</v>
       </c>
       <c r="B2710" s="5" t="s">
         <v>5033</v>
@@ -40048,7 +40048,7 @@
     </row>
     <row r="2711" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2711" s="2" t="s">
-        <v>5930</v>
+        <v>5929</v>
       </c>
       <c r="B2711" s="5" t="s">
         <v>5034</v>
@@ -40056,7 +40056,7 @@
     </row>
     <row r="2712" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2712" s="2" t="s">
-        <v>5931</v>
+        <v>5930</v>
       </c>
       <c r="B2712" s="5" t="s">
         <v>5035</v>
@@ -40139,7 +40139,7 @@
         <v>5053</v>
       </c>
       <c r="B2722" s="5" t="s">
-        <v>5849</v>
+        <v>5848</v>
       </c>
     </row>
     <row r="2723" spans="1:2" x14ac:dyDescent="0.25">
@@ -40323,7 +40323,7 @@
         <v>5098</v>
       </c>
       <c r="B2745" s="5" t="s">
-        <v>5850</v>
+        <v>5849</v>
       </c>
     </row>
     <row r="2746" spans="1:2" x14ac:dyDescent="0.25">
@@ -40707,7 +40707,7 @@
         <v>5193</v>
       </c>
       <c r="B2793" s="5" t="s">
-        <v>5851</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="2794" spans="1:2" x14ac:dyDescent="0.25">
@@ -40939,7 +40939,7 @@
         <v>5250</v>
       </c>
       <c r="B2822" s="5" t="s">
-        <v>5852</v>
+        <v>5851</v>
       </c>
     </row>
     <row r="2823" spans="1:2" x14ac:dyDescent="0.25">
@@ -42032,7 +42032,7 @@
     </row>
     <row r="2959" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2959" s="2" t="s">
-        <v>5932</v>
+        <v>5931</v>
       </c>
       <c r="B2959" s="5" t="s">
         <v>5518</v>
@@ -42040,7 +42040,7 @@
     </row>
     <row r="2960" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2960" s="2" t="s">
-        <v>5933</v>
+        <v>5932</v>
       </c>
       <c r="B2960" s="5" t="s">
         <v>5519</v>
@@ -42048,7 +42048,7 @@
     </row>
     <row r="2961" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2961" s="2" t="s">
-        <v>5934</v>
+        <v>5933</v>
       </c>
       <c r="B2961" s="5" t="s">
         <v>5520</v>
@@ -42056,7 +42056,7 @@
     </row>
     <row r="2962" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2962" s="2" t="s">
-        <v>5935</v>
+        <v>5934</v>
       </c>
       <c r="B2962" s="5" t="s">
         <v>5521</v>
@@ -42064,7 +42064,7 @@
     </row>
     <row r="2963" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2963" s="2" t="s">
-        <v>5936</v>
+        <v>5935</v>
       </c>
       <c r="B2963" s="5" t="s">
         <v>5522</v>
@@ -42072,7 +42072,7 @@
     </row>
     <row r="2964" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2964" s="2" t="s">
-        <v>5937</v>
+        <v>5936</v>
       </c>
       <c r="B2964" s="5" t="s">
         <v>5523</v>
@@ -42080,7 +42080,7 @@
     </row>
     <row r="2965" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2965" s="2" t="s">
-        <v>5938</v>
+        <v>5937</v>
       </c>
       <c r="B2965" s="5" t="s">
         <v>5524</v>
@@ -42088,15 +42088,15 @@
     </row>
     <row r="2966" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2966" s="2" t="s">
-        <v>5939</v>
+        <v>5938</v>
       </c>
       <c r="B2966" s="5" t="s">
-        <v>5878</v>
+        <v>5877</v>
       </c>
     </row>
     <row r="2967" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2967" s="2" t="s">
-        <v>5940</v>
+        <v>5939</v>
       </c>
       <c r="B2967" s="5" t="s">
         <v>5525</v>
@@ -42104,7 +42104,7 @@
     </row>
     <row r="2968" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2968" s="2" t="s">
-        <v>5941</v>
+        <v>5940</v>
       </c>
       <c r="B2968" s="5" t="s">
         <v>5526</v>
@@ -42112,7 +42112,7 @@
     </row>
     <row r="2969" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2969" s="2" t="s">
-        <v>5942</v>
+        <v>5941</v>
       </c>
       <c r="B2969" s="5" t="s">
         <v>5527</v>
@@ -42120,7 +42120,7 @@
     </row>
     <row r="2970" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2970" s="2" t="s">
-        <v>5943</v>
+        <v>5942</v>
       </c>
       <c r="B2970" s="5" t="s">
         <v>5528</v>
@@ -42128,7 +42128,7 @@
     </row>
     <row r="2971" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2971" s="2" t="s">
-        <v>5944</v>
+        <v>5943</v>
       </c>
       <c r="B2971" s="5" t="s">
         <v>5529</v>
@@ -42136,7 +42136,7 @@
     </row>
     <row r="2972" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2972" s="2" t="s">
-        <v>5945</v>
+        <v>5944</v>
       </c>
       <c r="B2972" s="5" t="s">
         <v>5530</v>
@@ -42144,7 +42144,7 @@
     </row>
     <row r="2973" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2973" s="2" t="s">
-        <v>5946</v>
+        <v>5945</v>
       </c>
       <c r="B2973" s="5" t="s">
         <v>5531</v>
@@ -42152,7 +42152,7 @@
     </row>
     <row r="2974" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2974" s="2" t="s">
-        <v>5947</v>
+        <v>5946</v>
       </c>
       <c r="B2974" s="5" t="s">
         <v>5532</v>
@@ -42160,7 +42160,7 @@
     </row>
     <row r="2975" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2975" s="2" t="s">
-        <v>5948</v>
+        <v>5947</v>
       </c>
       <c r="B2975" s="5" t="s">
         <v>5533</v>
@@ -42168,7 +42168,7 @@
     </row>
     <row r="2976" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2976" s="2" t="s">
-        <v>5949</v>
+        <v>5948</v>
       </c>
       <c r="B2976" s="5" t="s">
         <v>5534</v>
@@ -42176,7 +42176,7 @@
     </row>
     <row r="2977" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2977" s="2" t="s">
-        <v>5950</v>
+        <v>5949</v>
       </c>
       <c r="B2977" s="5" t="s">
         <v>5535</v>
@@ -42184,7 +42184,7 @@
     </row>
     <row r="2978" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2978" s="2" t="s">
-        <v>5951</v>
+        <v>5950</v>
       </c>
       <c r="B2978" s="5" t="s">
         <v>5536</v>
@@ -42192,7 +42192,7 @@
     </row>
     <row r="2979" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2979" s="2" t="s">
-        <v>5952</v>
+        <v>5951</v>
       </c>
       <c r="B2979" s="5" t="s">
         <v>5537</v>
@@ -42200,7 +42200,7 @@
     </row>
     <row r="2980" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2980" s="2" t="s">
-        <v>5953</v>
+        <v>5952</v>
       </c>
       <c r="B2980" s="5" t="s">
         <v>5538</v>
@@ -42208,7 +42208,7 @@
     </row>
     <row r="2981" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2981" s="2" t="s">
-        <v>5954</v>
+        <v>5953</v>
       </c>
       <c r="B2981" s="5" t="s">
         <v>5539</v>
@@ -42443,7 +42443,7 @@
         <v>5593</v>
       </c>
       <c r="B3010" s="5" t="s">
-        <v>5853</v>
+        <v>5852</v>
       </c>
     </row>
     <row r="3011" spans="1:2" x14ac:dyDescent="0.25">
@@ -42779,7 +42779,7 @@
         <v>5676</v>
       </c>
       <c r="B3052" s="5" t="s">
-        <v>5879</v>
+        <v>5878</v>
       </c>
     </row>
     <row r="3053" spans="1:2" x14ac:dyDescent="0.25">
@@ -42803,191 +42803,191 @@
         <v>5681</v>
       </c>
       <c r="B3055" s="5" t="s">
-        <v>5854</v>
+        <v>5853</v>
       </c>
     </row>
     <row r="3056" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3056" s="3" t="s">
+        <v>5968</v>
+      </c>
+      <c r="B3056" s="5" t="s">
         <v>5682</v>
-      </c>
-      <c r="B3056" s="5" t="s">
-        <v>5683</v>
       </c>
     </row>
     <row r="3057" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3057" s="3" t="s">
+        <v>5683</v>
+      </c>
+      <c r="B3057" s="5" t="s">
         <v>5684</v>
-      </c>
-      <c r="B3057" s="5" t="s">
-        <v>5685</v>
       </c>
     </row>
     <row r="3058" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3058" s="3" t="s">
+        <v>5685</v>
+      </c>
+      <c r="B3058" s="5" t="s">
         <v>5686</v>
-      </c>
-      <c r="B3058" s="5" t="s">
-        <v>5687</v>
       </c>
     </row>
     <row r="3059" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3059" s="3" t="s">
+        <v>5687</v>
+      </c>
+      <c r="B3059" s="5" t="s">
         <v>5688</v>
-      </c>
-      <c r="B3059" s="5" t="s">
-        <v>5689</v>
       </c>
     </row>
     <row r="3060" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3060" s="9" t="s">
-        <v>5888</v>
+        <v>5887</v>
       </c>
       <c r="B3060" s="5" t="s">
-        <v>5690</v>
+        <v>5689</v>
       </c>
     </row>
     <row r="3061" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3061" s="3" t="s">
+        <v>5690</v>
+      </c>
+      <c r="B3061" s="5" t="s">
         <v>5691</v>
-      </c>
-      <c r="B3061" s="5" t="s">
-        <v>5692</v>
       </c>
     </row>
     <row r="3062" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3062" s="3" t="s">
+        <v>5692</v>
+      </c>
+      <c r="B3062" s="5" t="s">
         <v>5693</v>
-      </c>
-      <c r="B3062" s="5" t="s">
-        <v>5694</v>
       </c>
     </row>
     <row r="3063" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3063" s="3" t="s">
+        <v>5694</v>
+      </c>
+      <c r="B3063" s="5" t="s">
         <v>5695</v>
-      </c>
-      <c r="B3063" s="5" t="s">
-        <v>5696</v>
       </c>
     </row>
     <row r="3064" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3064" s="3" t="s">
+        <v>5696</v>
+      </c>
+      <c r="B3064" s="5" t="s">
         <v>5697</v>
-      </c>
-      <c r="B3064" s="5" t="s">
-        <v>5698</v>
       </c>
     </row>
     <row r="3065" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3065" s="3" t="s">
+        <v>5698</v>
+      </c>
+      <c r="B3065" s="5" t="s">
         <v>5699</v>
-      </c>
-      <c r="B3065" s="5" t="s">
-        <v>5700</v>
       </c>
     </row>
     <row r="3066" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3066" s="3" t="s">
+        <v>5700</v>
+      </c>
+      <c r="B3066" s="5" t="s">
         <v>5701</v>
-      </c>
-      <c r="B3066" s="5" t="s">
-        <v>5702</v>
       </c>
     </row>
     <row r="3067" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3067" s="3" t="s">
+        <v>5702</v>
+      </c>
+      <c r="B3067" s="5" t="s">
         <v>5703</v>
-      </c>
-      <c r="B3067" s="5" t="s">
-        <v>5704</v>
       </c>
     </row>
     <row r="3068" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3068" s="3" t="s">
-        <v>5705</v>
+        <v>5704</v>
       </c>
       <c r="B3068" s="5" t="s">
-        <v>5855</v>
+        <v>5854</v>
       </c>
     </row>
     <row r="3069" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3069" s="3" t="s">
+        <v>5705</v>
+      </c>
+      <c r="B3069" s="5" t="s">
         <v>5706</v>
-      </c>
-      <c r="B3069" s="5" t="s">
-        <v>5707</v>
       </c>
     </row>
     <row r="3070" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3070" s="3" t="s">
+        <v>5707</v>
+      </c>
+      <c r="B3070" s="5" t="s">
         <v>5708</v>
-      </c>
-      <c r="B3070" s="5" t="s">
-        <v>5709</v>
       </c>
     </row>
     <row r="3071" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3071" s="3" t="s">
+        <v>5709</v>
+      </c>
+      <c r="B3071" s="5" t="s">
         <v>5710</v>
-      </c>
-      <c r="B3071" s="5" t="s">
-        <v>5711</v>
       </c>
     </row>
     <row r="3072" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3072" s="3" t="s">
+        <v>5711</v>
+      </c>
+      <c r="B3072" s="5" t="s">
         <v>5712</v>
-      </c>
-      <c r="B3072" s="5" t="s">
-        <v>5713</v>
       </c>
     </row>
     <row r="3073" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3073" s="3" t="s">
+        <v>5713</v>
+      </c>
+      <c r="B3073" s="5" t="s">
         <v>5714</v>
-      </c>
-      <c r="B3073" s="5" t="s">
-        <v>5715</v>
       </c>
     </row>
     <row r="3074" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3074" s="3" t="s">
+        <v>5715</v>
+      </c>
+      <c r="B3074" s="5" t="s">
         <v>5716</v>
-      </c>
-      <c r="B3074" s="5" t="s">
-        <v>5717</v>
       </c>
     </row>
     <row r="3075" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3075" s="3" t="s">
+        <v>5717</v>
+      </c>
+      <c r="B3075" s="5" t="s">
         <v>5718</v>
-      </c>
-      <c r="B3075" s="5" t="s">
-        <v>5719</v>
       </c>
     </row>
     <row r="3076" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3076" s="3" t="s">
+        <v>5719</v>
+      </c>
+      <c r="B3076" s="5" t="s">
         <v>5720</v>
-      </c>
-      <c r="B3076" s="5" t="s">
-        <v>5721</v>
       </c>
     </row>
     <row r="3077" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3077" s="3" t="s">
+        <v>5721</v>
+      </c>
+      <c r="B3077" s="5" t="s">
         <v>5722</v>
-      </c>
-      <c r="B3077" s="5" t="s">
-        <v>5723</v>
       </c>
     </row>
     <row r="3078" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3078" s="3" t="s">
+        <v>5723</v>
+      </c>
+      <c r="B3078" s="5" t="s">
         <v>5724</v>
-      </c>
-      <c r="B3078" s="5" t="s">
-        <v>5725</v>
       </c>
     </row>
   </sheetData>

--- a/englisch.xlsx
+++ b/englisch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nutzer\Desktop\Vokabellernspiel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E3A18D-5881-467C-9A75-7C9AC9588E8C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EF111A2-80EB-4CDF-9F8B-39CA63F095EB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="8655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17070,6 +17070,9 @@
     <t>Du siehst europäisch aus.</t>
   </si>
   <si>
+    <t>Das ist sehr deutsch.</t>
+  </si>
+  <si>
     <t>That is very german.</t>
   </si>
   <si>
@@ -17926,9 +17929,6 @@
   </si>
   <si>
     <t>Ihr (formell Du)</t>
-  </si>
-  <si>
-    <t>Das ist sehr schweiz.</t>
   </si>
 </sst>
 </file>
@@ -19067,7 +19067,7 @@
         <v>174</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>5750</v>
+        <v>5751</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -19080,7 +19080,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>5962</v>
+        <v>5963</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>177</v>
@@ -19112,7 +19112,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>5963</v>
+        <v>5964</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>184</v>
@@ -19120,7 +19120,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>5964</v>
+        <v>5965</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>185</v>
@@ -19152,7 +19152,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>5965</v>
+        <v>5966</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>191</v>
@@ -19163,7 +19163,7 @@
         <v>32</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>5960</v>
+        <v>5961</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -19184,7 +19184,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>5966</v>
+        <v>5967</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>195</v>
@@ -19192,7 +19192,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>5967</v>
+        <v>5968</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>196</v>
@@ -19235,7 +19235,7 @@
         <v>205</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>5725</v>
+        <v>5726</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -19251,7 +19251,7 @@
         <v>208</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>5855</v>
+        <v>5856</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -19283,7 +19283,7 @@
         <v>215</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>5726</v>
+        <v>5727</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -19291,7 +19291,7 @@
         <v>216</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>5727</v>
+        <v>5728</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -19419,7 +19419,7 @@
         <v>247</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>5959</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -19443,7 +19443,7 @@
         <v>252</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>5728</v>
+        <v>5729</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -19507,12 +19507,12 @@
         <v>267</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>5729</v>
+        <v>5730</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>5749</v>
+        <v>5750</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>268</v>
@@ -19523,7 +19523,7 @@
         <v>269</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>5751</v>
+        <v>5752</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -19587,7 +19587,7 @@
         <v>284</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>5958</v>
+        <v>5959</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -19603,7 +19603,7 @@
         <v>287</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>5730</v>
+        <v>5731</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -19627,7 +19627,7 @@
         <v>292</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>5731</v>
+        <v>5732</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -19635,7 +19635,7 @@
         <v>293</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>5752</v>
+        <v>5753</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -19643,7 +19643,7 @@
         <v>294</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>5732</v>
+        <v>5733</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -19691,7 +19691,7 @@
         <v>305</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>5961</v>
+        <v>5962</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -19739,7 +19739,7 @@
         <v>316</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>5733</v>
+        <v>5734</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -19867,7 +19867,7 @@
         <v>346</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>5734</v>
+        <v>5735</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -19899,7 +19899,7 @@
         <v>353</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>5735</v>
+        <v>5736</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -20403,7 +20403,7 @@
         <v>474</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>5753</v>
+        <v>5754</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
@@ -20475,7 +20475,7 @@
         <v>491</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>5754</v>
+        <v>5755</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
@@ -20619,7 +20619,7 @@
         <v>524</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>5755</v>
+        <v>5756</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
@@ -21155,7 +21155,7 @@
         <v>653</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>5756</v>
+        <v>5757</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
@@ -21283,7 +21283,7 @@
         <v>683</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>5736</v>
+        <v>5737</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
@@ -21427,7 +21427,7 @@
         <v>718</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>5757</v>
+        <v>5758</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
@@ -21459,7 +21459,7 @@
         <v>725</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>5758</v>
+        <v>5759</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
@@ -21483,7 +21483,7 @@
         <v>730</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
@@ -21547,7 +21547,7 @@
         <v>745</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>5760</v>
+        <v>5761</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
@@ -21555,7 +21555,7 @@
         <v>746</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>5856</v>
+        <v>5857</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
@@ -21595,7 +21595,7 @@
         <v>755</v>
       </c>
       <c r="B404" s="5" t="s">
-        <v>5857</v>
+        <v>5858</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
@@ -21603,7 +21603,7 @@
         <v>756</v>
       </c>
       <c r="B405" s="5" t="s">
-        <v>5761</v>
+        <v>5762</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
@@ -21611,7 +21611,7 @@
         <v>757</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>5762</v>
+        <v>5763</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
@@ -21627,7 +21627,7 @@
         <v>760</v>
       </c>
       <c r="B408" s="5" t="s">
-        <v>5763</v>
+        <v>5764</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
@@ -21667,7 +21667,7 @@
         <v>769</v>
       </c>
       <c r="B413" s="5" t="s">
-        <v>5737</v>
+        <v>5738</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
@@ -21675,7 +21675,7 @@
         <v>770</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>5738</v>
+        <v>5739</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
@@ -21747,7 +21747,7 @@
         <v>787</v>
       </c>
       <c r="B423" s="5" t="s">
-        <v>5739</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
@@ -21787,7 +21787,7 @@
         <v>796</v>
       </c>
       <c r="B428" s="5" t="s">
-        <v>5740</v>
+        <v>5741</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
@@ -22131,7 +22131,7 @@
         <v>862</v>
       </c>
       <c r="B471" s="5" t="s">
-        <v>5764</v>
+        <v>5765</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.25">
@@ -22203,7 +22203,7 @@
         <v>879</v>
       </c>
       <c r="B480" s="5" t="s">
-        <v>5741</v>
+        <v>5742</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.25">
@@ -22624,7 +22624,7 @@
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>5888</v>
+        <v>5889</v>
       </c>
       <c r="B533" s="5" t="s">
         <v>978</v>
@@ -22640,15 +22640,15 @@
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>5889</v>
+        <v>5890</v>
       </c>
       <c r="B535" s="5" t="s">
-        <v>5765</v>
+        <v>5766</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
-        <v>5890</v>
+        <v>5891</v>
       </c>
       <c r="B536" s="5" t="s">
         <v>981</v>
@@ -23299,7 +23299,7 @@
         <v>1137</v>
       </c>
       <c r="B617" s="5" t="s">
-        <v>5766</v>
+        <v>5767</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.25">
@@ -23355,7 +23355,7 @@
         <v>1150</v>
       </c>
       <c r="B624" s="5" t="s">
-        <v>5767</v>
+        <v>5768</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.25">
@@ -23363,7 +23363,7 @@
         <v>1151</v>
       </c>
       <c r="B625" s="5" t="s">
-        <v>5768</v>
+        <v>5769</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.25">
@@ -23571,7 +23571,7 @@
         <v>1202</v>
       </c>
       <c r="B651" s="5" t="s">
-        <v>5769</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.25">
@@ -23851,7 +23851,7 @@
         <v>1269</v>
       </c>
       <c r="B686" s="5" t="s">
-        <v>5742</v>
+        <v>5743</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.25">
@@ -23915,7 +23915,7 @@
         <v>1284</v>
       </c>
       <c r="B694" s="5" t="s">
-        <v>5743</v>
+        <v>5744</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.25">
@@ -23971,7 +23971,7 @@
         <v>1297</v>
       </c>
       <c r="B701" s="5" t="s">
-        <v>5858</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.25">
@@ -23979,7 +23979,7 @@
         <v>1298</v>
       </c>
       <c r="B702" s="5" t="s">
-        <v>5859</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.25">
@@ -23995,7 +23995,7 @@
         <v>1301</v>
       </c>
       <c r="B704" s="5" t="s">
-        <v>5744</v>
+        <v>5745</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.25">
@@ -24163,7 +24163,7 @@
         <v>1342</v>
       </c>
       <c r="B725" s="5" t="s">
-        <v>5860</v>
+        <v>5861</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.25">
@@ -24227,7 +24227,7 @@
         <v>1357</v>
       </c>
       <c r="B733" s="5" t="s">
-        <v>5770</v>
+        <v>5771</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.25">
@@ -24283,7 +24283,7 @@
         <v>1370</v>
       </c>
       <c r="B740" s="5" t="s">
-        <v>5771</v>
+        <v>5772</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.25">
@@ -24355,12 +24355,12 @@
         <v>1387</v>
       </c>
       <c r="B749" s="5" t="s">
-        <v>5772</v>
+        <v>5773</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A750" s="7" t="s">
-        <v>5879</v>
+        <v>5880</v>
       </c>
       <c r="B750" s="5" t="s">
         <v>1388</v>
@@ -24411,7 +24411,7 @@
         <v>1397</v>
       </c>
       <c r="B756" s="5" t="s">
-        <v>5773</v>
+        <v>5774</v>
       </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.25">
@@ -24443,7 +24443,7 @@
         <v>1404</v>
       </c>
       <c r="B760" s="5" t="s">
-        <v>5774</v>
+        <v>5775</v>
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.25">
@@ -24451,7 +24451,7 @@
         <v>1405</v>
       </c>
       <c r="B761" s="5" t="s">
-        <v>5775</v>
+        <v>5776</v>
       </c>
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.25">
@@ -24467,12 +24467,12 @@
         <v>1408</v>
       </c>
       <c r="B763" s="5" t="s">
-        <v>5776</v>
+        <v>5777</v>
       </c>
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A764" s="7" t="s">
-        <v>5880</v>
+        <v>5881</v>
       </c>
       <c r="B764" s="5" t="s">
         <v>1409</v>
@@ -24499,7 +24499,7 @@
         <v>347</v>
       </c>
       <c r="B767" s="5" t="s">
-        <v>5777</v>
+        <v>5778</v>
       </c>
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.25">
@@ -24579,7 +24579,7 @@
         <v>1432</v>
       </c>
       <c r="B777" s="5" t="s">
-        <v>5778</v>
+        <v>5779</v>
       </c>
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.25">
@@ -24651,7 +24651,7 @@
         <v>1449</v>
       </c>
       <c r="B786" s="5" t="s">
-        <v>5745</v>
+        <v>5746</v>
       </c>
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.25">
@@ -24899,7 +24899,7 @@
         <v>1510</v>
       </c>
       <c r="B817" s="5" t="s">
-        <v>5779</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="818" spans="1:2" x14ac:dyDescent="0.25">
@@ -24931,7 +24931,7 @@
         <v>1517</v>
       </c>
       <c r="B821" s="5" t="s">
-        <v>5780</v>
+        <v>5781</v>
       </c>
     </row>
     <row r="822" spans="1:2" x14ac:dyDescent="0.25">
@@ -24979,7 +24979,7 @@
         <v>1528</v>
       </c>
       <c r="B827" s="5" t="s">
-        <v>5861</v>
+        <v>5862</v>
       </c>
     </row>
     <row r="828" spans="1:2" x14ac:dyDescent="0.25">
@@ -24995,7 +24995,7 @@
         <v>1284</v>
       </c>
       <c r="B829" s="5" t="s">
-        <v>5862</v>
+        <v>5863</v>
       </c>
     </row>
     <row r="830" spans="1:2" x14ac:dyDescent="0.25">
@@ -25003,7 +25003,7 @@
         <v>1531</v>
       </c>
       <c r="B830" s="5" t="s">
-        <v>5863</v>
+        <v>5864</v>
       </c>
     </row>
     <row r="831" spans="1:2" x14ac:dyDescent="0.25">
@@ -25163,7 +25163,7 @@
         <v>1570</v>
       </c>
       <c r="B850" s="5" t="s">
-        <v>5864</v>
+        <v>5865</v>
       </c>
     </row>
     <row r="851" spans="1:2" x14ac:dyDescent="0.25">
@@ -25203,7 +25203,7 @@
         <v>1578</v>
       </c>
       <c r="B855" s="5" t="s">
-        <v>5781</v>
+        <v>5782</v>
       </c>
     </row>
     <row r="856" spans="1:2" x14ac:dyDescent="0.25">
@@ -25227,7 +25227,7 @@
         <v>1583</v>
       </c>
       <c r="B858" s="5" t="s">
-        <v>5782</v>
+        <v>5783</v>
       </c>
     </row>
     <row r="859" spans="1:2" x14ac:dyDescent="0.25">
@@ -25299,7 +25299,7 @@
         <v>1600</v>
       </c>
       <c r="B867" s="5" t="s">
-        <v>5746</v>
+        <v>5747</v>
       </c>
     </row>
     <row r="868" spans="1:2" x14ac:dyDescent="0.25">
@@ -25411,7 +25411,7 @@
         <v>1626</v>
       </c>
       <c r="B881" s="5" t="s">
-        <v>5783</v>
+        <v>5784</v>
       </c>
     </row>
     <row r="882" spans="1:2" x14ac:dyDescent="0.25">
@@ -25443,7 +25443,7 @@
         <v>1633</v>
       </c>
       <c r="B885" s="5" t="s">
-        <v>5784</v>
+        <v>5785</v>
       </c>
     </row>
     <row r="886" spans="1:2" x14ac:dyDescent="0.25">
@@ -25467,7 +25467,7 @@
         <v>1636</v>
       </c>
       <c r="B888" s="5" t="s">
-        <v>5785</v>
+        <v>5786</v>
       </c>
     </row>
     <row r="889" spans="1:2" x14ac:dyDescent="0.25">
@@ -25611,7 +25611,7 @@
         <v>1669</v>
       </c>
       <c r="B906" s="5" t="s">
-        <v>5786</v>
+        <v>5787</v>
       </c>
     </row>
     <row r="907" spans="1:2" x14ac:dyDescent="0.25">
@@ -25675,7 +25675,7 @@
         <v>1684</v>
       </c>
       <c r="B914" s="5" t="s">
-        <v>5787</v>
+        <v>5788</v>
       </c>
     </row>
     <row r="915" spans="1:2" x14ac:dyDescent="0.25">
@@ -25907,7 +25907,7 @@
         <v>1740</v>
       </c>
       <c r="B943" s="5" t="s">
-        <v>5788</v>
+        <v>5789</v>
       </c>
     </row>
     <row r="944" spans="1:2" x14ac:dyDescent="0.25">
@@ -25931,7 +25931,7 @@
         <v>1745</v>
       </c>
       <c r="B946" s="5" t="s">
-        <v>5789</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="947" spans="1:2" x14ac:dyDescent="0.25">
@@ -26651,7 +26651,7 @@
         <v>1922</v>
       </c>
       <c r="B1036" s="5" t="s">
-        <v>5790</v>
+        <v>5791</v>
       </c>
     </row>
     <row r="1037" spans="1:2" x14ac:dyDescent="0.25">
@@ -27040,7 +27040,7 @@
     </row>
     <row r="1085" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1085" s="2" t="s">
-        <v>5891</v>
+        <v>5892</v>
       </c>
       <c r="B1085" s="5" t="s">
         <v>2009</v>
@@ -27056,7 +27056,7 @@
     </row>
     <row r="1087" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1087" s="2" t="s">
-        <v>5892</v>
+        <v>5893</v>
       </c>
       <c r="B1087" s="5" t="s">
         <v>2012</v>
@@ -27835,7 +27835,7 @@
         <v>2202</v>
       </c>
       <c r="B1184" s="5" t="s">
-        <v>5791</v>
+        <v>5792</v>
       </c>
     </row>
     <row r="1185" spans="1:2" x14ac:dyDescent="0.25">
@@ -27899,7 +27899,7 @@
         <v>2217</v>
       </c>
       <c r="B1192" s="5" t="s">
-        <v>5792</v>
+        <v>5793</v>
       </c>
     </row>
     <row r="1193" spans="1:2" x14ac:dyDescent="0.25">
@@ -27936,7 +27936,7 @@
     </row>
     <row r="1197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1197" s="7" t="s">
-        <v>5881</v>
+        <v>5882</v>
       </c>
       <c r="B1197" s="5" t="s">
         <v>2226</v>
@@ -28059,7 +28059,7 @@
         <v>2255</v>
       </c>
       <c r="B1212" s="8" t="s">
-        <v>5793</v>
+        <v>5794</v>
       </c>
     </row>
     <row r="1213" spans="1:2" x14ac:dyDescent="0.25">
@@ -28155,7 +28155,7 @@
         <v>2278</v>
       </c>
       <c r="B1224" s="5" t="s">
-        <v>5794</v>
+        <v>5795</v>
       </c>
     </row>
     <row r="1225" spans="1:2" x14ac:dyDescent="0.25">
@@ -28331,7 +28331,7 @@
         <v>2321</v>
       </c>
       <c r="B1246" s="5" t="s">
-        <v>5795</v>
+        <v>5796</v>
       </c>
     </row>
     <row r="1247" spans="1:2" x14ac:dyDescent="0.25">
@@ -28544,7 +28544,7 @@
     </row>
     <row r="1273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1273" s="7" t="s">
-        <v>5882</v>
+        <v>5883</v>
       </c>
       <c r="B1273" s="5" t="s">
         <v>2374</v>
@@ -28555,7 +28555,7 @@
         <v>2375</v>
       </c>
       <c r="B1274" s="5" t="s">
-        <v>5796</v>
+        <v>5797</v>
       </c>
     </row>
     <row r="1275" spans="1:2" x14ac:dyDescent="0.25">
@@ -28619,7 +28619,7 @@
         <v>2390</v>
       </c>
       <c r="B1282" s="5" t="s">
-        <v>5865</v>
+        <v>5866</v>
       </c>
     </row>
     <row r="1283" spans="1:2" x14ac:dyDescent="0.25">
@@ -28995,7 +28995,7 @@
         <v>2483</v>
       </c>
       <c r="B1329" s="5" t="s">
-        <v>5797</v>
+        <v>5798</v>
       </c>
     </row>
     <row r="1330" spans="1:2" x14ac:dyDescent="0.25">
@@ -29451,7 +29451,7 @@
         <v>2592</v>
       </c>
       <c r="B1386" s="5" t="s">
-        <v>5798</v>
+        <v>5799</v>
       </c>
     </row>
     <row r="1387" spans="1:2" x14ac:dyDescent="0.25">
@@ -30288,7 +30288,7 @@
     </row>
     <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1491" s="2" t="s">
-        <v>5954</v>
+        <v>5955</v>
       </c>
       <c r="B1491" s="5" t="s">
         <v>2795</v>
@@ -30331,7 +30331,7 @@
         <v>2804</v>
       </c>
       <c r="B1496" s="5" t="s">
-        <v>5799</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
@@ -30379,7 +30379,7 @@
         <v>2813</v>
       </c>
       <c r="B1502" s="5" t="s">
-        <v>5800</v>
+        <v>5801</v>
       </c>
     </row>
     <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
@@ -30395,7 +30395,7 @@
         <v>2816</v>
       </c>
       <c r="B1504" s="5" t="s">
-        <v>5801</v>
+        <v>5802</v>
       </c>
     </row>
     <row r="1505" spans="1:2" x14ac:dyDescent="0.25">
@@ -30416,7 +30416,7 @@
     </row>
     <row r="1507" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1507" s="1" t="s">
-        <v>5955</v>
+        <v>5956</v>
       </c>
       <c r="B1507" s="5" t="s">
         <v>2821</v>
@@ -30427,7 +30427,7 @@
         <v>2822</v>
       </c>
       <c r="B1508" s="5" t="s">
-        <v>5802</v>
+        <v>5803</v>
       </c>
     </row>
     <row r="1509" spans="1:2" x14ac:dyDescent="0.25">
@@ -30931,7 +30931,7 @@
         <v>2935</v>
       </c>
       <c r="B1571" s="5" t="s">
-        <v>5866</v>
+        <v>5867</v>
       </c>
     </row>
     <row r="1572" spans="1:2" x14ac:dyDescent="0.25">
@@ -30979,7 +30979,7 @@
         <v>2946</v>
       </c>
       <c r="B1577" s="5" t="s">
-        <v>5867</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="1578" spans="1:2" x14ac:dyDescent="0.25">
@@ -31019,7 +31019,7 @@
         <v>2955</v>
       </c>
       <c r="B1582" s="5" t="s">
-        <v>5747</v>
+        <v>5748</v>
       </c>
     </row>
     <row r="1583" spans="1:2" x14ac:dyDescent="0.25">
@@ -31035,7 +31035,7 @@
         <v>2958</v>
       </c>
       <c r="B1584" s="5" t="s">
-        <v>5803</v>
+        <v>5804</v>
       </c>
     </row>
     <row r="1585" spans="1:2" x14ac:dyDescent="0.25">
@@ -31259,7 +31259,7 @@
         <v>3013</v>
       </c>
       <c r="B1612" s="5" t="s">
-        <v>5748</v>
+        <v>5749</v>
       </c>
     </row>
     <row r="1613" spans="1:2" x14ac:dyDescent="0.25">
@@ -31299,7 +31299,7 @@
         <v>3022</v>
       </c>
       <c r="B1617" s="5" t="s">
-        <v>5804</v>
+        <v>5805</v>
       </c>
     </row>
     <row r="1618" spans="1:2" x14ac:dyDescent="0.25">
@@ -31395,7 +31395,7 @@
         <v>3045</v>
       </c>
       <c r="B1629" s="5" t="s">
-        <v>5805</v>
+        <v>5806</v>
       </c>
     </row>
     <row r="1630" spans="1:2" x14ac:dyDescent="0.25">
@@ -31419,7 +31419,7 @@
         <v>3050</v>
       </c>
       <c r="B1632" s="5" t="s">
-        <v>5806</v>
+        <v>5807</v>
       </c>
     </row>
     <row r="1633" spans="1:2" x14ac:dyDescent="0.25">
@@ -31432,7 +31432,7 @@
     </row>
     <row r="1634" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1634" s="9" t="s">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="B1634" s="5" t="s">
         <v>3053</v>
@@ -31475,7 +31475,7 @@
         <v>3062</v>
       </c>
       <c r="B1639" s="5" t="s">
-        <v>5868</v>
+        <v>5869</v>
       </c>
     </row>
     <row r="1640" spans="1:2" x14ac:dyDescent="0.25">
@@ -31531,7 +31531,7 @@
         <v>3075</v>
       </c>
       <c r="B1646" s="5" t="s">
-        <v>5807</v>
+        <v>5808</v>
       </c>
     </row>
     <row r="1647" spans="1:2" x14ac:dyDescent="0.25">
@@ -31659,7 +31659,7 @@
         <v>3106</v>
       </c>
       <c r="B1662" s="5" t="s">
-        <v>5808</v>
+        <v>5809</v>
       </c>
     </row>
     <row r="1663" spans="1:2" x14ac:dyDescent="0.25">
@@ -31843,7 +31843,7 @@
         <v>3151</v>
       </c>
       <c r="B1685" s="5" t="s">
-        <v>5809</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="1686" spans="1:2" x14ac:dyDescent="0.25">
@@ -31963,7 +31963,7 @@
         <v>3180</v>
       </c>
       <c r="B1700" s="5" t="s">
-        <v>5810</v>
+        <v>5811</v>
       </c>
     </row>
     <row r="1701" spans="1:2" x14ac:dyDescent="0.25">
@@ -32059,7 +32059,7 @@
         <v>3203</v>
       </c>
       <c r="B1712" s="5" t="s">
-        <v>5811</v>
+        <v>5812</v>
       </c>
     </row>
     <row r="1713" spans="1:2" x14ac:dyDescent="0.25">
@@ -32075,7 +32075,7 @@
         <v>3206</v>
       </c>
       <c r="B1714" s="5" t="s">
-        <v>5812</v>
+        <v>5813</v>
       </c>
     </row>
     <row r="1715" spans="1:2" x14ac:dyDescent="0.25">
@@ -32131,7 +32131,7 @@
         <v>3219</v>
       </c>
       <c r="B1721" s="5" t="s">
-        <v>5813</v>
+        <v>5814</v>
       </c>
     </row>
     <row r="1722" spans="1:2" x14ac:dyDescent="0.25">
@@ -32139,7 +32139,7 @@
         <v>3220</v>
       </c>
       <c r="B1722" s="5" t="s">
-        <v>5814</v>
+        <v>5815</v>
       </c>
     </row>
     <row r="1723" spans="1:2" x14ac:dyDescent="0.25">
@@ -32219,7 +32219,7 @@
         <v>3239</v>
       </c>
       <c r="B1732" s="5" t="s">
-        <v>5815</v>
+        <v>5816</v>
       </c>
     </row>
     <row r="1733" spans="1:2" x14ac:dyDescent="0.25">
@@ -32856,7 +32856,7 @@
     </row>
     <row r="1812" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1812" s="2" t="s">
-        <v>5893</v>
+        <v>5894</v>
       </c>
       <c r="B1812" s="5" t="s">
         <v>3372</v>
@@ -32872,7 +32872,7 @@
     </row>
     <row r="1814" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1814" s="2" t="s">
-        <v>5956</v>
+        <v>5957</v>
       </c>
       <c r="B1814" s="5" t="s">
         <v>3375</v>
@@ -32928,7 +32928,7 @@
     </row>
     <row r="1821" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1821" s="2" t="s">
-        <v>5894</v>
+        <v>5895</v>
       </c>
       <c r="B1821" s="5" t="s">
         <v>3388</v>
@@ -32995,7 +32995,7 @@
         <v>3403</v>
       </c>
       <c r="B1829" s="5" t="s">
-        <v>5816</v>
+        <v>5817</v>
       </c>
     </row>
     <row r="1830" spans="1:2" x14ac:dyDescent="0.25">
@@ -33035,7 +33035,7 @@
         <v>3412</v>
       </c>
       <c r="B1834" s="5" t="s">
-        <v>5869</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="1835" spans="1:2" x14ac:dyDescent="0.25">
@@ -33771,7 +33771,7 @@
         <v>3577</v>
       </c>
       <c r="B1926" s="5" t="s">
-        <v>5817</v>
+        <v>5818</v>
       </c>
     </row>
     <row r="1927" spans="1:2" x14ac:dyDescent="0.25">
@@ -33907,7 +33907,7 @@
         <v>3610</v>
       </c>
       <c r="B1943" s="5" t="s">
-        <v>5818</v>
+        <v>5819</v>
       </c>
     </row>
     <row r="1944" spans="1:2" x14ac:dyDescent="0.25">
@@ -33987,7 +33987,7 @@
         <v>3629</v>
       </c>
       <c r="B1953" s="5" t="s">
-        <v>5819</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="1954" spans="1:2" x14ac:dyDescent="0.25">
@@ -34043,7 +34043,7 @@
         <v>3642</v>
       </c>
       <c r="B1960" s="5" t="s">
-        <v>5820</v>
+        <v>5821</v>
       </c>
     </row>
     <row r="1961" spans="1:2" x14ac:dyDescent="0.25">
@@ -34259,7 +34259,7 @@
         <v>3695</v>
       </c>
       <c r="B1987" s="5" t="s">
-        <v>5821</v>
+        <v>5822</v>
       </c>
     </row>
     <row r="1988" spans="1:2" x14ac:dyDescent="0.25">
@@ -34296,10 +34296,10 @@
     </row>
     <row r="1992" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1992" s="7" t="s">
-        <v>5884</v>
+        <v>5885</v>
       </c>
       <c r="B1992" s="5" t="s">
-        <v>5885</v>
+        <v>5886</v>
       </c>
     </row>
     <row r="1993" spans="1:2" x14ac:dyDescent="0.25">
@@ -34392,7 +34392,7 @@
     </row>
     <row r="2004" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2004" s="7" t="s">
-        <v>5886</v>
+        <v>5887</v>
       </c>
       <c r="B2004" s="5" t="s">
         <v>3726</v>
@@ -34563,7 +34563,7 @@
         <v>3767</v>
       </c>
       <c r="B2025" s="5" t="s">
-        <v>5822</v>
+        <v>5823</v>
       </c>
     </row>
     <row r="2026" spans="1:2" x14ac:dyDescent="0.25">
@@ -34643,7 +34643,7 @@
         <v>3784</v>
       </c>
       <c r="B2035" s="5" t="s">
-        <v>5870</v>
+        <v>5871</v>
       </c>
     </row>
     <row r="2036" spans="1:2" x14ac:dyDescent="0.25">
@@ -34675,7 +34675,7 @@
         <v>3791</v>
       </c>
       <c r="B2039" s="5" t="s">
-        <v>5823</v>
+        <v>5824</v>
       </c>
     </row>
     <row r="2040" spans="1:2" x14ac:dyDescent="0.25">
@@ -34755,7 +34755,7 @@
         <v>3810</v>
       </c>
       <c r="B2049" s="5" t="s">
-        <v>5871</v>
+        <v>5872</v>
       </c>
     </row>
     <row r="2050" spans="1:2" x14ac:dyDescent="0.25">
@@ -34795,7 +34795,7 @@
         <v>3819</v>
       </c>
       <c r="B2054" s="5" t="s">
-        <v>5824</v>
+        <v>5825</v>
       </c>
     </row>
     <row r="2055" spans="1:2" x14ac:dyDescent="0.25">
@@ -35043,7 +35043,7 @@
         <v>3880</v>
       </c>
       <c r="B2085" s="5" t="s">
-        <v>5825</v>
+        <v>5826</v>
       </c>
     </row>
     <row r="2086" spans="1:2" x14ac:dyDescent="0.25">
@@ -35227,7 +35227,7 @@
         <v>3925</v>
       </c>
       <c r="B2108" s="5" t="s">
-        <v>5826</v>
+        <v>5827</v>
       </c>
     </row>
     <row r="2109" spans="1:2" x14ac:dyDescent="0.25">
@@ -35424,7 +35424,7 @@
     </row>
     <row r="2133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2133" s="2" t="s">
-        <v>5895</v>
+        <v>5896</v>
       </c>
       <c r="B2133" s="5" t="s">
         <v>3971</v>
@@ -35432,7 +35432,7 @@
     </row>
     <row r="2134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2134" s="2" t="s">
-        <v>5896</v>
+        <v>5897</v>
       </c>
       <c r="B2134" s="5" t="s">
         <v>3972</v>
@@ -35504,7 +35504,7 @@
     </row>
     <row r="2143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2143" s="2" t="s">
-        <v>5897</v>
+        <v>5898</v>
       </c>
       <c r="B2143" s="5" t="s">
         <v>3989</v>
@@ -35520,7 +35520,7 @@
     </row>
     <row r="2145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2145" s="2" t="s">
-        <v>5898</v>
+        <v>5899</v>
       </c>
       <c r="B2145" s="5" t="s">
         <v>3992</v>
@@ -35795,7 +35795,7 @@
         <v>4052</v>
       </c>
       <c r="B2179" s="5" t="s">
-        <v>5827</v>
+        <v>5828</v>
       </c>
     </row>
     <row r="2180" spans="1:2" x14ac:dyDescent="0.25">
@@ -36107,7 +36107,7 @@
         <v>4129</v>
       </c>
       <c r="B2218" s="5" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
     </row>
     <row r="2219" spans="1:2" x14ac:dyDescent="0.25">
@@ -36203,7 +36203,7 @@
         <v>4152</v>
       </c>
       <c r="B2230" s="5" t="s">
-        <v>5829</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="2231" spans="1:2" x14ac:dyDescent="0.25">
@@ -36283,7 +36283,7 @@
         <v>4171</v>
       </c>
       <c r="B2240" s="5" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
     </row>
     <row r="2241" spans="1:2" x14ac:dyDescent="0.25">
@@ -36560,7 +36560,7 @@
     </row>
     <row r="2275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2275" s="2" t="s">
-        <v>5899</v>
+        <v>5900</v>
       </c>
       <c r="B2275" s="5" t="s">
         <v>4236</v>
@@ -36584,7 +36584,7 @@
     </row>
     <row r="2278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2278" s="2" t="s">
-        <v>5900</v>
+        <v>5901</v>
       </c>
       <c r="B2278" s="5" t="s">
         <v>4241</v>
@@ -36592,7 +36592,7 @@
     </row>
     <row r="2279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2279" s="2" t="s">
-        <v>5901</v>
+        <v>5902</v>
       </c>
       <c r="B2279" s="5" t="s">
         <v>4242</v>
@@ -36608,7 +36608,7 @@
     </row>
     <row r="2281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2281" s="2" t="s">
-        <v>5902</v>
+        <v>5903</v>
       </c>
       <c r="B2281" s="5" t="s">
         <v>4245</v>
@@ -36616,7 +36616,7 @@
     </row>
     <row r="2282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2282" s="2" t="s">
-        <v>5903</v>
+        <v>5904</v>
       </c>
       <c r="B2282" s="5" t="s">
         <v>4246</v>
@@ -37139,7 +37139,7 @@
         <v>4371</v>
       </c>
       <c r="B2347" s="5" t="s">
-        <v>5831</v>
+        <v>5832</v>
       </c>
     </row>
     <row r="2348" spans="1:2" x14ac:dyDescent="0.25">
@@ -37243,7 +37243,7 @@
         <v>4396</v>
       </c>
       <c r="B2360" s="5" t="s">
-        <v>5832</v>
+        <v>5833</v>
       </c>
     </row>
     <row r="2361" spans="1:2" x14ac:dyDescent="0.25">
@@ -37259,7 +37259,7 @@
         <v>4399</v>
       </c>
       <c r="B2362" s="5" t="s">
-        <v>5833</v>
+        <v>5834</v>
       </c>
     </row>
     <row r="2363" spans="1:2" x14ac:dyDescent="0.25">
@@ -37515,7 +37515,7 @@
         <v>4462</v>
       </c>
       <c r="B2394" s="5" t="s">
-        <v>5834</v>
+        <v>5835</v>
       </c>
     </row>
     <row r="2395" spans="1:2" x14ac:dyDescent="0.25">
@@ -37643,7 +37643,7 @@
         <v>4493</v>
       </c>
       <c r="B2410" s="5" t="s">
-        <v>5835</v>
+        <v>5836</v>
       </c>
     </row>
     <row r="2411" spans="1:2" x14ac:dyDescent="0.25">
@@ -37651,7 +37651,7 @@
         <v>4494</v>
       </c>
       <c r="B2411" s="5" t="s">
-        <v>5836</v>
+        <v>5837</v>
       </c>
     </row>
     <row r="2412" spans="1:2" x14ac:dyDescent="0.25">
@@ -37739,7 +37739,7 @@
         <v>4515</v>
       </c>
       <c r="B2422" s="5" t="s">
-        <v>5837</v>
+        <v>5838</v>
       </c>
     </row>
     <row r="2423" spans="1:2" x14ac:dyDescent="0.25">
@@ -37856,7 +37856,7 @@
     </row>
     <row r="2437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2437" s="2" t="s">
-        <v>5904</v>
+        <v>5905</v>
       </c>
       <c r="B2437" s="5" t="s">
         <v>4541</v>
@@ -37864,7 +37864,7 @@
     </row>
     <row r="2438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2438" s="2" t="s">
-        <v>5905</v>
+        <v>5906</v>
       </c>
       <c r="B2438" s="5" t="s">
         <v>4542</v>
@@ -38051,7 +38051,7 @@
         <v>4584</v>
       </c>
       <c r="B2461" s="5" t="s">
-        <v>5838</v>
+        <v>5839</v>
       </c>
     </row>
     <row r="2462" spans="1:2" x14ac:dyDescent="0.25">
@@ -38155,7 +38155,7 @@
         <v>4609</v>
       </c>
       <c r="B2474" s="5" t="s">
-        <v>5872</v>
+        <v>5873</v>
       </c>
     </row>
     <row r="2475" spans="1:2" x14ac:dyDescent="0.25">
@@ -38283,7 +38283,7 @@
         <v>4640</v>
       </c>
       <c r="B2490" s="5" t="s">
-        <v>5839</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="2491" spans="1:2" x14ac:dyDescent="0.25">
@@ -38347,7 +38347,7 @@
         <v>4655</v>
       </c>
       <c r="B2498" s="5" t="s">
-        <v>5840</v>
+        <v>5841</v>
       </c>
     </row>
     <row r="2499" spans="1:2" x14ac:dyDescent="0.25">
@@ -38379,7 +38379,7 @@
         <v>4662</v>
       </c>
       <c r="B2502" s="5" t="s">
-        <v>5873</v>
+        <v>5874</v>
       </c>
     </row>
     <row r="2503" spans="1:2" x14ac:dyDescent="0.25">
@@ -38443,7 +38443,7 @@
         <v>4677</v>
       </c>
       <c r="B2510" s="5" t="s">
-        <v>5841</v>
+        <v>5842</v>
       </c>
     </row>
     <row r="2511" spans="1:2" x14ac:dyDescent="0.25">
@@ -38587,7 +38587,7 @@
         <v>4710</v>
       </c>
       <c r="B2528" s="5" t="s">
-        <v>5842</v>
+        <v>5843</v>
       </c>
     </row>
     <row r="2529" spans="1:2" x14ac:dyDescent="0.25">
@@ -38699,7 +38699,7 @@
         <v>4737</v>
       </c>
       <c r="B2542" s="5" t="s">
-        <v>5843</v>
+        <v>5844</v>
       </c>
     </row>
     <row r="2543" spans="1:2" x14ac:dyDescent="0.25">
@@ -38771,7 +38771,7 @@
         <v>4753</v>
       </c>
       <c r="B2551" s="5" t="s">
-        <v>5874</v>
+        <v>5875</v>
       </c>
     </row>
     <row r="2552" spans="1:2" x14ac:dyDescent="0.25">
@@ -38915,7 +38915,7 @@
         <v>4787</v>
       </c>
       <c r="B2569" s="5" t="s">
-        <v>5875</v>
+        <v>5876</v>
       </c>
     </row>
     <row r="2570" spans="1:2" x14ac:dyDescent="0.25">
@@ -39075,7 +39075,7 @@
         <v>4823</v>
       </c>
       <c r="B2589" s="5" t="s">
-        <v>5876</v>
+        <v>5877</v>
       </c>
     </row>
     <row r="2590" spans="1:2" x14ac:dyDescent="0.25">
@@ -39235,7 +39235,7 @@
         <v>4862</v>
       </c>
       <c r="B2609" s="5" t="s">
-        <v>5844</v>
+        <v>5845</v>
       </c>
     </row>
     <row r="2610" spans="1:2" x14ac:dyDescent="0.25">
@@ -39331,7 +39331,7 @@
         <v>4885</v>
       </c>
       <c r="B2621" s="5" t="s">
-        <v>5845</v>
+        <v>5846</v>
       </c>
     </row>
     <row r="2622" spans="1:2" x14ac:dyDescent="0.25">
@@ -39443,7 +39443,7 @@
         <v>4912</v>
       </c>
       <c r="B2635" s="5" t="s">
-        <v>5846</v>
+        <v>5847</v>
       </c>
     </row>
     <row r="2636" spans="1:2" x14ac:dyDescent="0.25">
@@ -39624,7 +39624,7 @@
     </row>
     <row r="2658" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2658" s="2" t="s">
-        <v>5906</v>
+        <v>5907</v>
       </c>
       <c r="B2658" s="5" t="s">
         <v>4953</v>
@@ -39632,7 +39632,7 @@
     </row>
     <row r="2659" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2659" s="2" t="s">
-        <v>5907</v>
+        <v>5908</v>
       </c>
       <c r="B2659" s="5" t="s">
         <v>4954</v>
@@ -39747,7 +39747,7 @@
         <v>4981</v>
       </c>
       <c r="B2673" s="5" t="s">
-        <v>5847</v>
+        <v>5848</v>
       </c>
     </row>
     <row r="2674" spans="1:2" x14ac:dyDescent="0.25">
@@ -39824,7 +39824,7 @@
     </row>
     <row r="2683" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2683" s="2" t="s">
-        <v>5908</v>
+        <v>5909</v>
       </c>
       <c r="B2683" s="5" t="s">
         <v>5000</v>
@@ -39832,7 +39832,7 @@
     </row>
     <row r="2684" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2684" s="2" t="s">
-        <v>5909</v>
+        <v>5910</v>
       </c>
       <c r="B2684" s="5" t="s">
         <v>5001</v>
@@ -39840,7 +39840,7 @@
     </row>
     <row r="2685" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2685" s="2" t="s">
-        <v>5910</v>
+        <v>5911</v>
       </c>
       <c r="B2685" s="5" t="s">
         <v>5002</v>
@@ -39864,7 +39864,7 @@
     </row>
     <row r="2688" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2688" s="2" t="s">
-        <v>5911</v>
+        <v>5912</v>
       </c>
       <c r="B2688" s="5" t="s">
         <v>5007</v>
@@ -39872,7 +39872,7 @@
     </row>
     <row r="2689" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2689" s="2" t="s">
-        <v>5912</v>
+        <v>5913</v>
       </c>
       <c r="B2689" s="5" t="s">
         <v>5008</v>
@@ -39880,7 +39880,7 @@
     </row>
     <row r="2690" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2690" s="2" t="s">
-        <v>5913</v>
+        <v>5914</v>
       </c>
       <c r="B2690" s="5" t="s">
         <v>5009</v>
@@ -39888,7 +39888,7 @@
     </row>
     <row r="2691" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2691" s="2" t="s">
-        <v>5914</v>
+        <v>5915</v>
       </c>
       <c r="B2691" s="5" t="s">
         <v>5010</v>
@@ -39896,7 +39896,7 @@
     </row>
     <row r="2692" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2692" s="2" t="s">
-        <v>5915</v>
+        <v>5916</v>
       </c>
       <c r="B2692" s="5" t="s">
         <v>5011</v>
@@ -39904,7 +39904,7 @@
     </row>
     <row r="2693" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2693" s="2" t="s">
-        <v>5916</v>
+        <v>5917</v>
       </c>
       <c r="B2693" s="5" t="s">
         <v>5012</v>
@@ -39912,7 +39912,7 @@
     </row>
     <row r="2694" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2694" s="2" t="s">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="B2694" s="5" t="s">
         <v>5013</v>
@@ -39920,7 +39920,7 @@
     </row>
     <row r="2695" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2695" s="2" t="s">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="B2695" s="5" t="s">
         <v>5014</v>
@@ -39936,7 +39936,7 @@
     </row>
     <row r="2697" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2697" s="2" t="s">
-        <v>5919</v>
+        <v>5920</v>
       </c>
       <c r="B2697" s="5" t="s">
         <v>5017</v>
@@ -39944,7 +39944,7 @@
     </row>
     <row r="2698" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2698" s="2" t="s">
-        <v>5920</v>
+        <v>5921</v>
       </c>
       <c r="B2698" s="5" t="s">
         <v>5018</v>
@@ -39952,7 +39952,7 @@
     </row>
     <row r="2699" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2699" s="2" t="s">
-        <v>5921</v>
+        <v>5922</v>
       </c>
       <c r="B2699" s="5" t="s">
         <v>5019</v>
@@ -39960,7 +39960,7 @@
     </row>
     <row r="2700" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2700" s="2" t="s">
-        <v>5922</v>
+        <v>5923</v>
       </c>
       <c r="B2700" s="5" t="s">
         <v>5020</v>
@@ -39968,7 +39968,7 @@
     </row>
     <row r="2701" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2701" s="2" t="s">
-        <v>5923</v>
+        <v>5924</v>
       </c>
       <c r="B2701" s="5" t="s">
         <v>5021</v>
@@ -39976,7 +39976,7 @@
     </row>
     <row r="2702" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2702" s="2" t="s">
-        <v>5924</v>
+        <v>5925</v>
       </c>
       <c r="B2702" s="5" t="s">
         <v>5022</v>
@@ -39984,7 +39984,7 @@
     </row>
     <row r="2703" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2703" s="2" t="s">
-        <v>5925</v>
+        <v>5926</v>
       </c>
       <c r="B2703" s="5" t="s">
         <v>5023</v>
@@ -39992,7 +39992,7 @@
     </row>
     <row r="2704" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2704" s="2" t="s">
-        <v>5926</v>
+        <v>5927</v>
       </c>
       <c r="B2704" s="5" t="s">
         <v>5024</v>
@@ -40000,7 +40000,7 @@
     </row>
     <row r="2705" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2705" s="2" t="s">
-        <v>5927</v>
+        <v>5928</v>
       </c>
       <c r="B2705" s="5" t="s">
         <v>5025</v>
@@ -40032,7 +40032,7 @@
     </row>
     <row r="2709" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2709" s="2" t="s">
-        <v>5928</v>
+        <v>5929</v>
       </c>
       <c r="B2709" s="5" t="s">
         <v>5032</v>
@@ -40040,7 +40040,7 @@
     </row>
     <row r="2710" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2710" s="2" t="s">
-        <v>5957</v>
+        <v>5958</v>
       </c>
       <c r="B2710" s="5" t="s">
         <v>5033</v>
@@ -40048,7 +40048,7 @@
     </row>
     <row r="2711" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2711" s="2" t="s">
-        <v>5929</v>
+        <v>5930</v>
       </c>
       <c r="B2711" s="5" t="s">
         <v>5034</v>
@@ -40056,7 +40056,7 @@
     </row>
     <row r="2712" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2712" s="2" t="s">
-        <v>5930</v>
+        <v>5931</v>
       </c>
       <c r="B2712" s="5" t="s">
         <v>5035</v>
@@ -40139,7 +40139,7 @@
         <v>5053</v>
       </c>
       <c r="B2722" s="5" t="s">
-        <v>5848</v>
+        <v>5849</v>
       </c>
     </row>
     <row r="2723" spans="1:2" x14ac:dyDescent="0.25">
@@ -40323,7 +40323,7 @@
         <v>5098</v>
       </c>
       <c r="B2745" s="5" t="s">
-        <v>5849</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="2746" spans="1:2" x14ac:dyDescent="0.25">
@@ -40707,7 +40707,7 @@
         <v>5193</v>
       </c>
       <c r="B2793" s="5" t="s">
-        <v>5850</v>
+        <v>5851</v>
       </c>
     </row>
     <row r="2794" spans="1:2" x14ac:dyDescent="0.25">
@@ -40939,7 +40939,7 @@
         <v>5250</v>
       </c>
       <c r="B2822" s="5" t="s">
-        <v>5851</v>
+        <v>5852</v>
       </c>
     </row>
     <row r="2823" spans="1:2" x14ac:dyDescent="0.25">
@@ -42032,7 +42032,7 @@
     </row>
     <row r="2959" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2959" s="2" t="s">
-        <v>5931</v>
+        <v>5932</v>
       </c>
       <c r="B2959" s="5" t="s">
         <v>5518</v>
@@ -42040,7 +42040,7 @@
     </row>
     <row r="2960" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2960" s="2" t="s">
-        <v>5932</v>
+        <v>5933</v>
       </c>
       <c r="B2960" s="5" t="s">
         <v>5519</v>
@@ -42048,7 +42048,7 @@
     </row>
     <row r="2961" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2961" s="2" t="s">
-        <v>5933</v>
+        <v>5934</v>
       </c>
       <c r="B2961" s="5" t="s">
         <v>5520</v>
@@ -42056,7 +42056,7 @@
     </row>
     <row r="2962" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2962" s="2" t="s">
-        <v>5934</v>
+        <v>5935</v>
       </c>
       <c r="B2962" s="5" t="s">
         <v>5521</v>
@@ -42064,7 +42064,7 @@
     </row>
     <row r="2963" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2963" s="2" t="s">
-        <v>5935</v>
+        <v>5936</v>
       </c>
       <c r="B2963" s="5" t="s">
         <v>5522</v>
@@ -42072,7 +42072,7 @@
     </row>
     <row r="2964" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2964" s="2" t="s">
-        <v>5936</v>
+        <v>5937</v>
       </c>
       <c r="B2964" s="5" t="s">
         <v>5523</v>
@@ -42080,7 +42080,7 @@
     </row>
     <row r="2965" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2965" s="2" t="s">
-        <v>5937</v>
+        <v>5938</v>
       </c>
       <c r="B2965" s="5" t="s">
         <v>5524</v>
@@ -42088,15 +42088,15 @@
     </row>
     <row r="2966" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2966" s="2" t="s">
-        <v>5938</v>
+        <v>5939</v>
       </c>
       <c r="B2966" s="5" t="s">
-        <v>5877</v>
+        <v>5878</v>
       </c>
     </row>
     <row r="2967" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2967" s="2" t="s">
-        <v>5939</v>
+        <v>5940</v>
       </c>
       <c r="B2967" s="5" t="s">
         <v>5525</v>
@@ -42104,7 +42104,7 @@
     </row>
     <row r="2968" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2968" s="2" t="s">
-        <v>5940</v>
+        <v>5941</v>
       </c>
       <c r="B2968" s="5" t="s">
         <v>5526</v>
@@ -42112,7 +42112,7 @@
     </row>
     <row r="2969" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2969" s="2" t="s">
-        <v>5941</v>
+        <v>5942</v>
       </c>
       <c r="B2969" s="5" t="s">
         <v>5527</v>
@@ -42120,7 +42120,7 @@
     </row>
     <row r="2970" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2970" s="2" t="s">
-        <v>5942</v>
+        <v>5943</v>
       </c>
       <c r="B2970" s="5" t="s">
         <v>5528</v>
@@ -42128,7 +42128,7 @@
     </row>
     <row r="2971" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2971" s="2" t="s">
-        <v>5943</v>
+        <v>5944</v>
       </c>
       <c r="B2971" s="5" t="s">
         <v>5529</v>
@@ -42136,7 +42136,7 @@
     </row>
     <row r="2972" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2972" s="2" t="s">
-        <v>5944</v>
+        <v>5945</v>
       </c>
       <c r="B2972" s="5" t="s">
         <v>5530</v>
@@ -42144,7 +42144,7 @@
     </row>
     <row r="2973" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2973" s="2" t="s">
-        <v>5945</v>
+        <v>5946</v>
       </c>
       <c r="B2973" s="5" t="s">
         <v>5531</v>
@@ -42152,7 +42152,7 @@
     </row>
     <row r="2974" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2974" s="2" t="s">
-        <v>5946</v>
+        <v>5947</v>
       </c>
       <c r="B2974" s="5" t="s">
         <v>5532</v>
@@ -42160,7 +42160,7 @@
     </row>
     <row r="2975" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2975" s="2" t="s">
-        <v>5947</v>
+        <v>5948</v>
       </c>
       <c r="B2975" s="5" t="s">
         <v>5533</v>
@@ -42168,7 +42168,7 @@
     </row>
     <row r="2976" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2976" s="2" t="s">
-        <v>5948</v>
+        <v>5949</v>
       </c>
       <c r="B2976" s="5" t="s">
         <v>5534</v>
@@ -42176,7 +42176,7 @@
     </row>
     <row r="2977" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2977" s="2" t="s">
-        <v>5949</v>
+        <v>5950</v>
       </c>
       <c r="B2977" s="5" t="s">
         <v>5535</v>
@@ -42184,7 +42184,7 @@
     </row>
     <row r="2978" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2978" s="2" t="s">
-        <v>5950</v>
+        <v>5951</v>
       </c>
       <c r="B2978" s="5" t="s">
         <v>5536</v>
@@ -42192,7 +42192,7 @@
     </row>
     <row r="2979" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2979" s="2" t="s">
-        <v>5951</v>
+        <v>5952</v>
       </c>
       <c r="B2979" s="5" t="s">
         <v>5537</v>
@@ -42200,7 +42200,7 @@
     </row>
     <row r="2980" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2980" s="2" t="s">
-        <v>5952</v>
+        <v>5953</v>
       </c>
       <c r="B2980" s="5" t="s">
         <v>5538</v>
@@ -42208,7 +42208,7 @@
     </row>
     <row r="2981" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2981" s="2" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="B2981" s="5" t="s">
         <v>5539</v>
@@ -42443,7 +42443,7 @@
         <v>5593</v>
       </c>
       <c r="B3010" s="5" t="s">
-        <v>5852</v>
+        <v>5853</v>
       </c>
     </row>
     <row r="3011" spans="1:2" x14ac:dyDescent="0.25">
@@ -42779,7 +42779,7 @@
         <v>5676</v>
       </c>
       <c r="B3052" s="5" t="s">
-        <v>5878</v>
+        <v>5879</v>
       </c>
     </row>
     <row r="3053" spans="1:2" x14ac:dyDescent="0.25">
@@ -42803,191 +42803,191 @@
         <v>5681</v>
       </c>
       <c r="B3055" s="5" t="s">
-        <v>5853</v>
+        <v>5854</v>
       </c>
     </row>
     <row r="3056" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3056" s="3" t="s">
-        <v>5968</v>
+        <v>5682</v>
       </c>
       <c r="B3056" s="5" t="s">
-        <v>5682</v>
+        <v>5683</v>
       </c>
     </row>
     <row r="3057" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3057" s="3" t="s">
-        <v>5683</v>
+        <v>5684</v>
       </c>
       <c r="B3057" s="5" t="s">
-        <v>5684</v>
+        <v>5685</v>
       </c>
     </row>
     <row r="3058" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3058" s="3" t="s">
-        <v>5685</v>
+        <v>5686</v>
       </c>
       <c r="B3058" s="5" t="s">
-        <v>5686</v>
+        <v>5687</v>
       </c>
     </row>
     <row r="3059" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3059" s="3" t="s">
-        <v>5687</v>
+        <v>5688</v>
       </c>
       <c r="B3059" s="5" t="s">
-        <v>5688</v>
+        <v>5689</v>
       </c>
     </row>
     <row r="3060" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3060" s="9" t="s">
-        <v>5887</v>
+        <v>5888</v>
       </c>
       <c r="B3060" s="5" t="s">
-        <v>5689</v>
+        <v>5690</v>
       </c>
     </row>
     <row r="3061" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3061" s="3" t="s">
-        <v>5690</v>
+        <v>5691</v>
       </c>
       <c r="B3061" s="5" t="s">
-        <v>5691</v>
+        <v>5692</v>
       </c>
     </row>
     <row r="3062" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3062" s="3" t="s">
-        <v>5692</v>
+        <v>5693</v>
       </c>
       <c r="B3062" s="5" t="s">
-        <v>5693</v>
+        <v>5694</v>
       </c>
     </row>
     <row r="3063" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3063" s="3" t="s">
-        <v>5694</v>
+        <v>5695</v>
       </c>
       <c r="B3063" s="5" t="s">
-        <v>5695</v>
+        <v>5696</v>
       </c>
     </row>
     <row r="3064" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3064" s="3" t="s">
-        <v>5696</v>
+        <v>5697</v>
       </c>
       <c r="B3064" s="5" t="s">
-        <v>5697</v>
+        <v>5698</v>
       </c>
     </row>
     <row r="3065" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3065" s="3" t="s">
-        <v>5698</v>
+        <v>5699</v>
       </c>
       <c r="B3065" s="5" t="s">
-        <v>5699</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="3066" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3066" s="3" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="B3066" s="5" t="s">
-        <v>5701</v>
+        <v>5702</v>
       </c>
     </row>
     <row r="3067" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3067" s="3" t="s">
-        <v>5702</v>
+        <v>5703</v>
       </c>
       <c r="B3067" s="5" t="s">
-        <v>5703</v>
+        <v>5704</v>
       </c>
     </row>
     <row r="3068" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3068" s="3" t="s">
-        <v>5704</v>
+        <v>5705</v>
       </c>
       <c r="B3068" s="5" t="s">
-        <v>5854</v>
+        <v>5855</v>
       </c>
     </row>
     <row r="3069" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3069" s="3" t="s">
-        <v>5705</v>
+        <v>5706</v>
       </c>
       <c r="B3069" s="5" t="s">
-        <v>5706</v>
+        <v>5707</v>
       </c>
     </row>
     <row r="3070" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3070" s="3" t="s">
-        <v>5707</v>
+        <v>5708</v>
       </c>
       <c r="B3070" s="5" t="s">
-        <v>5708</v>
+        <v>5709</v>
       </c>
     </row>
     <row r="3071" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3071" s="3" t="s">
-        <v>5709</v>
+        <v>5710</v>
       </c>
       <c r="B3071" s="5" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
     </row>
     <row r="3072" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3072" s="3" t="s">
-        <v>5711</v>
+        <v>5712</v>
       </c>
       <c r="B3072" s="5" t="s">
-        <v>5712</v>
+        <v>5713</v>
       </c>
     </row>
     <row r="3073" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3073" s="3" t="s">
-        <v>5713</v>
+        <v>5714</v>
       </c>
       <c r="B3073" s="5" t="s">
-        <v>5714</v>
+        <v>5715</v>
       </c>
     </row>
     <row r="3074" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3074" s="3" t="s">
-        <v>5715</v>
+        <v>5716</v>
       </c>
       <c r="B3074" s="5" t="s">
-        <v>5716</v>
+        <v>5717</v>
       </c>
     </row>
     <row r="3075" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3075" s="3" t="s">
-        <v>5717</v>
+        <v>5718</v>
       </c>
       <c r="B3075" s="5" t="s">
-        <v>5718</v>
+        <v>5719</v>
       </c>
     </row>
     <row r="3076" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3076" s="3" t="s">
-        <v>5719</v>
+        <v>5720</v>
       </c>
       <c r="B3076" s="5" t="s">
-        <v>5720</v>
+        <v>5721</v>
       </c>
     </row>
     <row r="3077" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3077" s="3" t="s">
-        <v>5721</v>
+        <v>5722</v>
       </c>
       <c r="B3077" s="5" t="s">
-        <v>5722</v>
+        <v>5723</v>
       </c>
     </row>
     <row r="3078" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3078" s="3" t="s">
-        <v>5723</v>
+        <v>5724</v>
       </c>
       <c r="B3078" s="5" t="s">
-        <v>5724</v>
+        <v>5725</v>
       </c>
     </row>
   </sheetData>
